--- a/dados/Campanha Captação.xlsx
+++ b/dados/Campanha Captação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BRUNO.SILVA\Downloads\App campanha\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8114E08-E7C1-44C1-8CA1-5C273E81CD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216263ED-B368-4A0A-A687-08CAD454B7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28875" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{65BC80B7-CA5D-453E-A132-5DB34208399A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$K$991</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$K$985</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4519" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4489" uniqueCount="885">
   <si>
     <t>Corretora</t>
   </si>
@@ -2342,9 +2342,6 @@
     <t>Luca Bueno</t>
   </si>
   <si>
-    <t>Guilherme dos Santos</t>
-  </si>
-  <si>
     <t>Jose Delio de Sa Junior</t>
   </si>
   <si>
@@ -2381,9 +2378,6 @@
     <t>Paulo Coelho Avila</t>
   </si>
   <si>
-    <t>Paulo Henrique de Moraes Mendes</t>
-  </si>
-  <si>
     <t>Sergio Henrique Nunes Pereira</t>
   </si>
   <si>
@@ -2429,34 +2423,16 @@
     <t>Alessandro Lourenco Januario</t>
   </si>
   <si>
-    <t>Jose Washington de Carvalho Novaes</t>
-  </si>
-  <si>
-    <t>Matrice</t>
-  </si>
-  <si>
     <t>Leonardo Jardim</t>
   </si>
   <si>
     <t>Conquest</t>
   </si>
   <si>
-    <t>Marta Maria Prado de Souza Coe</t>
-  </si>
-  <si>
     <t>Patricia Soares Assad Andrade</t>
   </si>
   <si>
     <t>Vitor Mafra</t>
-  </si>
-  <si>
-    <t>Raquel Fagundes Braga Ferreira</t>
-  </si>
-  <si>
-    <t>Rodrigo Felipe Marques</t>
-  </si>
-  <si>
-    <t>Tatiana Lima Carvalho</t>
   </si>
   <si>
     <t>Walesca Assad Andrade</t>
@@ -3457,7 +3433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}">
-  <dimension ref="A1:L896"/>
+  <dimension ref="A1:L890"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -3503,10 +3479,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -3656,7 +3632,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="C6" s="5">
         <v>16322281</v>
@@ -4170,7 +4146,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="C20" s="5">
         <v>5024046</v>
@@ -4208,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="C21" s="5">
         <v>4890599</v>
@@ -4946,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="C41" s="5">
         <v>4514241</v>
@@ -7054,7 +7030,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="C98" s="5">
         <v>4360431</v>
@@ -7506,7 +7482,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C110" s="5">
         <v>4332544</v>
@@ -10790,7 +10766,7 @@
         <v>10</v>
       </c>
       <c r="B199" s="12" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="C199" s="13">
         <v>4587320</v>
@@ -11912,7 +11888,7 @@
         <v>10</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="C229" s="5">
         <v>4281300</v>
@@ -13122,7 +13098,7 @@
         <v>10</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="C262" s="5">
         <v>4363250</v>
@@ -13420,7 +13396,7 @@
         <v>10</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="C270" s="5">
         <v>4332207</v>
@@ -13982,7 +13958,7 @@
         <v>10</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="C285" s="5">
         <v>4381415</v>
@@ -14130,7 +14106,7 @@
         <v>10</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="C289" s="5">
         <v>4216657</v>
@@ -14350,7 +14326,7 @@
         <v>10</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="C295" s="5">
         <v>5121919</v>
@@ -14388,7 +14364,7 @@
         <v>10</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="C296" s="5">
         <v>5068961</v>
@@ -14654,7 +14630,7 @@
         <v>10</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C303" s="15">
         <v>8857042</v>
@@ -14684,7 +14660,7 @@
         <v>10</v>
       </c>
       <c r="B304" s="16" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="C304" s="22">
         <v>2687737</v>
@@ -14982,7 +14958,7 @@
         <v>10</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C312" s="5">
         <v>16618803</v>
@@ -15048,7 +15024,7 @@
         <v>10</v>
       </c>
       <c r="B314" s="12" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="C314" s="13">
         <v>2401479</v>
@@ -15084,7 +15060,7 @@
         <v>10</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="C315" s="5">
         <v>4405234</v>
@@ -15608,7 +15584,7 @@
         <v>10</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C329" s="5">
         <v>17085325</v>
@@ -16076,19 +16052,19 @@
         <v>10</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C342" s="5">
         <v>9273070</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E342" s="5" t="s">
         <v>129</v>
       </c>
       <c r="F342" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G342" s="6"/>
       <c r="H342" s="6"/>
@@ -16290,7 +16266,7 @@
         <v>10</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="C348" s="5">
         <v>4278212</v>
@@ -16366,7 +16342,7 @@
         <v>10</v>
       </c>
       <c r="B350" s="12" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="C350" s="19">
         <v>4334158</v>
@@ -17040,7 +17016,7 @@
         <v>10</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C368" s="5">
         <v>17180118</v>
@@ -18310,7 +18286,7 @@
         <v>13</v>
       </c>
       <c r="F402" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G402" s="6">
         <v>470888.69</v>
@@ -18348,7 +18324,7 @@
         <v>13</v>
       </c>
       <c r="F403" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G403" s="6"/>
       <c r="H403" s="6"/>
@@ -18666,7 +18642,7 @@
         <v>10</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="C412" s="5">
         <v>4214604</v>
@@ -19226,7 +19202,7 @@
         <v>10</v>
       </c>
       <c r="B427" s="20" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="C427" s="17">
         <v>4395599</v>
@@ -20206,7 +20182,7 @@
         <v>10</v>
       </c>
       <c r="B453" s="12" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="C453" s="31">
         <v>1759765</v>
@@ -20394,7 +20370,7 @@
         <v>10</v>
       </c>
       <c r="B458" s="28" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C458" s="14">
         <v>4371857</v>
@@ -20734,19 +20710,19 @@
         <v>10</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C467" s="5">
         <v>3313722</v>
       </c>
       <c r="D467" s="5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E467" s="5" t="s">
         <v>129</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G467" s="6">
         <v>18361.05</v>
@@ -21254,7 +21230,7 @@
         <v>10</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="C481" s="14">
         <v>4404248</v>
@@ -21704,7 +21680,7 @@
         <v>10</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="C493" s="5">
         <v>4381359</v>
@@ -22114,7 +22090,7 @@
         <v>10</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="C504" s="5">
         <v>4457389</v>
@@ -23570,7 +23546,7 @@
         <v>10</v>
       </c>
       <c r="B543" s="11" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C543" s="5">
         <v>13882576</v>
@@ -23612,7 +23588,7 @@
         <v>20</v>
       </c>
       <c r="F544" s="5" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="G544" s="6">
         <v>0</v>
@@ -23672,7 +23648,7 @@
         <v>10</v>
       </c>
       <c r="B546" s="11" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="C546" s="5">
         <v>4207955</v>
@@ -24334,7 +24310,7 @@
         <v>10</v>
       </c>
       <c r="B564" s="11" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="C564" s="36">
         <v>4202332</v>
@@ -24596,7 +24572,7 @@
         <v>10</v>
       </c>
       <c r="B571" s="11" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="C571" s="5">
         <v>1879977</v>
@@ -24706,7 +24682,7 @@
         <v>10</v>
       </c>
       <c r="B574" s="4" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C574" s="5">
         <v>4425261</v>
@@ -24858,7 +24834,7 @@
         <v>10</v>
       </c>
       <c r="B578" s="20" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="C578" s="17">
         <v>4224011</v>
@@ -25106,7 +25082,7 @@
         <v>10</v>
       </c>
       <c r="B585" s="4" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="C585" s="15">
         <v>5105172</v>
@@ -25366,7 +25342,7 @@
         <v>10</v>
       </c>
       <c r="B592" s="4" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="C592" s="5">
         <v>4806286</v>
@@ -25588,7 +25564,7 @@
         <v>10</v>
       </c>
       <c r="B598" s="4" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C598" s="5">
         <v>17384165</v>
@@ -26548,7 +26524,7 @@
         <v>537</v>
       </c>
       <c r="B624" s="4" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C624" s="5">
         <v>5568034</v>
@@ -27038,7 +27014,7 @@
         <v>537</v>
       </c>
       <c r="B637" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C637" s="5">
         <v>3862487</v>
@@ -27053,16 +27029,16 @@
         <v>138</v>
       </c>
       <c r="G637" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="H637" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="I637" s="7" t="s">
         <v>787</v>
       </c>
-      <c r="H637" s="6" t="s">
+      <c r="J637" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="I637" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="J637" s="8" t="s">
-        <v>790</v>
       </c>
       <c r="K637" s="9">
         <v>87768.348859999998</v>
@@ -28450,7 +28426,7 @@
         <v>537</v>
       </c>
       <c r="B675" s="4" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C675" s="5">
         <v>18801240</v>
@@ -28480,10 +28456,10 @@
         <v>537</v>
       </c>
       <c r="B676" s="4" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C676" s="5" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D676" s="5" t="s">
         <v>12</v>
@@ -29998,7 +29974,7 @@
         <v>616</v>
       </c>
       <c r="B717" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C717" s="5">
         <v>3252345</v>
@@ -30036,7 +30012,7 @@
         <v>616</v>
       </c>
       <c r="B718" s="4" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C718" s="5">
         <v>3252027</v>
@@ -31594,37 +31570,37 @@
         <v>616</v>
       </c>
       <c r="B759" s="4" t="s">
-        <v>796</v>
+        <v>298</v>
       </c>
       <c r="C759" s="14">
-        <v>3252558</v>
+        <v>3252400</v>
       </c>
       <c r="D759" s="14" t="s">
-        <v>797</v>
+        <v>29</v>
       </c>
       <c r="E759" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F759" s="14" t="s">
-        <v>797</v>
+        <v>36</v>
       </c>
       <c r="G759" s="6">
-        <v>130476.49</v>
+        <v>0</v>
       </c>
       <c r="H759" s="44">
-        <v>128991.05</v>
+        <v>0</v>
       </c>
       <c r="I759" s="44">
-        <v>132754.13</v>
+        <v>0</v>
       </c>
       <c r="J759" s="44">
-        <v>135355.10999999999</v>
+        <v>0</v>
       </c>
       <c r="K759" s="44">
-        <v>136562.41</v>
+        <v>0</v>
       </c>
       <c r="L759" s="44">
-        <v>136562.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="760" spans="1:12">
@@ -31632,10 +31608,10 @@
         <v>616</v>
       </c>
       <c r="B760" s="4" t="s">
-        <v>298</v>
+        <v>643</v>
       </c>
       <c r="C760" s="14">
-        <v>3252400</v>
+        <v>3251764</v>
       </c>
       <c r="D760" s="14" t="s">
         <v>29</v>
@@ -31647,22 +31623,22 @@
         <v>36</v>
       </c>
       <c r="G760" s="6">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="H760" s="44">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="I760" s="44">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="J760" s="44">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="K760" s="44">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="L760" s="44">
-        <v>0</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="761" spans="1:12">
@@ -31673,7 +31649,7 @@
         <v>643</v>
       </c>
       <c r="C761" s="14">
-        <v>3251764</v>
+        <v>3251802</v>
       </c>
       <c r="D761" s="14" t="s">
         <v>29</v>
@@ -31685,22 +31661,22 @@
         <v>36</v>
       </c>
       <c r="G761" s="6">
-        <v>3.19</v>
+        <v>1.74</v>
       </c>
       <c r="H761" s="44">
-        <v>3.19</v>
+        <v>1.74</v>
       </c>
       <c r="I761" s="44">
-        <v>3.19</v>
+        <v>1.74</v>
       </c>
       <c r="J761" s="44">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="K761" s="44">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="L761" s="44">
-        <v>3.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="762" spans="1:12">
@@ -31708,28 +31684,28 @@
         <v>616</v>
       </c>
       <c r="B762" s="4" t="s">
-        <v>643</v>
+        <v>773</v>
       </c>
       <c r="C762" s="14">
-        <v>3251802</v>
+        <v>3252485</v>
       </c>
       <c r="D762" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E762" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F762" s="14" t="s">
-        <v>36</v>
+        <v>794</v>
       </c>
       <c r="G762" s="6">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="H762" s="44">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="I762" s="44">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="J762" s="44">
         <v>0</v>
@@ -31746,10 +31722,10 @@
         <v>616</v>
       </c>
       <c r="B763" s="4" t="s">
-        <v>774</v>
+        <v>644</v>
       </c>
       <c r="C763" s="14">
-        <v>3252485</v>
+        <v>3252205</v>
       </c>
       <c r="D763" s="14" t="s">
         <v>19</v>
@@ -31758,25 +31734,25 @@
         <v>13</v>
       </c>
       <c r="F763" s="14" t="s">
-        <v>798</v>
+        <v>619</v>
       </c>
       <c r="G763" s="6">
-        <v>0</v>
+        <v>840129.58</v>
       </c>
       <c r="H763" s="44">
-        <v>0</v>
+        <v>858885.56</v>
       </c>
       <c r="I763" s="44">
-        <v>0</v>
+        <v>866279.31</v>
       </c>
       <c r="J763" s="44">
-        <v>0</v>
+        <v>874389.87</v>
       </c>
       <c r="K763" s="44">
-        <v>0</v>
+        <v>881909.66</v>
       </c>
       <c r="L763" s="44">
-        <v>0</v>
+        <v>881909.66</v>
       </c>
     </row>
     <row r="764" spans="1:12">
@@ -31784,10 +31760,10 @@
         <v>616</v>
       </c>
       <c r="B764" s="4" t="s">
-        <v>644</v>
+        <v>581</v>
       </c>
       <c r="C764" s="14">
-        <v>3252205</v>
+        <v>3252060</v>
       </c>
       <c r="D764" s="14" t="s">
         <v>19</v>
@@ -31796,25 +31772,25 @@
         <v>13</v>
       </c>
       <c r="F764" s="14" t="s">
-        <v>619</v>
+        <v>34</v>
       </c>
       <c r="G764" s="6">
-        <v>840129.58</v>
+        <v>233.44</v>
       </c>
       <c r="H764" s="44">
-        <v>858885.56</v>
+        <v>335.35</v>
       </c>
       <c r="I764" s="44">
-        <v>866279.31</v>
+        <v>335.5</v>
       </c>
       <c r="J764" s="44">
-        <v>874389.87</v>
+        <v>335.67</v>
       </c>
       <c r="K764" s="44">
-        <v>881909.66</v>
+        <v>335.82</v>
       </c>
       <c r="L764" s="44">
-        <v>881909.66</v>
+        <v>335.82</v>
       </c>
     </row>
     <row r="765" spans="1:12">
@@ -31825,7 +31801,7 @@
         <v>581</v>
       </c>
       <c r="C765" s="14">
-        <v>3252060</v>
+        <v>3252078</v>
       </c>
       <c r="D765" s="14" t="s">
         <v>19</v>
@@ -31837,22 +31813,22 @@
         <v>34</v>
       </c>
       <c r="G765" s="6">
-        <v>233.44</v>
+        <v>42748.97</v>
       </c>
       <c r="H765" s="44">
-        <v>335.35</v>
+        <v>474.67</v>
       </c>
       <c r="I765" s="44">
-        <v>335.5</v>
+        <v>474.41</v>
       </c>
       <c r="J765" s="44">
-        <v>335.67</v>
+        <v>474.59</v>
       </c>
       <c r="K765" s="44">
-        <v>335.82</v>
+        <v>474.98</v>
       </c>
       <c r="L765" s="44">
-        <v>335.82</v>
+        <v>474.98</v>
       </c>
     </row>
     <row r="766" spans="1:12">
@@ -31860,10 +31836,10 @@
         <v>616</v>
       </c>
       <c r="B766" s="4" t="s">
-        <v>581</v>
+        <v>645</v>
       </c>
       <c r="C766" s="14">
-        <v>3252078</v>
+        <v>3252141</v>
       </c>
       <c r="D766" s="14" t="s">
         <v>19</v>
@@ -31875,22 +31851,22 @@
         <v>34</v>
       </c>
       <c r="G766" s="6">
-        <v>42748.97</v>
+        <v>0</v>
       </c>
       <c r="H766" s="44">
-        <v>474.67</v>
+        <v>0</v>
       </c>
       <c r="I766" s="44">
-        <v>474.41</v>
+        <v>0</v>
       </c>
       <c r="J766" s="44">
-        <v>474.59</v>
+        <v>0</v>
       </c>
       <c r="K766" s="44">
-        <v>474.98</v>
+        <v>0</v>
       </c>
       <c r="L766" s="44">
-        <v>474.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="767" spans="1:12">
@@ -31898,10 +31874,10 @@
         <v>616</v>
       </c>
       <c r="B767" s="4" t="s">
-        <v>645</v>
+        <v>774</v>
       </c>
       <c r="C767" s="14">
-        <v>3252141</v>
+        <v>3252299</v>
       </c>
       <c r="D767" s="14" t="s">
         <v>19</v>
@@ -31913,22 +31889,22 @@
         <v>34</v>
       </c>
       <c r="G767" s="6">
-        <v>0</v>
+        <v>193143.83</v>
       </c>
       <c r="H767" s="44">
-        <v>0</v>
+        <v>191588.24</v>
       </c>
       <c r="I767" s="44">
-        <v>0</v>
+        <v>195839.45</v>
       </c>
       <c r="J767" s="44">
-        <v>0</v>
+        <v>199881.1</v>
       </c>
       <c r="K767" s="44">
-        <v>0</v>
+        <v>203036.81</v>
       </c>
       <c r="L767" s="44">
-        <v>0</v>
+        <v>203036.81</v>
       </c>
     </row>
     <row r="768" spans="1:12">
@@ -31936,37 +31912,37 @@
         <v>616</v>
       </c>
       <c r="B768" s="4" t="s">
-        <v>775</v>
+        <v>358</v>
       </c>
       <c r="C768" s="14">
-        <v>3252299</v>
+        <v>3252370</v>
       </c>
       <c r="D768" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E768" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F768" s="14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G768" s="6">
-        <v>193143.83</v>
+        <v>37069.68</v>
       </c>
       <c r="H768" s="44">
-        <v>191588.24</v>
+        <v>37484.910000000003</v>
       </c>
       <c r="I768" s="44">
-        <v>195839.45</v>
+        <v>37862.21</v>
       </c>
       <c r="J768" s="44">
-        <v>199881.1</v>
+        <v>38264.85</v>
       </c>
       <c r="K768" s="44">
-        <v>203036.81</v>
+        <v>38144.800000000003</v>
       </c>
       <c r="L768" s="44">
-        <v>203036.81</v>
+        <v>38144.800000000003</v>
       </c>
     </row>
     <row r="769" spans="1:12">
@@ -31974,37 +31950,37 @@
         <v>616</v>
       </c>
       <c r="B769" s="4" t="s">
-        <v>358</v>
+        <v>646</v>
       </c>
       <c r="C769" s="14">
-        <v>3252370</v>
+        <v>3252264</v>
       </c>
       <c r="D769" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E769" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F769" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G769" s="6">
-        <v>37069.68</v>
+        <v>118598.5</v>
       </c>
       <c r="H769" s="44">
-        <v>37484.910000000003</v>
+        <v>119890.71</v>
       </c>
       <c r="I769" s="44">
-        <v>37862.21</v>
+        <v>120764.74</v>
       </c>
       <c r="J769" s="44">
-        <v>38264.85</v>
+        <v>121942.57</v>
       </c>
       <c r="K769" s="44">
-        <v>38144.800000000003</v>
+        <v>123291.05</v>
       </c>
       <c r="L769" s="44">
-        <v>38144.800000000003</v>
+        <v>123291.05</v>
       </c>
     </row>
     <row r="770" spans="1:12">
@@ -32012,37 +31988,37 @@
         <v>616</v>
       </c>
       <c r="B770" s="4" t="s">
-        <v>646</v>
+        <v>370</v>
       </c>
       <c r="C770" s="14">
-        <v>3252264</v>
+        <v>3252353</v>
       </c>
       <c r="D770" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E770" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F770" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G770" s="6">
-        <v>118598.5</v>
+        <v>0</v>
       </c>
       <c r="H770" s="44">
-        <v>119890.71</v>
+        <v>0</v>
       </c>
       <c r="I770" s="44">
-        <v>120764.74</v>
+        <v>0</v>
       </c>
       <c r="J770" s="44">
-        <v>121942.57</v>
+        <v>0</v>
       </c>
       <c r="K770" s="44">
-        <v>123291.05</v>
+        <v>0</v>
       </c>
       <c r="L770" s="44">
-        <v>123291.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="771" spans="1:12">
@@ -32050,37 +32026,37 @@
         <v>616</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>370</v>
+        <v>647</v>
       </c>
       <c r="C771" s="14">
-        <v>3252353</v>
+        <v>3252302</v>
       </c>
       <c r="D771" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E771" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F771" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G771" s="6">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="H771" s="44">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="I771" s="44">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="J771" s="44">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="K771" s="44">
-        <v>0</v>
+        <v>15.79</v>
       </c>
       <c r="L771" s="44">
-        <v>0</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="772" spans="1:12">
@@ -32088,37 +32064,37 @@
         <v>616</v>
       </c>
       <c r="B772" s="4" t="s">
-        <v>647</v>
+        <v>382</v>
       </c>
       <c r="C772" s="14">
-        <v>3252302</v>
+        <v>3251845</v>
       </c>
       <c r="D772" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E772" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F772" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G772" s="6">
-        <v>15.79</v>
+        <v>0</v>
       </c>
       <c r="H772" s="44">
-        <v>15.79</v>
+        <v>0</v>
       </c>
       <c r="I772" s="44">
-        <v>15.79</v>
+        <v>0</v>
       </c>
       <c r="J772" s="44">
-        <v>15.79</v>
+        <v>0</v>
       </c>
       <c r="K772" s="44">
-        <v>15.79</v>
+        <v>0</v>
       </c>
       <c r="L772" s="44">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="773" spans="1:12">
@@ -32126,37 +32102,37 @@
         <v>616</v>
       </c>
       <c r="B773" s="4" t="s">
-        <v>382</v>
+        <v>648</v>
       </c>
       <c r="C773" s="14">
-        <v>3251845</v>
+        <v>3252132</v>
       </c>
       <c r="D773" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E773" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F773" s="14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G773" s="6">
-        <v>0</v>
+        <v>393098.91</v>
       </c>
       <c r="H773" s="44">
-        <v>0</v>
+        <v>397600.68</v>
       </c>
       <c r="I773" s="44">
-        <v>0</v>
+        <v>397116.33</v>
       </c>
       <c r="J773" s="44">
-        <v>0</v>
+        <v>401087.31</v>
       </c>
       <c r="K773" s="44">
-        <v>0</v>
+        <v>401596.52</v>
       </c>
       <c r="L773" s="44">
-        <v>0</v>
+        <v>401596.52</v>
       </c>
     </row>
     <row r="774" spans="1:12">
@@ -32164,37 +32140,37 @@
         <v>616</v>
       </c>
       <c r="B774" s="4" t="s">
-        <v>800</v>
+        <v>409</v>
       </c>
       <c r="C774" s="14">
-        <v>3252183</v>
+        <v>3251977</v>
       </c>
       <c r="D774" s="14" t="s">
-        <v>797</v>
+        <v>29</v>
       </c>
       <c r="E774" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F774" s="14" t="s">
-        <v>797</v>
+        <v>36</v>
       </c>
       <c r="G774" s="6">
-        <v>247032.89</v>
+        <v>282.82</v>
       </c>
       <c r="H774" s="44">
-        <v>241459.01</v>
+        <v>282.82</v>
       </c>
       <c r="I774" s="44">
-        <v>235548.42</v>
+        <v>282.82</v>
       </c>
       <c r="J774" s="44">
-        <v>258992.33</v>
+        <v>282.82</v>
       </c>
       <c r="K774" s="44">
-        <v>262997.34000000003</v>
+        <v>282.82</v>
       </c>
       <c r="L774" s="44">
-        <v>262997.34000000003</v>
+        <v>282.82</v>
       </c>
     </row>
     <row r="775" spans="1:12">
@@ -32202,37 +32178,37 @@
         <v>616</v>
       </c>
       <c r="B775" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C775" s="14">
-        <v>3252132</v>
+        <v>3252035</v>
       </c>
       <c r="D775" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E775" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F775" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G775" s="6">
-        <v>393098.91</v>
+        <v>0.54</v>
       </c>
       <c r="H775" s="44">
-        <v>397600.68</v>
+        <v>0.54</v>
       </c>
       <c r="I775" s="44">
-        <v>397116.33</v>
+        <v>0.54</v>
       </c>
       <c r="J775" s="44">
-        <v>401087.31</v>
+        <v>0.54</v>
       </c>
       <c r="K775" s="44">
-        <v>401596.52</v>
+        <v>0.54</v>
       </c>
       <c r="L775" s="44">
-        <v>401596.52</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="776" spans="1:12">
@@ -32240,37 +32216,37 @@
         <v>616</v>
       </c>
       <c r="B776" s="4" t="s">
-        <v>409</v>
+        <v>796</v>
       </c>
       <c r="C776" s="14">
-        <v>3251977</v>
+        <v>3252515</v>
       </c>
       <c r="D776" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E776" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F776" s="14" t="s">
-        <v>36</v>
+        <v>797</v>
       </c>
       <c r="G776" s="6">
-        <v>282.82</v>
+        <v>0</v>
       </c>
       <c r="H776" s="44">
-        <v>282.82</v>
+        <v>5.79</v>
       </c>
       <c r="I776" s="44">
-        <v>282.82</v>
+        <v>5.79</v>
       </c>
       <c r="J776" s="44">
-        <v>282.82</v>
+        <v>5.79</v>
       </c>
       <c r="K776" s="44">
-        <v>282.82</v>
+        <v>5.79</v>
       </c>
       <c r="L776" s="44">
-        <v>282.82</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="777" spans="1:12">
@@ -32278,10 +32254,10 @@
         <v>616</v>
       </c>
       <c r="B777" s="4" t="s">
-        <v>649</v>
+        <v>427</v>
       </c>
       <c r="C777" s="14">
-        <v>3252035</v>
+        <v>3251861</v>
       </c>
       <c r="D777" s="14" t="s">
         <v>29</v>
@@ -32293,22 +32269,22 @@
         <v>36</v>
       </c>
       <c r="G777" s="6">
-        <v>0.54</v>
+        <v>31.04</v>
       </c>
       <c r="H777" s="44">
-        <v>0.54</v>
+        <v>31.04</v>
       </c>
       <c r="I777" s="44">
-        <v>0.54</v>
+        <v>31.04</v>
       </c>
       <c r="J777" s="44">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="K777" s="44">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L777" s="44">
-        <v>0.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="778" spans="1:12">
@@ -32316,37 +32292,37 @@
         <v>616</v>
       </c>
       <c r="B778" s="4" t="s">
-        <v>801</v>
+        <v>650</v>
       </c>
       <c r="C778" s="14">
-        <v>3252515</v>
+        <v>3251616</v>
       </c>
       <c r="D778" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E778" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F778" s="14" t="s">
-        <v>802</v>
+        <v>120</v>
       </c>
       <c r="G778" s="6">
         <v>0</v>
       </c>
       <c r="H778" s="44">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="I778" s="44">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="J778" s="44">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="K778" s="44">
-        <v>5.79</v>
+        <v>0</v>
       </c>
       <c r="L778" s="44">
-        <v>5.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="779" spans="1:12">
@@ -32354,10 +32330,10 @@
         <v>616</v>
       </c>
       <c r="B779" s="4" t="s">
-        <v>427</v>
+        <v>650</v>
       </c>
       <c r="C779" s="14">
-        <v>3251861</v>
+        <v>3251632</v>
       </c>
       <c r="D779" s="14" t="s">
         <v>29</v>
@@ -32366,16 +32342,16 @@
         <v>30</v>
       </c>
       <c r="F779" s="14" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="G779" s="6">
-        <v>31.04</v>
+        <v>0</v>
       </c>
       <c r="H779" s="44">
-        <v>31.04</v>
+        <v>0</v>
       </c>
       <c r="I779" s="44">
-        <v>31.04</v>
+        <v>0</v>
       </c>
       <c r="J779" s="44">
         <v>0</v>
@@ -32392,37 +32368,37 @@
         <v>616</v>
       </c>
       <c r="B780" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C780" s="14">
-        <v>3251616</v>
+        <v>3252337</v>
       </c>
       <c r="D780" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E780" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F780" s="14" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="G780" s="6">
-        <v>0</v>
+        <v>1190084.67</v>
       </c>
       <c r="H780" s="44">
-        <v>0</v>
+        <v>1197715.79</v>
       </c>
       <c r="I780" s="44">
-        <v>0</v>
+        <v>1196949.43</v>
       </c>
       <c r="J780" s="44">
-        <v>0</v>
+        <v>1178107.1599999999</v>
       </c>
       <c r="K780" s="44">
-        <v>0</v>
+        <v>1186978.0900000001</v>
       </c>
       <c r="L780" s="44">
-        <v>0</v>
+        <v>1186978.0900000001</v>
       </c>
     </row>
     <row r="781" spans="1:12">
@@ -32430,37 +32406,37 @@
         <v>616</v>
       </c>
       <c r="B781" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C781" s="14">
-        <v>3251632</v>
+        <v>3252671</v>
       </c>
       <c r="D781" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E781" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F781" s="14" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="G781" s="6">
-        <v>0</v>
+        <v>117928.39</v>
       </c>
       <c r="H781" s="44">
-        <v>0</v>
+        <v>119270.66</v>
       </c>
       <c r="I781" s="44">
-        <v>0</v>
+        <v>120470.84</v>
       </c>
       <c r="J781" s="44">
-        <v>0</v>
+        <v>121761.47</v>
       </c>
       <c r="K781" s="44">
-        <v>0</v>
+        <v>123123.88</v>
       </c>
       <c r="L781" s="44">
-        <v>0</v>
+        <v>123123.88</v>
       </c>
     </row>
     <row r="782" spans="1:12">
@@ -32468,37 +32444,37 @@
         <v>616</v>
       </c>
       <c r="B782" s="4" t="s">
-        <v>651</v>
+        <v>434</v>
       </c>
       <c r="C782" s="14">
-        <v>3252337</v>
+        <v>3258475</v>
       </c>
       <c r="D782" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E782" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F782" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G782" s="6">
-        <v>1190084.67</v>
+        <v>417.66</v>
       </c>
       <c r="H782" s="44">
-        <v>1197715.79</v>
+        <v>417.66</v>
       </c>
       <c r="I782" s="44">
-        <v>1196949.43</v>
+        <v>417.66</v>
       </c>
       <c r="J782" s="44">
-        <v>1178107.1599999999</v>
+        <v>417.66</v>
       </c>
       <c r="K782" s="44">
-        <v>1186978.0900000001</v>
+        <v>417.66</v>
       </c>
       <c r="L782" s="44">
-        <v>1186978.0900000001</v>
+        <v>417.66</v>
       </c>
     </row>
     <row r="783" spans="1:12">
@@ -32506,10 +32482,10 @@
         <v>616</v>
       </c>
       <c r="B783" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C783" s="14">
-        <v>3252671</v>
+        <v>3252426</v>
       </c>
       <c r="D783" s="14" t="s">
         <v>19</v>
@@ -32518,25 +32494,25 @@
         <v>13</v>
       </c>
       <c r="F783" s="14" t="s">
-        <v>34</v>
+        <v>619</v>
       </c>
       <c r="G783" s="6">
-        <v>117928.39</v>
+        <v>1983.22</v>
       </c>
       <c r="H783" s="44">
-        <v>119270.66</v>
+        <v>1983.22</v>
       </c>
       <c r="I783" s="44">
-        <v>120470.84</v>
+        <v>1983.22</v>
       </c>
       <c r="J783" s="44">
-        <v>121761.47</v>
+        <v>1983.22</v>
       </c>
       <c r="K783" s="44">
-        <v>123123.88</v>
+        <v>1983.22</v>
       </c>
       <c r="L783" s="44">
-        <v>123123.88</v>
+        <v>1983.22</v>
       </c>
     </row>
     <row r="784" spans="1:12">
@@ -32544,10 +32520,10 @@
         <v>616</v>
       </c>
       <c r="B784" s="4" t="s">
-        <v>780</v>
+        <v>653</v>
       </c>
       <c r="C784" s="14">
-        <v>3252213</v>
+        <v>3252442</v>
       </c>
       <c r="D784" s="14" t="s">
         <v>19</v>
@@ -32556,25 +32532,25 @@
         <v>13</v>
       </c>
       <c r="F784" s="14" t="s">
-        <v>767</v>
+        <v>619</v>
       </c>
       <c r="G784" s="6">
-        <v>0.51</v>
+        <v>1.6</v>
       </c>
       <c r="H784" s="44">
-        <v>0.51</v>
+        <v>1.6</v>
       </c>
       <c r="I784" s="44">
-        <v>0.51</v>
+        <v>1.6</v>
       </c>
       <c r="J784" s="44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="K784" s="44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L784" s="44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="785" spans="1:12">
@@ -32582,10 +32558,10 @@
         <v>616</v>
       </c>
       <c r="B785" s="4" t="s">
-        <v>434</v>
+        <v>654</v>
       </c>
       <c r="C785" s="14">
-        <v>3258475</v>
+        <v>3252256</v>
       </c>
       <c r="D785" s="14" t="s">
         <v>29</v>
@@ -32594,25 +32570,25 @@
         <v>30</v>
       </c>
       <c r="F785" s="14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G785" s="6">
-        <v>417.66</v>
+        <v>1.03</v>
       </c>
       <c r="H785" s="44">
-        <v>417.66</v>
+        <v>1.03</v>
       </c>
       <c r="I785" s="44">
-        <v>417.66</v>
+        <v>1.03</v>
       </c>
       <c r="J785" s="44">
-        <v>417.66</v>
+        <v>1.03</v>
       </c>
       <c r="K785" s="44">
-        <v>417.66</v>
+        <v>1.03</v>
       </c>
       <c r="L785" s="44">
-        <v>417.66</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="786" spans="1:12">
@@ -32620,10 +32596,10 @@
         <v>616</v>
       </c>
       <c r="B786" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C786" s="14">
-        <v>3252426</v>
+        <v>3252086</v>
       </c>
       <c r="D786" s="14" t="s">
         <v>19</v>
@@ -32632,25 +32608,25 @@
         <v>13</v>
       </c>
       <c r="F786" s="14" t="s">
-        <v>619</v>
+        <v>34</v>
       </c>
       <c r="G786" s="6">
-        <v>1983.22</v>
+        <v>151.18</v>
       </c>
       <c r="H786" s="44">
-        <v>1983.22</v>
+        <v>151.18</v>
       </c>
       <c r="I786" s="44">
-        <v>1983.22</v>
+        <v>151.18</v>
       </c>
       <c r="J786" s="44">
-        <v>1983.22</v>
+        <v>0</v>
       </c>
       <c r="K786" s="44">
-        <v>1983.22</v>
+        <v>0</v>
       </c>
       <c r="L786" s="44">
-        <v>1983.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="787" spans="1:12">
@@ -32658,37 +32634,37 @@
         <v>616</v>
       </c>
       <c r="B787" s="4" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C787" s="14">
-        <v>3252442</v>
+        <v>3251934</v>
       </c>
       <c r="D787" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E787" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F787" s="14" t="s">
-        <v>619</v>
+        <v>31</v>
       </c>
       <c r="G787" s="6">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H787" s="44">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I787" s="44">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J787" s="44">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="K787" s="44">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L787" s="44">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="788" spans="1:12">
@@ -32696,10 +32672,10 @@
         <v>616</v>
       </c>
       <c r="B788" s="4" t="s">
-        <v>654</v>
+        <v>464</v>
       </c>
       <c r="C788" s="14">
-        <v>3252256</v>
+        <v>3251853</v>
       </c>
       <c r="D788" s="14" t="s">
         <v>29</v>
@@ -32708,25 +32684,25 @@
         <v>30</v>
       </c>
       <c r="F788" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G788" s="6">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="H788" s="44">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="I788" s="44">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="J788" s="44">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="K788" s="44">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="L788" s="44">
-        <v>1.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="789" spans="1:12">
@@ -32734,28 +32710,28 @@
         <v>616</v>
       </c>
       <c r="B789" s="4" t="s">
-        <v>655</v>
+        <v>464</v>
       </c>
       <c r="C789" s="14">
-        <v>3252086</v>
+        <v>3251870</v>
       </c>
       <c r="D789" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E789" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F789" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G789" s="6">
-        <v>151.18</v>
+        <v>0</v>
       </c>
       <c r="H789" s="44">
-        <v>151.18</v>
+        <v>0</v>
       </c>
       <c r="I789" s="44">
-        <v>151.18</v>
+        <v>0</v>
       </c>
       <c r="J789" s="44">
         <v>0</v>
@@ -32772,37 +32748,37 @@
         <v>616</v>
       </c>
       <c r="B790" s="4" t="s">
-        <v>803</v>
+        <v>464</v>
       </c>
       <c r="C790" s="14">
-        <v>3252159</v>
+        <v>3251888</v>
       </c>
       <c r="D790" s="14" t="s">
-        <v>797</v>
+        <v>29</v>
       </c>
       <c r="E790" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F790" s="14" t="s">
-        <v>797</v>
+        <v>36</v>
       </c>
       <c r="G790" s="6">
-        <v>96038.28</v>
+        <v>0</v>
       </c>
       <c r="H790" s="44">
-        <v>21600.47</v>
+        <v>0</v>
       </c>
       <c r="I790" s="44">
-        <v>21824.44</v>
+        <v>0</v>
       </c>
       <c r="J790" s="44">
-        <v>22055.49</v>
+        <v>0</v>
       </c>
       <c r="K790" s="44">
-        <v>22300.92</v>
+        <v>0</v>
       </c>
       <c r="L790" s="44">
-        <v>22300.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="791" spans="1:12">
@@ -32810,10 +32786,10 @@
         <v>616</v>
       </c>
       <c r="B791" s="4" t="s">
-        <v>656</v>
+        <v>471</v>
       </c>
       <c r="C791" s="14">
-        <v>3251934</v>
+        <v>3251926</v>
       </c>
       <c r="D791" s="14" t="s">
         <v>29</v>
@@ -32848,10 +32824,10 @@
         <v>616</v>
       </c>
       <c r="B792" s="4" t="s">
-        <v>464</v>
+        <v>657</v>
       </c>
       <c r="C792" s="14">
-        <v>3251853</v>
+        <v>3251942</v>
       </c>
       <c r="D792" s="14" t="s">
         <v>29</v>
@@ -32860,25 +32836,25 @@
         <v>30</v>
       </c>
       <c r="F792" s="14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G792" s="6">
-        <v>0</v>
+        <v>19.66</v>
       </c>
       <c r="H792" s="44">
-        <v>0</v>
+        <v>19.66</v>
       </c>
       <c r="I792" s="44">
-        <v>0</v>
+        <v>19.66</v>
       </c>
       <c r="J792" s="44">
-        <v>0</v>
+        <v>19.66</v>
       </c>
       <c r="K792" s="44">
-        <v>0</v>
+        <v>19.66</v>
       </c>
       <c r="L792" s="44">
-        <v>0</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="793" spans="1:12">
@@ -32886,10 +32862,10 @@
         <v>616</v>
       </c>
       <c r="B793" s="4" t="s">
-        <v>464</v>
+        <v>518</v>
       </c>
       <c r="C793" s="14">
-        <v>3251870</v>
+        <v>3251659</v>
       </c>
       <c r="D793" s="14" t="s">
         <v>29</v>
@@ -32898,7 +32874,7 @@
         <v>30</v>
       </c>
       <c r="F793" s="14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G793" s="6">
         <v>0</v>
@@ -32924,37 +32900,37 @@
         <v>616</v>
       </c>
       <c r="B794" s="4" t="s">
-        <v>464</v>
+        <v>798</v>
       </c>
       <c r="C794" s="14">
-        <v>3251888</v>
+        <v>3252124</v>
       </c>
       <c r="D794" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E794" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F794" s="14" t="s">
-        <v>36</v>
+        <v>797</v>
       </c>
       <c r="G794" s="6">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="H794" s="44">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I794" s="44">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="J794" s="44">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="K794" s="44">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="L794" s="44">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="795" spans="1:12">
@@ -32962,37 +32938,37 @@
         <v>616</v>
       </c>
       <c r="B795" s="4" t="s">
-        <v>471</v>
+        <v>799</v>
       </c>
       <c r="C795" s="14">
-        <v>3251926</v>
+        <v>3252221</v>
       </c>
       <c r="D795" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E795" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F795" s="14" t="s">
-        <v>31</v>
+        <v>797</v>
       </c>
       <c r="G795" s="6">
         <v>0</v>
       </c>
       <c r="H795" s="44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I795" s="44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="J795" s="44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="K795" s="44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="L795" s="44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="796" spans="1:12">
@@ -33000,10 +32976,10 @@
         <v>616</v>
       </c>
       <c r="B796" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C796" s="14">
-        <v>3251942</v>
+        <v>3251772</v>
       </c>
       <c r="D796" s="14" t="s">
         <v>29</v>
@@ -33015,22 +32991,22 @@
         <v>31</v>
       </c>
       <c r="G796" s="6">
-        <v>19.66</v>
+        <v>1063.24</v>
       </c>
       <c r="H796" s="44">
-        <v>19.66</v>
+        <v>1063.24</v>
       </c>
       <c r="I796" s="44">
-        <v>19.66</v>
+        <v>1063.24</v>
       </c>
       <c r="J796" s="44">
-        <v>19.66</v>
+        <v>1063.24</v>
       </c>
       <c r="K796" s="44">
-        <v>19.66</v>
+        <v>1063.24</v>
       </c>
       <c r="L796" s="44">
-        <v>19.66</v>
+        <v>1063.24</v>
       </c>
     </row>
     <row r="797" spans="1:12">
@@ -33038,95 +33014,95 @@
         <v>616</v>
       </c>
       <c r="B797" s="4" t="s">
-        <v>804</v>
+        <v>534</v>
       </c>
       <c r="C797" s="14">
-        <v>3252175</v>
+        <v>3251896</v>
       </c>
       <c r="D797" s="14" t="s">
-        <v>797</v>
+        <v>29</v>
       </c>
       <c r="E797" s="14" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F797" s="14" t="s">
-        <v>797</v>
+        <v>31</v>
       </c>
       <c r="G797" s="6">
-        <v>87075.27</v>
+        <v>0.02</v>
       </c>
       <c r="H797" s="44">
-        <v>85724.85</v>
+        <v>0.02</v>
       </c>
       <c r="I797" s="44">
-        <v>83636.17</v>
+        <v>0.02</v>
       </c>
       <c r="J797" s="44">
-        <v>91532.88</v>
+        <v>0.02</v>
       </c>
       <c r="K797" s="44">
-        <v>93243.91</v>
+        <v>0.02</v>
       </c>
       <c r="L797" s="44">
-        <v>93243.91</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="798" spans="1:12">
       <c r="A798" s="16" t="s">
-        <v>616</v>
+        <v>659</v>
       </c>
       <c r="B798" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="C798" s="14">
-        <v>3252451</v>
+        <v>660</v>
+      </c>
+      <c r="C798" s="14" t="s">
+        <v>800</v>
       </c>
       <c r="D798" s="14" t="s">
-        <v>797</v>
+        <v>19</v>
       </c>
       <c r="E798" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F798" s="14" t="s">
-        <v>797</v>
+        <v>39</v>
       </c>
       <c r="G798" s="6">
-        <v>46397.22</v>
+        <v>0</v>
       </c>
       <c r="H798" s="44">
-        <v>46938.07</v>
+        <v>0</v>
       </c>
       <c r="I798" s="44">
-        <v>47438.26</v>
+        <v>0</v>
       </c>
       <c r="J798" s="44">
-        <v>47959.21</v>
+        <v>0</v>
       </c>
       <c r="K798" s="44">
-        <v>48508.38</v>
+        <v>0</v>
       </c>
       <c r="L798" s="44">
-        <v>48508.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="799" spans="1:12">
       <c r="A799" s="16" t="s">
-        <v>616</v>
+        <v>659</v>
       </c>
       <c r="B799" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="C799" s="14">
-        <v>3251659</v>
+        <v>50</v>
+      </c>
+      <c r="C799" s="14" t="s">
+        <v>801</v>
       </c>
       <c r="D799" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E799" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F799" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G799" s="6">
         <v>0</v>
@@ -33149,13 +33125,13 @@
     </row>
     <row r="800" spans="1:12">
       <c r="A800" s="16" t="s">
-        <v>616</v>
+        <v>659</v>
       </c>
       <c r="B800" s="4" t="s">
-        <v>806</v>
-      </c>
-      <c r="C800" s="14">
-        <v>3252124</v>
+        <v>802</v>
+      </c>
+      <c r="C800" s="14" t="s">
+        <v>803</v>
       </c>
       <c r="D800" s="14" t="s">
         <v>19</v>
@@ -33164,36 +33140,36 @@
         <v>13</v>
       </c>
       <c r="F800" s="14" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="G800" s="6">
-        <v>0.16</v>
+        <v>143715.87</v>
       </c>
       <c r="H800" s="44">
-        <v>0.16</v>
-      </c>
-      <c r="I800" s="44">
-        <v>0.16</v>
+        <v>145376.06</v>
+      </c>
+      <c r="I800" s="44" t="s">
+        <v>804</v>
       </c>
       <c r="J800" s="44">
-        <v>0.16</v>
+        <v>148082.32999999999</v>
       </c>
       <c r="K800" s="44">
-        <v>0.16</v>
+        <v>149774.26</v>
       </c>
       <c r="L800" s="44">
-        <v>0.16</v>
+        <v>149774.26</v>
       </c>
     </row>
     <row r="801" spans="1:12">
       <c r="A801" s="16" t="s">
-        <v>616</v>
+        <v>659</v>
       </c>
       <c r="B801" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="C801" s="14">
-        <v>3252221</v>
+        <v>733</v>
+      </c>
+      <c r="C801" s="14" t="s">
+        <v>805</v>
       </c>
       <c r="D801" s="14" t="s">
         <v>19</v>
@@ -33202,101 +33178,101 @@
         <v>13</v>
       </c>
       <c r="F801" s="14" t="s">
-        <v>802</v>
+        <v>734</v>
       </c>
       <c r="G801" s="6">
         <v>0</v>
       </c>
       <c r="H801" s="44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I801" s="44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="J801" s="44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="K801" s="44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="L801" s="44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="802" spans="1:12">
       <c r="A802" s="16" t="s">
-        <v>616</v>
+        <v>659</v>
       </c>
       <c r="B802" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="C802" s="14">
-        <v>3251772</v>
+        <v>735</v>
+      </c>
+      <c r="C802" s="14" t="s">
+        <v>806</v>
       </c>
       <c r="D802" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E802" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F802" s="14" t="s">
-        <v>31</v>
+        <v>726</v>
       </c>
       <c r="G802" s="6">
-        <v>1063.24</v>
+        <v>0</v>
       </c>
       <c r="H802" s="44">
-        <v>1063.24</v>
+        <v>0</v>
       </c>
       <c r="I802" s="44">
-        <v>1063.24</v>
+        <v>0</v>
       </c>
       <c r="J802" s="44">
-        <v>1063.24</v>
+        <v>0</v>
       </c>
       <c r="K802" s="44">
-        <v>1063.24</v>
+        <v>0</v>
       </c>
       <c r="L802" s="44">
-        <v>1063.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="803" spans="1:12">
       <c r="A803" s="16" t="s">
-        <v>616</v>
+        <v>659</v>
       </c>
       <c r="B803" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="C803" s="14">
-        <v>3251896</v>
+        <v>91</v>
+      </c>
+      <c r="C803" s="14" t="s">
+        <v>807</v>
       </c>
       <c r="D803" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E803" s="14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F803" s="14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G803" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H803" s="44">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I803" s="44">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J803" s="44">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="K803" s="44">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L803" s="44">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="804" spans="1:12">
@@ -33304,7 +33280,7 @@
         <v>659</v>
       </c>
       <c r="B804" s="4" t="s">
-        <v>660</v>
+        <v>97</v>
       </c>
       <c r="C804" s="14" t="s">
         <v>808</v>
@@ -33316,7 +33292,7 @@
         <v>13</v>
       </c>
       <c r="F804" s="14" t="s">
-        <v>39</v>
+        <v>736</v>
       </c>
       <c r="G804" s="6">
         <v>0</v>
@@ -33342,7 +33318,7 @@
         <v>659</v>
       </c>
       <c r="B805" s="4" t="s">
-        <v>50</v>
+        <v>737</v>
       </c>
       <c r="C805" s="14" t="s">
         <v>809</v>
@@ -33354,7 +33330,7 @@
         <v>13</v>
       </c>
       <c r="F805" s="14" t="s">
-        <v>34</v>
+        <v>736</v>
       </c>
       <c r="G805" s="6">
         <v>0</v>
@@ -33380,11 +33356,11 @@
         <v>659</v>
       </c>
       <c r="B806" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C806" s="14" t="s">
         <v>810</v>
       </c>
-      <c r="C806" s="14" t="s">
-        <v>811</v>
-      </c>
       <c r="D806" s="14" t="s">
         <v>19</v>
       </c>
@@ -33392,25 +33368,25 @@
         <v>13</v>
       </c>
       <c r="F806" s="14" t="s">
-        <v>764</v>
+        <v>19</v>
       </c>
       <c r="G806" s="6">
-        <v>143715.87</v>
+        <v>0</v>
       </c>
       <c r="H806" s="44">
-        <v>145376.06</v>
-      </c>
-      <c r="I806" s="44" t="s">
-        <v>812</v>
+        <v>0</v>
+      </c>
+      <c r="I806" s="44">
+        <v>0</v>
       </c>
       <c r="J806" s="44">
-        <v>148082.32999999999</v>
+        <v>0</v>
       </c>
       <c r="K806" s="44">
-        <v>149774.26</v>
+        <v>0</v>
       </c>
       <c r="L806" s="44">
-        <v>149774.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="807" spans="1:12">
@@ -33418,19 +33394,19 @@
         <v>659</v>
       </c>
       <c r="B807" s="4" t="s">
-        <v>733</v>
+        <v>811</v>
       </c>
       <c r="C807" s="14" t="s">
+        <v>812</v>
+      </c>
+      <c r="D807" s="14" t="s">
+        <v>761</v>
+      </c>
+      <c r="E807" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F807" s="14" t="s">
         <v>813</v>
-      </c>
-      <c r="D807" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E807" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F807" s="14" t="s">
-        <v>734</v>
       </c>
       <c r="G807" s="6">
         <v>0</v>
@@ -33456,7 +33432,7 @@
         <v>659</v>
       </c>
       <c r="B808" s="4" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C808" s="14" t="s">
         <v>814</v>
@@ -33468,7 +33444,7 @@
         <v>13</v>
       </c>
       <c r="F808" s="14" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="G808" s="6">
         <v>0</v>
@@ -33494,7 +33470,7 @@
         <v>659</v>
       </c>
       <c r="B809" s="4" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="C809" s="14" t="s">
         <v>815</v>
@@ -33506,7 +33482,7 @@
         <v>13</v>
       </c>
       <c r="F809" s="14" t="s">
-        <v>34</v>
+        <v>739</v>
       </c>
       <c r="G809" s="6">
         <v>0</v>
@@ -33532,19 +33508,19 @@
         <v>659</v>
       </c>
       <c r="B810" s="4" t="s">
-        <v>97</v>
+        <v>816</v>
       </c>
       <c r="C810" s="14" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D810" s="14" t="s">
-        <v>19</v>
+        <v>795</v>
       </c>
       <c r="E810" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F810" s="14" t="s">
-        <v>736</v>
+        <v>795</v>
       </c>
       <c r="G810" s="6">
         <v>0</v>
@@ -33566,14 +33542,14 @@
       </c>
     </row>
     <row r="811" spans="1:12">
-      <c r="A811" s="16" t="s">
+      <c r="A811" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="B811" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="C811" s="14" t="s">
-        <v>817</v>
+      <c r="B811" s="46" t="s">
+        <v>662</v>
+      </c>
+      <c r="C811" s="47" t="s">
+        <v>818</v>
       </c>
       <c r="D811" s="14" t="s">
         <v>19</v>
@@ -33581,37 +33557,37 @@
       <c r="E811" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F811" s="14" t="s">
-        <v>736</v>
-      </c>
-      <c r="G811" s="6">
-        <v>0</v>
-      </c>
-      <c r="H811" s="44">
-        <v>0</v>
-      </c>
-      <c r="I811" s="44">
-        <v>0</v>
-      </c>
-      <c r="J811" s="44">
-        <v>0</v>
-      </c>
-      <c r="K811" s="44">
-        <v>0</v>
-      </c>
-      <c r="L811" s="44">
-        <v>0</v>
+      <c r="F811" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G811" s="49">
+        <v>438968.32000000001</v>
+      </c>
+      <c r="H811" s="50">
+        <v>444144.33</v>
+      </c>
+      <c r="I811" s="50">
+        <v>427724.54</v>
+      </c>
+      <c r="J811" s="50">
+        <v>453090.18</v>
+      </c>
+      <c r="K811" s="50">
+        <v>458407.07</v>
+      </c>
+      <c r="L811" s="50">
+        <v>458407.07</v>
       </c>
     </row>
     <row r="812" spans="1:12">
-      <c r="A812" s="16" t="s">
+      <c r="A812" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="B812" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="C812" s="14" t="s">
-        <v>818</v>
+      <c r="B812" s="51" t="s">
+        <v>663</v>
+      </c>
+      <c r="C812" s="52" t="s">
+        <v>819</v>
       </c>
       <c r="D812" s="14" t="s">
         <v>19</v>
@@ -33619,177 +33595,177 @@
       <c r="E812" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F812" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G812" s="6">
-        <v>0</v>
-      </c>
-      <c r="H812" s="44">
-        <v>0</v>
-      </c>
-      <c r="I812" s="44">
-        <v>0</v>
-      </c>
-      <c r="J812" s="44">
-        <v>0</v>
-      </c>
-      <c r="K812" s="44">
-        <v>0</v>
-      </c>
-      <c r="L812" s="44">
+      <c r="F812" s="53" t="s">
+        <v>664</v>
+      </c>
+      <c r="G812" s="49">
+        <v>0</v>
+      </c>
+      <c r="H812" s="50">
+        <v>0</v>
+      </c>
+      <c r="I812" s="50">
+        <v>0</v>
+      </c>
+      <c r="J812" s="50">
+        <v>0</v>
+      </c>
+      <c r="K812" s="50">
+        <v>0</v>
+      </c>
+      <c r="L812" s="50">
         <v>0</v>
       </c>
     </row>
     <row r="813" spans="1:12">
-      <c r="A813" s="16" t="s">
+      <c r="A813" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="B813" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="C813" s="14" t="s">
+      <c r="B813" s="55" t="s">
+        <v>326</v>
+      </c>
+      <c r="C813" s="52" t="s">
         <v>820</v>
       </c>
       <c r="D813" s="14" t="s">
-        <v>761</v>
+        <v>19</v>
       </c>
       <c r="E813" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F813" s="14" t="s">
+      <c r="F813" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="G813" s="49">
+        <v>2360.8200000000002</v>
+      </c>
+      <c r="H813" s="50">
+        <v>2385.62</v>
+      </c>
+      <c r="I813" s="50">
+        <v>1978.85</v>
+      </c>
+      <c r="J813" s="50">
+        <v>2432.48</v>
+      </c>
+      <c r="K813" s="50">
+        <v>2458.06</v>
+      </c>
+      <c r="L813" s="50">
+        <v>2458.06</v>
+      </c>
+    </row>
+    <row r="814" spans="1:12">
+      <c r="A814" s="46" t="s">
+        <v>659</v>
+      </c>
+      <c r="B814" s="51" t="s">
+        <v>740</v>
+      </c>
+      <c r="C814" s="56" t="s">
         <v>821</v>
       </c>
-      <c r="G813" s="6">
-        <v>0</v>
-      </c>
-      <c r="H813" s="44">
-        <v>0</v>
-      </c>
-      <c r="I813" s="44">
-        <v>0</v>
-      </c>
-      <c r="J813" s="44">
-        <v>0</v>
-      </c>
-      <c r="K813" s="44">
-        <v>0</v>
-      </c>
-      <c r="L813" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="814" spans="1:12">
-      <c r="A814" s="16" t="s">
+      <c r="D814" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E814" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F814" s="53" t="s">
+        <v>731</v>
+      </c>
+      <c r="G814" s="49">
+        <v>0</v>
+      </c>
+      <c r="H814" s="50">
+        <v>0</v>
+      </c>
+      <c r="I814" s="50">
+        <v>0</v>
+      </c>
+      <c r="J814" s="50">
+        <v>0</v>
+      </c>
+      <c r="K814" s="50">
+        <v>0</v>
+      </c>
+      <c r="L814" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815" spans="1:12">
+      <c r="A815" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="B814" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="C814" s="14" t="s">
+      <c r="B815" s="51" t="s">
+        <v>665</v>
+      </c>
+      <c r="C815" s="52" t="s">
         <v>822</v>
       </c>
-      <c r="D814" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E814" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F814" s="14" t="s">
-        <v>736</v>
-      </c>
-      <c r="G814" s="6">
-        <v>0</v>
-      </c>
-      <c r="H814" s="44">
-        <v>0</v>
-      </c>
-      <c r="I814" s="44">
-        <v>0</v>
-      </c>
-      <c r="J814" s="44">
-        <v>0</v>
-      </c>
-      <c r="K814" s="44">
-        <v>0</v>
-      </c>
-      <c r="L814" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="815" spans="1:12">
-      <c r="A815" s="16" t="s">
+      <c r="D815" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E815" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F815" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="G815" s="49">
+        <v>1597847.33</v>
+      </c>
+      <c r="H815" s="50">
+        <v>2502843.37</v>
+      </c>
+      <c r="I815" s="50">
+        <v>2438101.4900000002</v>
+      </c>
+      <c r="J815" s="50">
+        <v>2639015.37</v>
+      </c>
+      <c r="K815" s="50">
+        <v>2586057.1800000002</v>
+      </c>
+      <c r="L815" s="50">
+        <v>2586057.1800000002</v>
+      </c>
+    </row>
+    <row r="816" spans="1:12">
+      <c r="A816" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="B815" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C815" s="14" t="s">
+      <c r="B816" s="51" t="s">
         <v>823</v>
       </c>
-      <c r="D815" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E815" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F815" s="14" t="s">
-        <v>739</v>
-      </c>
-      <c r="G815" s="6">
-        <v>0</v>
-      </c>
-      <c r="H815" s="44">
-        <v>0</v>
-      </c>
-      <c r="I815" s="44">
-        <v>0</v>
-      </c>
-      <c r="J815" s="44">
-        <v>0</v>
-      </c>
-      <c r="K815" s="44">
-        <v>0</v>
-      </c>
-      <c r="L815" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="816" spans="1:12">
-      <c r="A816" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="B816" s="4" t="s">
+      <c r="C816" s="52" t="s">
         <v>824</v>
       </c>
-      <c r="C816" s="14" t="s">
+      <c r="D816" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E816" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F816" s="54" t="s">
         <v>825</v>
       </c>
-      <c r="D816" s="14" t="s">
-        <v>799</v>
-      </c>
-      <c r="E816" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F816" s="14" t="s">
-        <v>799</v>
-      </c>
-      <c r="G816" s="6">
-        <v>0</v>
-      </c>
-      <c r="H816" s="44">
-        <v>0</v>
-      </c>
-      <c r="I816" s="44">
-        <v>0</v>
-      </c>
-      <c r="J816" s="44">
-        <v>0</v>
-      </c>
-      <c r="K816" s="44">
-        <v>0</v>
-      </c>
-      <c r="L816" s="44">
+      <c r="G816" s="49">
+        <v>0</v>
+      </c>
+      <c r="H816" s="50">
+        <v>0</v>
+      </c>
+      <c r="I816" s="50">
+        <v>0</v>
+      </c>
+      <c r="J816" s="50">
+        <v>0</v>
+      </c>
+      <c r="K816" s="50">
+        <v>0</v>
+      </c>
+      <c r="L816" s="50">
         <v>0</v>
       </c>
     </row>
@@ -33797,10 +33773,10 @@
       <c r="A817" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="B817" s="46" t="s">
-        <v>662</v>
-      </c>
-      <c r="C817" s="47" t="s">
+      <c r="B817" s="51" t="s">
+        <v>666</v>
+      </c>
+      <c r="C817" s="52" t="s">
         <v>826</v>
       </c>
       <c r="D817" s="14" t="s">
@@ -33809,26 +33785,26 @@
       <c r="E817" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F817" s="48" t="s">
-        <v>34</v>
+      <c r="F817" s="53" t="s">
+        <v>98</v>
       </c>
       <c r="G817" s="49">
-        <v>438968.32000000001</v>
+        <v>0</v>
       </c>
       <c r="H817" s="50">
-        <v>444144.33</v>
+        <v>0</v>
       </c>
       <c r="I817" s="50">
-        <v>427724.54</v>
+        <v>0</v>
       </c>
       <c r="J817" s="50">
-        <v>453090.18</v>
+        <v>0</v>
       </c>
       <c r="K817" s="50">
-        <v>458407.07</v>
+        <v>0</v>
       </c>
       <c r="L817" s="50">
-        <v>458407.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="818" spans="1:12">
@@ -33836,7 +33812,7 @@
         <v>659</v>
       </c>
       <c r="B818" s="51" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C818" s="52" t="s">
         <v>827</v>
@@ -33847,37 +33823,37 @@
       <c r="E818" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F818" s="53" t="s">
-        <v>664</v>
-      </c>
-      <c r="G818" s="49">
-        <v>0</v>
-      </c>
-      <c r="H818" s="50">
-        <v>0</v>
-      </c>
-      <c r="I818" s="50">
-        <v>0</v>
+      <c r="F818" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="G818" s="49" t="s">
+        <v>828</v>
+      </c>
+      <c r="H818" s="50" t="s">
+        <v>829</v>
+      </c>
+      <c r="I818" s="50" t="s">
+        <v>830</v>
       </c>
       <c r="J818" s="50">
-        <v>0</v>
+        <v>20004.05</v>
       </c>
       <c r="K818" s="50">
-        <v>0</v>
+        <v>20082.189999999999</v>
       </c>
       <c r="L818" s="50">
-        <v>0</v>
+        <v>20082.189999999999</v>
       </c>
     </row>
     <row r="819" spans="1:12">
       <c r="A819" s="46" t="s">
         <v>659</v>
       </c>
-      <c r="B819" s="55" t="s">
-        <v>326</v>
+      <c r="B819" s="51" t="s">
+        <v>668</v>
       </c>
       <c r="C819" s="52" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D819" s="14" t="s">
         <v>19</v>
@@ -33885,26 +33861,26 @@
       <c r="E819" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F819" s="53" t="s">
-        <v>98</v>
+      <c r="F819" s="54" t="s">
+        <v>34</v>
       </c>
       <c r="G819" s="49">
-        <v>2360.8200000000002</v>
+        <v>0</v>
       </c>
       <c r="H819" s="50">
-        <v>2385.62</v>
+        <v>0</v>
       </c>
       <c r="I819" s="50">
-        <v>1978.85</v>
+        <v>0</v>
       </c>
       <c r="J819" s="50">
-        <v>2432.48</v>
+        <v>0</v>
       </c>
       <c r="K819" s="50">
-        <v>2458.06</v>
+        <v>0</v>
       </c>
       <c r="L819" s="50">
-        <v>2458.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="820" spans="1:12">
@@ -33912,10 +33888,10 @@
         <v>659</v>
       </c>
       <c r="B820" s="51" t="s">
-        <v>740</v>
-      </c>
-      <c r="C820" s="56" t="s">
-        <v>829</v>
+        <v>669</v>
+      </c>
+      <c r="C820" s="52" t="s">
+        <v>832</v>
       </c>
       <c r="D820" s="14" t="s">
         <v>19</v>
@@ -33923,8 +33899,8 @@
       <c r="E820" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F820" s="53" t="s">
-        <v>731</v>
+      <c r="F820" s="54" t="s">
+        <v>619</v>
       </c>
       <c r="G820" s="49">
         <v>0</v>
@@ -33950,37 +33926,37 @@
         <v>659</v>
       </c>
       <c r="B821" s="51" t="s">
-        <v>665</v>
+        <v>741</v>
       </c>
       <c r="C821" s="52" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D821" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E821" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F821" s="54" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="F821" s="53" t="s">
+        <v>742</v>
       </c>
       <c r="G821" s="49">
-        <v>1597847.33</v>
+        <v>0</v>
       </c>
       <c r="H821" s="50">
-        <v>2502843.37</v>
+        <v>0</v>
       </c>
       <c r="I821" s="50">
-        <v>2438101.4900000002</v>
+        <v>0</v>
       </c>
       <c r="J821" s="50">
-        <v>2639015.37</v>
+        <v>0</v>
       </c>
       <c r="K821" s="50">
-        <v>2586057.1800000002</v>
+        <v>0</v>
       </c>
       <c r="L821" s="50">
-        <v>2586057.1800000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822" spans="1:12">
@@ -33988,10 +33964,10 @@
         <v>659</v>
       </c>
       <c r="B822" s="51" t="s">
-        <v>831</v>
+        <v>743</v>
       </c>
       <c r="C822" s="52" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D822" s="14" t="s">
         <v>19</v>
@@ -33999,8 +33975,8 @@
       <c r="E822" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F822" s="54" t="s">
-        <v>833</v>
+      <c r="F822" s="53" t="s">
+        <v>744</v>
       </c>
       <c r="G822" s="49">
         <v>0</v>
@@ -34026,10 +34002,10 @@
         <v>659</v>
       </c>
       <c r="B823" s="51" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C823" s="52" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D823" s="14" t="s">
         <v>19</v>
@@ -34037,8 +34013,8 @@
       <c r="E823" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F823" s="53" t="s">
-        <v>98</v>
+      <c r="F823" s="54" t="s">
+        <v>664</v>
       </c>
       <c r="G823" s="49">
         <v>0</v>
@@ -34064,10 +34040,10 @@
         <v>659</v>
       </c>
       <c r="B824" s="51" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C824" s="52" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D824" s="14" t="s">
         <v>19</v>
@@ -34075,227 +34051,225 @@
       <c r="E824" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F824" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="G824" s="49" t="s">
-        <v>836</v>
-      </c>
-      <c r="H824" s="50" t="s">
+      <c r="F824" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G824" s="49">
+        <v>0</v>
+      </c>
+      <c r="H824" s="50">
+        <v>0</v>
+      </c>
+      <c r="I824" s="50">
+        <v>0</v>
+      </c>
+      <c r="J824" s="50">
+        <v>0</v>
+      </c>
+      <c r="K824" s="50">
+        <v>0</v>
+      </c>
+      <c r="L824" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825" spans="1:12">
+      <c r="A825" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B825" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="C825" s="24" t="s">
         <v>837</v>
       </c>
-      <c r="I824" s="50" t="s">
+      <c r="D825" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E825" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F825" s="14" t="s">
+        <v>731</v>
+      </c>
+      <c r="G825" s="57">
+        <v>0</v>
+      </c>
+      <c r="H825" s="57">
+        <v>0</v>
+      </c>
+      <c r="I825" s="57">
+        <v>0</v>
+      </c>
+      <c r="J825" s="57">
+        <v>0</v>
+      </c>
+      <c r="K825" s="57">
+        <v>0</v>
+      </c>
+      <c r="L825" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826" spans="1:12">
+      <c r="A826" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B826" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C826" s="24" t="s">
         <v>838</v>
       </c>
-      <c r="J824" s="50">
-        <v>20004.05</v>
-      </c>
-      <c r="K824" s="50">
-        <v>20082.189999999999</v>
-      </c>
-      <c r="L824" s="50">
-        <v>20082.189999999999</v>
-      </c>
-    </row>
-    <row r="825" spans="1:12">
-      <c r="A825" s="46" t="s">
+      <c r="D826" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E826" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F826" s="14" t="s">
+        <v>731</v>
+      </c>
+      <c r="G826" s="57">
+        <v>0</v>
+      </c>
+      <c r="H826" s="57">
+        <v>0</v>
+      </c>
+      <c r="I826" s="57">
+        <v>0</v>
+      </c>
+      <c r="J826" s="57">
+        <v>0</v>
+      </c>
+      <c r="K826" s="57">
+        <v>0</v>
+      </c>
+      <c r="L826" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827" spans="1:12">
+      <c r="A827" s="11" t="s">
         <v>659</v>
       </c>
-      <c r="B825" s="51" t="s">
-        <v>668</v>
-      </c>
-      <c r="C825" s="52" t="s">
+      <c r="B827" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="C827" s="24" t="s">
         <v>839</v>
       </c>
-      <c r="D825" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E825" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F825" s="54" t="s">
+      <c r="D827" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E827" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F827" s="14" t="s">
+        <v>736</v>
+      </c>
+      <c r="G827" s="57">
+        <v>0</v>
+      </c>
+      <c r="H827" s="57">
+        <v>0</v>
+      </c>
+      <c r="I827" s="57">
+        <v>0</v>
+      </c>
+      <c r="J827" s="57">
+        <v>0</v>
+      </c>
+      <c r="K827" s="57">
+        <v>0</v>
+      </c>
+      <c r="L827" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828" spans="1:12">
+      <c r="A828" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="B828" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="C828" s="24">
+        <v>11005560</v>
+      </c>
+      <c r="D828" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E828" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F828" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G825" s="49">
-        <v>0</v>
-      </c>
-      <c r="H825" s="50">
-        <v>0</v>
-      </c>
-      <c r="I825" s="50">
-        <v>0</v>
-      </c>
-      <c r="J825" s="50">
-        <v>0</v>
-      </c>
-      <c r="K825" s="50">
-        <v>0</v>
-      </c>
-      <c r="L825" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="826" spans="1:12">
-      <c r="A826" s="46" t="s">
-        <v>659</v>
-      </c>
-      <c r="B826" s="51" t="s">
-        <v>669</v>
-      </c>
-      <c r="C826" s="52" t="s">
-        <v>840</v>
-      </c>
-      <c r="D826" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E826" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F826" s="54" t="s">
-        <v>619</v>
-      </c>
-      <c r="G826" s="49">
-        <v>0</v>
-      </c>
-      <c r="H826" s="50">
-        <v>0</v>
-      </c>
-      <c r="I826" s="50">
-        <v>0</v>
-      </c>
-      <c r="J826" s="50">
-        <v>0</v>
-      </c>
-      <c r="K826" s="50">
-        <v>0</v>
-      </c>
-      <c r="L826" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="827" spans="1:12">
-      <c r="A827" s="46" t="s">
-        <v>659</v>
-      </c>
-      <c r="B827" s="51" t="s">
-        <v>741</v>
-      </c>
-      <c r="C827" s="52" t="s">
-        <v>841</v>
-      </c>
-      <c r="D827" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E827" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F827" s="53" t="s">
-        <v>742</v>
-      </c>
-      <c r="G827" s="49">
-        <v>0</v>
-      </c>
-      <c r="H827" s="50">
-        <v>0</v>
-      </c>
-      <c r="I827" s="50">
-        <v>0</v>
-      </c>
-      <c r="J827" s="50">
-        <v>0</v>
-      </c>
-      <c r="K827" s="50">
-        <v>0</v>
-      </c>
-      <c r="L827" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="828" spans="1:12">
-      <c r="A828" s="46" t="s">
-        <v>659</v>
-      </c>
-      <c r="B828" s="51" t="s">
-        <v>743</v>
-      </c>
-      <c r="C828" s="52" t="s">
-        <v>842</v>
-      </c>
-      <c r="D828" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E828" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F828" s="53" t="s">
-        <v>744</v>
-      </c>
-      <c r="G828" s="49">
-        <v>0</v>
-      </c>
-      <c r="H828" s="50">
-        <v>0</v>
-      </c>
-      <c r="I828" s="50">
-        <v>0</v>
-      </c>
-      <c r="J828" s="50">
-        <v>0</v>
-      </c>
-      <c r="K828" s="50">
-        <v>0</v>
-      </c>
-      <c r="L828" s="50">
-        <v>0</v>
+      <c r="G828" s="57">
+        <v>3547349.92</v>
+      </c>
+      <c r="H828" s="57">
+        <v>5584985.7199999997</v>
+      </c>
+      <c r="I828" s="57">
+        <v>5629373.79</v>
+      </c>
+      <c r="J828" s="57">
+        <v>5672338.3700000001</v>
+      </c>
+      <c r="K828" s="57">
+        <v>5736847.6799999997</v>
+      </c>
+      <c r="L828" s="57">
+        <v>5757667.7000000002</v>
       </c>
     </row>
     <row r="829" spans="1:12">
-      <c r="A829" s="46" t="s">
-        <v>659</v>
-      </c>
-      <c r="B829" s="51" t="s">
-        <v>670</v>
-      </c>
-      <c r="C829" s="52" t="s">
-        <v>843</v>
+      <c r="A829" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="B829" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="C829" s="24">
+        <v>15667976</v>
       </c>
       <c r="D829" s="14" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="E829" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F829" s="54" t="s">
-        <v>664</v>
-      </c>
-      <c r="G829" s="49">
-        <v>0</v>
-      </c>
-      <c r="H829" s="50">
-        <v>0</v>
-      </c>
-      <c r="I829" s="50">
-        <v>0</v>
-      </c>
-      <c r="J829" s="50">
-        <v>0</v>
-      </c>
-      <c r="K829" s="50">
-        <v>0</v>
-      </c>
-      <c r="L829" s="50">
-        <v>0</v>
+      <c r="F829" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G829" s="57"/>
+      <c r="H829" s="57">
+        <v>0</v>
+      </c>
+      <c r="I829" s="57">
+        <v>601667.09</v>
+      </c>
+      <c r="J829" s="57">
+        <v>608802.88</v>
+      </c>
+      <c r="K829" s="57">
+        <v>814501</v>
+      </c>
+      <c r="L829" s="57">
+        <v>816049.08</v>
       </c>
     </row>
     <row r="830" spans="1:12">
-      <c r="A830" s="46" t="s">
-        <v>659</v>
-      </c>
-      <c r="B830" s="51" t="s">
-        <v>671</v>
-      </c>
-      <c r="C830" s="52" t="s">
-        <v>844</v>
+      <c r="A830" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="B830" s="20" t="s">
+        <v>748</v>
+      </c>
+      <c r="C830" s="24">
+        <v>10940590</v>
       </c>
       <c r="D830" s="14" t="s">
         <v>19</v>
@@ -34303,75 +34277,67 @@
       <c r="E830" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F830" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="G830" s="49">
-        <v>0</v>
-      </c>
-      <c r="H830" s="50">
-        <v>0</v>
-      </c>
-      <c r="I830" s="50">
-        <v>0</v>
-      </c>
-      <c r="J830" s="50">
-        <v>0</v>
-      </c>
-      <c r="K830" s="50">
-        <v>0</v>
-      </c>
-      <c r="L830" s="50">
-        <v>0</v>
+      <c r="F830" s="24" t="s">
+        <v>726</v>
+      </c>
+      <c r="G830" s="57">
+        <v>693260.12</v>
+      </c>
+      <c r="H830" s="57">
+        <v>693384.27</v>
+      </c>
+      <c r="I830" s="57">
+        <v>703513.4</v>
+      </c>
+      <c r="J830" s="57">
+        <v>712240.78</v>
+      </c>
+      <c r="K830" s="57">
+        <v>0</v>
+      </c>
+      <c r="L830" s="57">
+        <v>67.39</v>
       </c>
     </row>
     <row r="831" spans="1:12">
       <c r="A831" s="11" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="B831" s="11" t="s">
-        <v>745</v>
-      </c>
-      <c r="C831" s="24" t="s">
-        <v>845</v>
+        <v>142</v>
+      </c>
+      <c r="C831" s="24">
+        <v>11830618</v>
       </c>
       <c r="D831" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E831" s="14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F831" s="14" t="s">
-        <v>731</v>
-      </c>
-      <c r="G831" s="57">
-        <v>0</v>
-      </c>
-      <c r="H831" s="57">
-        <v>0</v>
-      </c>
-      <c r="I831" s="57">
-        <v>0</v>
-      </c>
-      <c r="J831" s="57">
-        <v>0</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G831" s="57"/>
+      <c r="H831" s="57"/>
+      <c r="I831" s="57"/>
+      <c r="J831" s="57"/>
       <c r="K831" s="57">
-        <v>0</v>
+        <v>181600.49</v>
       </c>
       <c r="L831" s="57">
-        <v>0</v>
+        <v>182337.8</v>
       </c>
     </row>
     <row r="832" spans="1:12">
       <c r="A832" s="11" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="B832" s="11" t="s">
-        <v>746</v>
+        <v>674</v>
       </c>
       <c r="C832" s="24" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="D832" s="14" t="s">
         <v>19</v>
@@ -34380,7 +34346,7 @@
         <v>13</v>
       </c>
       <c r="F832" s="14" t="s">
-        <v>731</v>
+        <v>19</v>
       </c>
       <c r="G832" s="57">
         <v>0</v>
@@ -34397,19 +34363,19 @@
       <c r="K832" s="57">
         <v>0</v>
       </c>
-      <c r="L832" s="57">
-        <v>0</v>
+      <c r="L832" s="57" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="833" spans="1:12">
       <c r="A833" s="11" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="B833" s="11" t="s">
-        <v>747</v>
-      </c>
-      <c r="C833" s="24" t="s">
-        <v>847</v>
+        <v>675</v>
+      </c>
+      <c r="C833" s="24">
+        <v>10982276</v>
       </c>
       <c r="D833" s="14" t="s">
         <v>19</v>
@@ -34418,36 +34384,36 @@
         <v>13</v>
       </c>
       <c r="F833" s="14" t="s">
-        <v>736</v>
+        <v>676</v>
       </c>
       <c r="G833" s="57">
-        <v>0</v>
+        <v>9267874.1799999997</v>
       </c>
       <c r="H833" s="57">
-        <v>0</v>
+        <v>8895735.3000000007</v>
       </c>
       <c r="I833" s="57">
-        <v>0</v>
+        <v>9108114.6199999992</v>
       </c>
       <c r="J833" s="57">
-        <v>0</v>
+        <v>9228957.0899999999</v>
       </c>
       <c r="K833" s="57">
-        <v>0</v>
+        <v>9118300.2799999993</v>
       </c>
       <c r="L833" s="57">
-        <v>0</v>
+        <v>9052259.0099999998</v>
       </c>
     </row>
     <row r="834" spans="1:12">
       <c r="A834" s="11" t="s">
         <v>672</v>
       </c>
-      <c r="B834" s="20" t="s">
-        <v>540</v>
+      <c r="B834" s="11" t="s">
+        <v>727</v>
       </c>
       <c r="C834" s="24">
-        <v>11005560</v>
+        <v>12307245</v>
       </c>
       <c r="D834" s="14" t="s">
         <v>19</v>
@@ -34455,26 +34421,26 @@
       <c r="E834" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F834" s="24" t="s">
-        <v>34</v>
+      <c r="F834" s="14" t="s">
+        <v>726</v>
       </c>
       <c r="G834" s="57">
-        <v>3547349.92</v>
+        <v>0</v>
       </c>
       <c r="H834" s="57">
-        <v>5584985.7199999997</v>
+        <v>0</v>
       </c>
       <c r="I834" s="57">
-        <v>5629373.79</v>
+        <v>0</v>
       </c>
       <c r="J834" s="57">
-        <v>5672338.3700000001</v>
+        <v>0</v>
       </c>
       <c r="K834" s="57">
-        <v>5736847.6799999997</v>
+        <v>0</v>
       </c>
       <c r="L834" s="57">
-        <v>5757667.7000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="835" spans="1:12">
@@ -34482,46 +34448,48 @@
         <v>672</v>
       </c>
       <c r="B835" s="11" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C835" s="24">
-        <v>15667976</v>
+        <v>3844136</v>
       </c>
       <c r="D835" s="14" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="E835" s="14" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="F835" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G835" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="G835" s="57">
+        <v>57774.21</v>
+      </c>
       <c r="H835" s="57">
-        <v>0</v>
+        <v>57301.25</v>
       </c>
       <c r="I835" s="57">
-        <v>601667.09</v>
+        <v>58201.73</v>
       </c>
       <c r="J835" s="57">
-        <v>608802.88</v>
+        <v>58766.74</v>
       </c>
       <c r="K835" s="57">
-        <v>814501</v>
+        <v>59670.1</v>
       </c>
       <c r="L835" s="57">
-        <v>816049.08</v>
+        <v>60227.95</v>
       </c>
     </row>
     <row r="836" spans="1:12">
       <c r="A836" s="11" t="s">
         <v>672</v>
       </c>
-      <c r="B836" s="20" t="s">
-        <v>748</v>
+      <c r="B836" s="11" t="s">
+        <v>359</v>
       </c>
       <c r="C836" s="24">
-        <v>10940590</v>
+        <v>10936630</v>
       </c>
       <c r="D836" s="14" t="s">
         <v>19</v>
@@ -34529,342 +34497,350 @@
       <c r="E836" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F836" s="24" t="s">
+      <c r="F836" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G836" s="57">
+        <v>0</v>
+      </c>
+      <c r="H836" s="57">
+        <v>0</v>
+      </c>
+      <c r="I836" s="57">
+        <v>0</v>
+      </c>
+      <c r="J836" s="57">
+        <v>0</v>
+      </c>
+      <c r="K836" s="57">
+        <v>0</v>
+      </c>
+      <c r="L836" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837" spans="1:12">
+      <c r="A837" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="B837" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C837" s="5">
+        <v>10944986</v>
+      </c>
+      <c r="D837" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E837" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F837" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G837" s="58">
+        <v>0</v>
+      </c>
+      <c r="H837" s="58">
+        <v>0</v>
+      </c>
+      <c r="I837" s="58">
+        <v>0</v>
+      </c>
+      <c r="J837" s="58">
+        <v>0</v>
+      </c>
+      <c r="K837" s="58">
+        <v>0</v>
+      </c>
+      <c r="L837" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838" spans="1:12">
+      <c r="A838" s="59" t="s">
+        <v>672</v>
+      </c>
+      <c r="B838" s="34" t="s">
+        <v>678</v>
+      </c>
+      <c r="C838" s="60">
+        <v>11071318</v>
+      </c>
+      <c r="D838" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E838" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F838" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G838" s="58">
+        <v>388119.7</v>
+      </c>
+      <c r="H838" s="58">
+        <v>453391.34</v>
+      </c>
+      <c r="I838" s="58">
+        <v>458010.44</v>
+      </c>
+      <c r="J838" s="58">
+        <v>463159.45</v>
+      </c>
+      <c r="K838" s="58">
+        <v>467745.11</v>
+      </c>
+      <c r="L838" s="58">
+        <v>469506.01</v>
+      </c>
+    </row>
+    <row r="839" spans="1:12">
+      <c r="A839" s="61" t="s">
+        <v>672</v>
+      </c>
+      <c r="B839" s="61" t="s">
+        <v>363</v>
+      </c>
+      <c r="C839" s="62" t="s">
+        <v>841</v>
+      </c>
+      <c r="D839" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E839" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F839" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="G839" s="58">
+        <v>0</v>
+      </c>
+      <c r="H839" s="58">
+        <v>0</v>
+      </c>
+      <c r="I839" s="58">
+        <v>0</v>
+      </c>
+      <c r="J839" s="58">
+        <v>0</v>
+      </c>
+      <c r="K839" s="58">
+        <v>0</v>
+      </c>
+      <c r="L839" s="58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="840" spans="1:12">
+      <c r="A840" s="61" t="s">
+        <v>672</v>
+      </c>
+      <c r="B840" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C840" s="5">
+        <v>11026371</v>
+      </c>
+      <c r="D840" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E840" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F840" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G840" s="58">
+        <v>4007767.83</v>
+      </c>
+      <c r="H840" s="58">
+        <v>4183923.59</v>
+      </c>
+      <c r="I840" s="58">
+        <v>4337170.46</v>
+      </c>
+      <c r="J840" s="58">
+        <v>4490316.03</v>
+      </c>
+      <c r="K840" s="58">
+        <v>0</v>
+      </c>
+      <c r="L840" s="58">
+        <v>333.27</v>
+      </c>
+    </row>
+    <row r="841" spans="1:12">
+      <c r="A841" s="61" t="s">
+        <v>672</v>
+      </c>
+      <c r="B841" s="61" t="s">
+        <v>732</v>
+      </c>
+      <c r="C841" s="62" t="s">
+        <v>842</v>
+      </c>
+      <c r="D841" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E841" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F841" s="32" t="s">
         <v>726</v>
       </c>
-      <c r="G836" s="57">
-        <v>693260.12</v>
-      </c>
-      <c r="H836" s="57">
-        <v>693384.27</v>
-      </c>
-      <c r="I836" s="57">
-        <v>703513.4</v>
-      </c>
-      <c r="J836" s="57">
-        <v>712240.78</v>
-      </c>
-      <c r="K836" s="57">
-        <v>0</v>
-      </c>
-      <c r="L836" s="57">
-        <v>67.39</v>
-      </c>
-    </row>
-    <row r="837" spans="1:12">
-      <c r="A837" s="11" t="s">
+      <c r="G841" s="58">
+        <v>91444.94</v>
+      </c>
+      <c r="H841" s="58">
+        <v>92329.17</v>
+      </c>
+      <c r="I841" s="58">
+        <v>94752.2</v>
+      </c>
+      <c r="J841" s="58">
+        <v>96388.33</v>
+      </c>
+      <c r="K841" s="58">
+        <v>98887.16</v>
+      </c>
+      <c r="L841" s="58">
+        <v>98887.16</v>
+      </c>
+    </row>
+    <row r="842" spans="1:12">
+      <c r="A842" s="63" t="s">
         <v>672</v>
       </c>
-      <c r="B837" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C837" s="24">
-        <v>11830618</v>
-      </c>
-      <c r="D837" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E837" s="14" t="s">
+      <c r="B842" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C842" s="64" t="s">
+        <v>843</v>
+      </c>
+      <c r="D842" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E842" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F842" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="G842" s="65">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="H842" s="65">
+        <v>0</v>
+      </c>
+      <c r="I842" s="65">
+        <v>0</v>
+      </c>
+      <c r="J842" s="65">
+        <v>0</v>
+      </c>
+      <c r="K842" s="65">
+        <v>0</v>
+      </c>
+      <c r="L842" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843" spans="1:12">
+      <c r="A843" s="61" t="s">
+        <v>681</v>
+      </c>
+      <c r="B843" s="66" t="s">
+        <v>111</v>
+      </c>
+      <c r="C843" s="67">
+        <v>5637768</v>
+      </c>
+      <c r="D843" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E843" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F843" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="G843" s="58">
+        <v>110396.14</v>
+      </c>
+      <c r="H843" s="58">
+        <v>111483.66</v>
+      </c>
+      <c r="I843" s="58">
+        <v>108075.3</v>
+      </c>
+      <c r="J843" s="58">
+        <v>108551.75</v>
+      </c>
+      <c r="K843" s="58">
+        <v>105789.27</v>
+      </c>
+      <c r="L843" s="58">
+        <v>105789.27</v>
+      </c>
+    </row>
+    <row r="844" spans="1:12">
+      <c r="A844" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B844" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C844" s="67" t="s">
+        <v>683</v>
+      </c>
+      <c r="D844" s="14" t="s">
+        <v>749</v>
+      </c>
+      <c r="E844" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F837" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G837" s="57"/>
-      <c r="H837" s="57"/>
-      <c r="I837" s="57"/>
-      <c r="J837" s="57"/>
-      <c r="K837" s="57">
-        <v>181600.49</v>
-      </c>
-      <c r="L837" s="57">
-        <v>182337.8</v>
-      </c>
-    </row>
-    <row r="838" spans="1:12">
-      <c r="A838" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="B838" s="11" t="s">
-        <v>674</v>
-      </c>
-      <c r="C838" s="24" t="s">
-        <v>848</v>
-      </c>
-      <c r="D838" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E838" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F838" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G838" s="57">
-        <v>0</v>
-      </c>
-      <c r="H838" s="57">
-        <v>0</v>
-      </c>
-      <c r="I838" s="57">
-        <v>0</v>
-      </c>
-      <c r="J838" s="57">
-        <v>0</v>
-      </c>
-      <c r="K838" s="57">
-        <v>0</v>
-      </c>
-      <c r="L838" s="57" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="839" spans="1:12">
-      <c r="A839" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="B839" s="11" t="s">
-        <v>675</v>
-      </c>
-      <c r="C839" s="24">
-        <v>10982276</v>
-      </c>
-      <c r="D839" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E839" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F839" s="14" t="s">
-        <v>676</v>
-      </c>
-      <c r="G839" s="57">
-        <v>9267874.1799999997</v>
-      </c>
-      <c r="H839" s="57">
-        <v>8895735.3000000007</v>
-      </c>
-      <c r="I839" s="57">
-        <v>9108114.6199999992</v>
-      </c>
-      <c r="J839" s="57">
-        <v>9228957.0899999999</v>
-      </c>
-      <c r="K839" s="57">
-        <v>9118300.2799999993</v>
-      </c>
-      <c r="L839" s="57">
-        <v>9052259.0099999998</v>
-      </c>
-    </row>
-    <row r="840" spans="1:12">
-      <c r="A840" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="B840" s="11" t="s">
-        <v>727</v>
-      </c>
-      <c r="C840" s="24">
-        <v>12307245</v>
-      </c>
-      <c r="D840" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E840" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F840" s="14" t="s">
-        <v>726</v>
-      </c>
-      <c r="G840" s="57">
-        <v>0</v>
-      </c>
-      <c r="H840" s="57">
-        <v>0</v>
-      </c>
-      <c r="I840" s="57">
-        <v>0</v>
-      </c>
-      <c r="J840" s="57">
-        <v>0</v>
-      </c>
-      <c r="K840" s="57">
-        <v>0</v>
-      </c>
-      <c r="L840" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="841" spans="1:12">
-      <c r="A841" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="B841" s="11" t="s">
-        <v>677</v>
-      </c>
-      <c r="C841" s="24">
-        <v>3844136</v>
-      </c>
-      <c r="D841" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E841" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F841" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="G841" s="57">
-        <v>57774.21</v>
-      </c>
-      <c r="H841" s="57">
-        <v>57301.25</v>
-      </c>
-      <c r="I841" s="57">
-        <v>58201.73</v>
-      </c>
-      <c r="J841" s="57">
-        <v>58766.74</v>
-      </c>
-      <c r="K841" s="57">
-        <v>59670.1</v>
-      </c>
-      <c r="L841" s="57">
-        <v>60227.95</v>
-      </c>
-    </row>
-    <row r="842" spans="1:12">
-      <c r="A842" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="B842" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="C842" s="24">
-        <v>10936630</v>
-      </c>
-      <c r="D842" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E842" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F842" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="G842" s="57">
-        <v>0</v>
-      </c>
-      <c r="H842" s="57">
-        <v>0</v>
-      </c>
-      <c r="I842" s="57">
-        <v>0</v>
-      </c>
-      <c r="J842" s="57">
-        <v>0</v>
-      </c>
-      <c r="K842" s="57">
-        <v>0</v>
-      </c>
-      <c r="L842" s="57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="843" spans="1:12">
-      <c r="A843" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="B843" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="C843" s="5">
-        <v>10944986</v>
-      </c>
-      <c r="D843" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E843" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F843" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G843" s="58">
-        <v>0</v>
-      </c>
-      <c r="H843" s="58">
-        <v>0</v>
-      </c>
-      <c r="I843" s="58">
-        <v>0</v>
-      </c>
-      <c r="J843" s="58">
-        <v>0</v>
-      </c>
-      <c r="K843" s="58">
-        <v>0</v>
-      </c>
-      <c r="L843" s="58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="844" spans="1:12">
-      <c r="A844" s="59" t="s">
-        <v>672</v>
-      </c>
-      <c r="B844" s="34" t="s">
-        <v>678</v>
-      </c>
-      <c r="C844" s="60">
-        <v>11071318</v>
-      </c>
-      <c r="D844" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E844" s="14" t="s">
-        <v>13</v>
-      </c>
       <c r="F844" s="32" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G844" s="58">
-        <v>388119.7</v>
+        <v>62476.1</v>
       </c>
       <c r="H844" s="58">
-        <v>453391.34</v>
+        <v>63892.32</v>
       </c>
       <c r="I844" s="58">
-        <v>458010.44</v>
+        <v>64778.33</v>
       </c>
       <c r="J844" s="58">
-        <v>463159.45</v>
+        <v>65726.7</v>
       </c>
       <c r="K844" s="58">
-        <v>467745.11</v>
+        <v>65726.7</v>
       </c>
       <c r="L844" s="58">
-        <v>469506.01</v>
+        <v>65726.7</v>
       </c>
     </row>
     <row r="845" spans="1:12">
       <c r="A845" s="61" t="s">
-        <v>672</v>
-      </c>
-      <c r="B845" s="61" t="s">
-        <v>363</v>
-      </c>
-      <c r="C845" s="62" t="s">
-        <v>849</v>
-      </c>
-      <c r="D845" s="5" t="s">
-        <v>19</v>
+        <v>682</v>
+      </c>
+      <c r="B845" s="66" t="s">
+        <v>750</v>
+      </c>
+      <c r="C845" s="67" t="s">
+        <v>751</v>
+      </c>
+      <c r="D845" s="14" t="s">
+        <v>752</v>
       </c>
       <c r="E845" s="14" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="F845" s="32" t="s">
-        <v>39</v>
+        <v>753</v>
       </c>
       <c r="G845" s="58">
         <v>0</v>
@@ -34881,19 +34857,19 @@
       <c r="K845" s="58">
         <v>0</v>
       </c>
-      <c r="L845" s="58" t="s">
-        <v>22</v>
+      <c r="L845" s="58">
+        <v>0</v>
       </c>
     </row>
     <row r="846" spans="1:12">
       <c r="A846" s="61" t="s">
-        <v>672</v>
-      </c>
-      <c r="B846" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="C846" s="5">
-        <v>11026371</v>
+        <v>682</v>
+      </c>
+      <c r="B846" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C846" s="62" t="s">
+        <v>754</v>
       </c>
       <c r="D846" s="14" t="s">
         <v>19</v>
@@ -34901,189 +34877,177 @@
       <c r="E846" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F846" s="14" t="s">
-        <v>98</v>
+      <c r="F846" s="32" t="s">
+        <v>731</v>
       </c>
       <c r="G846" s="58">
-        <v>4007767.83</v>
+        <v>117240.88</v>
       </c>
       <c r="H846" s="58">
-        <v>4183923.59</v>
+        <v>120226.22</v>
       </c>
       <c r="I846" s="58">
-        <v>4337170.46</v>
+        <v>122541.13</v>
       </c>
       <c r="J846" s="58">
-        <v>4490316.03</v>
+        <v>125168.34</v>
       </c>
       <c r="K846" s="58">
-        <v>0</v>
+        <v>125168.34</v>
       </c>
       <c r="L846" s="58">
-        <v>333.27</v>
+        <v>125168.34</v>
       </c>
     </row>
     <row r="847" spans="1:12">
-      <c r="A847" s="61" t="s">
-        <v>672</v>
-      </c>
-      <c r="B847" s="61" t="s">
-        <v>732</v>
-      </c>
-      <c r="C847" s="62" t="s">
-        <v>850</v>
+      <c r="A847" s="63" t="s">
+        <v>682</v>
+      </c>
+      <c r="B847" s="63" t="s">
+        <v>684</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>685</v>
       </c>
       <c r="D847" s="14" t="s">
-        <v>19</v>
+        <v>749</v>
       </c>
       <c r="E847" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F847" s="32" t="s">
-        <v>726</v>
-      </c>
-      <c r="G847" s="58">
-        <v>91444.94</v>
-      </c>
-      <c r="H847" s="58">
-        <v>92329.17</v>
-      </c>
-      <c r="I847" s="58">
-        <v>94752.2</v>
-      </c>
-      <c r="J847" s="58">
-        <v>96388.33</v>
-      </c>
-      <c r="K847" s="58">
-        <v>98887.16</v>
-      </c>
-      <c r="L847" s="58">
-        <v>98887.16</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F847" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G847" s="58"/>
+      <c r="H847" s="58"/>
+      <c r="I847" s="65"/>
+      <c r="J847" s="65"/>
+      <c r="K847" s="65"/>
+      <c r="L847" s="65"/>
     </row>
     <row r="848" spans="1:12">
-      <c r="A848" s="63" t="s">
-        <v>672</v>
-      </c>
-      <c r="B848" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="C848" s="64" t="s">
-        <v>851</v>
-      </c>
-      <c r="D848" s="14" t="s">
+      <c r="A848" s="59" t="s">
+        <v>682</v>
+      </c>
+      <c r="B848" s="61" t="s">
+        <v>686</v>
+      </c>
+      <c r="C848" s="68" t="s">
+        <v>687</v>
+      </c>
+      <c r="D848" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E848" s="14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F848" s="14" t="s">
-        <v>619</v>
-      </c>
-      <c r="G848" s="65">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="H848" s="65">
-        <v>0</v>
-      </c>
-      <c r="I848" s="65">
-        <v>0</v>
-      </c>
-      <c r="J848" s="65">
-        <v>0</v>
-      </c>
-      <c r="K848" s="65">
-        <v>0</v>
-      </c>
-      <c r="L848" s="65">
+        <v>46</v>
+      </c>
+      <c r="G848" s="58">
+        <v>0</v>
+      </c>
+      <c r="H848" s="58">
+        <v>0</v>
+      </c>
+      <c r="I848" s="58">
+        <v>0</v>
+      </c>
+      <c r="J848" s="58">
+        <v>0</v>
+      </c>
+      <c r="K848" s="58">
+        <v>0</v>
+      </c>
+      <c r="L848" s="58">
         <v>0</v>
       </c>
     </row>
     <row r="849" spans="1:12">
-      <c r="A849" s="61" t="s">
-        <v>681</v>
-      </c>
-      <c r="B849" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="C849" s="67">
-        <v>5637768</v>
+      <c r="A849" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="B849" s="63" t="s">
+        <v>688</v>
+      </c>
+      <c r="C849" s="69" t="s">
+        <v>689</v>
       </c>
       <c r="D849" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E849" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F849" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="G849" s="58">
-        <v>110396.14</v>
-      </c>
-      <c r="H849" s="58">
-        <v>111483.66</v>
-      </c>
-      <c r="I849" s="58">
-        <v>108075.3</v>
-      </c>
-      <c r="J849" s="58">
-        <v>108551.75</v>
-      </c>
-      <c r="K849" s="58">
-        <v>105789.27</v>
-      </c>
-      <c r="L849" s="58">
-        <v>105789.27</v>
+        <v>13</v>
+      </c>
+      <c r="F849" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G849" s="65">
+        <v>0</v>
+      </c>
+      <c r="H849" s="65">
+        <v>0</v>
+      </c>
+      <c r="I849" s="65">
+        <v>0</v>
+      </c>
+      <c r="J849" s="65">
+        <v>0</v>
+      </c>
+      <c r="K849" s="65">
+        <v>0</v>
+      </c>
+      <c r="L849" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="850" spans="1:12">
-      <c r="A850" s="61" t="s">
+      <c r="A850" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B850" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="C850" s="67" t="s">
-        <v>683</v>
+      <c r="B850" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="C850" s="64" t="s">
+        <v>845</v>
       </c>
       <c r="D850" s="14" t="s">
-        <v>749</v>
+        <v>19</v>
       </c>
       <c r="E850" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F850" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="G850" s="58">
-        <v>62476.1</v>
-      </c>
-      <c r="H850" s="58">
-        <v>63892.32</v>
-      </c>
-      <c r="I850" s="58">
-        <v>64778.33</v>
-      </c>
-      <c r="J850" s="58">
-        <v>65726.7</v>
-      </c>
-      <c r="K850" s="58">
-        <v>65726.7</v>
-      </c>
-      <c r="L850" s="58">
-        <v>65726.7</v>
+        <v>13</v>
+      </c>
+      <c r="F850" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="G850" s="65">
+        <v>0</v>
+      </c>
+      <c r="H850" s="65">
+        <v>0</v>
+      </c>
+      <c r="I850" s="65">
+        <v>0</v>
+      </c>
+      <c r="J850" s="65">
+        <v>0</v>
+      </c>
+      <c r="K850" s="65">
+        <v>0</v>
+      </c>
+      <c r="L850" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="851" spans="1:12">
-      <c r="A851" s="61" t="s">
+      <c r="A851" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B851" s="66" t="s">
-        <v>750</v>
-      </c>
-      <c r="C851" s="67" t="s">
-        <v>751</v>
+      <c r="B851" s="63" t="s">
+        <v>755</v>
+      </c>
+      <c r="C851" s="69" t="s">
+        <v>756</v>
       </c>
       <c r="D851" s="14" t="s">
         <v>752</v>
@@ -35091,7 +35055,7 @@
       <c r="E851" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F851" s="32" t="s">
+      <c r="F851" s="14" t="s">
         <v>753</v>
       </c>
       <c r="G851" s="58">
@@ -35114,537 +35078,537 @@
       </c>
     </row>
     <row r="852" spans="1:12">
-      <c r="A852" s="61" t="s">
+      <c r="A852" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B852" s="61" t="s">
-        <v>33</v>
-      </c>
-      <c r="C852" s="62" t="s">
-        <v>754</v>
+      <c r="B852" s="63" t="s">
+        <v>846</v>
+      </c>
+      <c r="C852" s="69" t="s">
+        <v>847</v>
       </c>
       <c r="D852" s="14" t="s">
-        <v>19</v>
+        <v>761</v>
       </c>
       <c r="E852" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F852" s="32" t="s">
-        <v>731</v>
-      </c>
-      <c r="G852" s="58">
-        <v>117240.88</v>
-      </c>
-      <c r="H852" s="58">
-        <v>120226.22</v>
-      </c>
-      <c r="I852" s="58">
-        <v>122541.13</v>
-      </c>
-      <c r="J852" s="58">
-        <v>125168.34</v>
-      </c>
-      <c r="K852" s="58">
-        <v>125168.34</v>
-      </c>
-      <c r="L852" s="58">
-        <v>125168.34</v>
+      <c r="F852" s="14" t="s">
+        <v>762</v>
+      </c>
+      <c r="G852" s="65">
+        <v>0</v>
+      </c>
+      <c r="H852" s="65">
+        <v>0</v>
+      </c>
+      <c r="I852" s="65">
+        <v>0</v>
+      </c>
+      <c r="J852" s="65">
+        <v>0</v>
+      </c>
+      <c r="K852" s="65">
+        <v>0</v>
+      </c>
+      <c r="L852" s="65">
+        <v>0</v>
       </c>
     </row>
     <row r="853" spans="1:12">
-      <c r="A853" s="63" t="s">
+      <c r="A853" s="59" t="s">
         <v>682</v>
       </c>
-      <c r="B853" s="63" t="s">
-        <v>684</v>
-      </c>
-      <c r="C853" s="5" t="s">
-        <v>685</v>
+      <c r="B853" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C853" s="60" t="s">
+        <v>690</v>
       </c>
       <c r="D853" s="14" t="s">
-        <v>749</v>
+        <v>19</v>
       </c>
       <c r="E853" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F853" s="14" t="s">
-        <v>27</v>
+      <c r="F853" s="32" t="s">
+        <v>21</v>
       </c>
       <c r="G853" s="58"/>
       <c r="H853" s="58"/>
-      <c r="I853" s="65"/>
-      <c r="J853" s="65"/>
-      <c r="K853" s="65"/>
-      <c r="L853" s="65"/>
+      <c r="I853" s="58"/>
+      <c r="J853" s="58"/>
+      <c r="K853" s="58"/>
+      <c r="L853" s="58"/>
     </row>
     <row r="854" spans="1:12">
-      <c r="A854" s="59" t="s">
+      <c r="A854" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B854" s="61" t="s">
-        <v>686</v>
-      </c>
-      <c r="C854" s="68" t="s">
-        <v>687</v>
-      </c>
-      <c r="D854" s="5" t="s">
+      <c r="B854" s="63" t="s">
+        <v>555</v>
+      </c>
+      <c r="C854" s="24" t="s">
+        <v>691</v>
+      </c>
+      <c r="D854" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E854" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F854" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G854" s="65">
+        <v>142799.35</v>
+      </c>
+      <c r="H854" s="65">
+        <v>200631.22</v>
+      </c>
+      <c r="I854" s="65">
+        <v>260124.32</v>
+      </c>
+      <c r="J854" s="65">
+        <v>313433.53000000003</v>
+      </c>
+      <c r="K854" s="65">
+        <v>313433.53000000003</v>
+      </c>
+      <c r="L854" s="65">
+        <v>313433.53000000003</v>
+      </c>
+    </row>
+    <row r="855" spans="1:12">
+      <c r="A855" s="34" t="s">
+        <v>682</v>
+      </c>
+      <c r="B855" s="61" t="s">
+        <v>180</v>
+      </c>
+      <c r="C855" s="60" t="s">
+        <v>692</v>
+      </c>
+      <c r="D855" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E855" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F855" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G855" s="58">
+        <v>0</v>
+      </c>
+      <c r="H855" s="58">
+        <v>0</v>
+      </c>
+      <c r="I855" s="58">
+        <v>17721.21</v>
+      </c>
+      <c r="J855" s="58">
+        <v>17737.8</v>
+      </c>
+      <c r="K855" s="58">
+        <v>17737.8</v>
+      </c>
+      <c r="L855" s="58">
+        <v>17737.8</v>
+      </c>
+    </row>
+    <row r="856" spans="1:12">
+      <c r="A856" s="59" t="s">
+        <v>682</v>
+      </c>
+      <c r="B856" s="59" t="s">
+        <v>693</v>
+      </c>
+      <c r="C856" s="60" t="s">
+        <v>694</v>
+      </c>
+      <c r="D856" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E856" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F854" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G854" s="58">
-        <v>0</v>
-      </c>
-      <c r="H854" s="58">
-        <v>0</v>
-      </c>
-      <c r="I854" s="58">
-        <v>0</v>
-      </c>
-      <c r="J854" s="58">
-        <v>0</v>
-      </c>
-      <c r="K854" s="58">
-        <v>0</v>
-      </c>
-      <c r="L854" s="58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="855" spans="1:12">
-      <c r="A855" s="11" t="s">
+      <c r="F856" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G856" s="58"/>
+      <c r="H856" s="58"/>
+      <c r="I856" s="58"/>
+      <c r="J856" s="58"/>
+      <c r="K856" s="58"/>
+      <c r="L856" s="58"/>
+    </row>
+    <row r="857" spans="1:12">
+      <c r="A857" s="59" t="s">
         <v>682</v>
       </c>
-      <c r="B855" s="63" t="s">
-        <v>688</v>
-      </c>
-      <c r="C855" s="69" t="s">
-        <v>689</v>
-      </c>
-      <c r="D855" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E855" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F855" s="14" t="s">
+      <c r="B857" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="C857" s="60" t="s">
+        <v>695</v>
+      </c>
+      <c r="D857" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E857" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F857" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G855" s="65">
-        <v>0</v>
-      </c>
-      <c r="H855" s="65">
-        <v>0</v>
-      </c>
-      <c r="I855" s="65">
-        <v>0</v>
-      </c>
-      <c r="J855" s="65">
-        <v>0</v>
-      </c>
-      <c r="K855" s="65">
-        <v>0</v>
-      </c>
-      <c r="L855" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="856" spans="1:12">
-      <c r="A856" s="11" t="s">
+      <c r="G857" s="58">
+        <v>0</v>
+      </c>
+      <c r="H857" s="58">
+        <v>0</v>
+      </c>
+      <c r="I857" s="58">
+        <v>0</v>
+      </c>
+      <c r="J857" s="58">
+        <v>0</v>
+      </c>
+      <c r="K857" s="58">
+        <v>0</v>
+      </c>
+      <c r="L857" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858" spans="1:12">
+      <c r="A858" s="61" t="s">
         <v>682</v>
       </c>
-      <c r="B856" s="11" t="s">
-        <v>852</v>
-      </c>
-      <c r="C856" s="64" t="s">
-        <v>853</v>
-      </c>
-      <c r="D856" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E856" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F856" s="14" t="s">
-        <v>766</v>
-      </c>
-      <c r="G856" s="65">
-        <v>0</v>
-      </c>
-      <c r="H856" s="65">
-        <v>0</v>
-      </c>
-      <c r="I856" s="65">
-        <v>0</v>
-      </c>
-      <c r="J856" s="65">
-        <v>0</v>
-      </c>
-      <c r="K856" s="65">
-        <v>0</v>
-      </c>
-      <c r="L856" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="857" spans="1:12">
-      <c r="A857" s="11" t="s">
+      <c r="B858" s="61" t="s">
+        <v>696</v>
+      </c>
+      <c r="C858" s="62" t="s">
+        <v>697</v>
+      </c>
+      <c r="D858" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E858" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F858" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G858" s="58">
+        <v>0</v>
+      </c>
+      <c r="H858" s="58">
+        <v>0</v>
+      </c>
+      <c r="I858" s="58">
+        <v>161361.94</v>
+      </c>
+      <c r="J858" s="58">
+        <v>163040.57999999999</v>
+      </c>
+      <c r="K858" s="58">
+        <v>163040.57999999999</v>
+      </c>
+      <c r="L858" s="58">
+        <v>163040.57999999999</v>
+      </c>
+    </row>
+    <row r="859" spans="1:12">
+      <c r="A859" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B857" s="63" t="s">
-        <v>755</v>
-      </c>
-      <c r="C857" s="69" t="s">
-        <v>756</v>
-      </c>
-      <c r="D857" s="14" t="s">
+      <c r="B859" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C859" s="24" t="s">
+        <v>758</v>
+      </c>
+      <c r="D859" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="E857" s="14" t="s">
+      <c r="E859" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F857" s="14" t="s">
+      <c r="F859" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="G857" s="58">
-        <v>0</v>
-      </c>
-      <c r="H857" s="58">
-        <v>0</v>
-      </c>
-      <c r="I857" s="58">
-        <v>0</v>
-      </c>
-      <c r="J857" s="58">
-        <v>0</v>
-      </c>
-      <c r="K857" s="58">
-        <v>0</v>
-      </c>
-      <c r="L857" s="58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="858" spans="1:12">
-      <c r="A858" s="11" t="s">
-        <v>682</v>
-      </c>
-      <c r="B858" s="63" t="s">
-        <v>854</v>
-      </c>
-      <c r="C858" s="69" t="s">
-        <v>855</v>
-      </c>
-      <c r="D858" s="14" t="s">
-        <v>761</v>
-      </c>
-      <c r="E858" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F858" s="14" t="s">
-        <v>762</v>
-      </c>
-      <c r="G858" s="65">
-        <v>0</v>
-      </c>
-      <c r="H858" s="65">
-        <v>0</v>
-      </c>
-      <c r="I858" s="65">
-        <v>0</v>
-      </c>
-      <c r="J858" s="65">
-        <v>0</v>
-      </c>
-      <c r="K858" s="65">
-        <v>0</v>
-      </c>
-      <c r="L858" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="859" spans="1:12">
-      <c r="A859" s="59" t="s">
-        <v>682</v>
-      </c>
-      <c r="B859" s="61" t="s">
-        <v>142</v>
-      </c>
-      <c r="C859" s="60" t="s">
-        <v>690</v>
-      </c>
-      <c r="D859" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E859" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F859" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G859" s="58"/>
-      <c r="H859" s="58"/>
-      <c r="I859" s="58"/>
-      <c r="J859" s="58"/>
-      <c r="K859" s="58"/>
-      <c r="L859" s="58"/>
+      <c r="G859" s="65">
+        <v>0</v>
+      </c>
+      <c r="H859" s="65">
+        <v>0</v>
+      </c>
+      <c r="I859" s="65">
+        <v>0</v>
+      </c>
+      <c r="J859" s="65">
+        <v>0</v>
+      </c>
+      <c r="K859" s="65">
+        <v>0</v>
+      </c>
+      <c r="L859" s="65">
+        <v>0</v>
+      </c>
     </row>
     <row r="860" spans="1:12">
       <c r="A860" s="11" t="s">
         <v>682</v>
       </c>
       <c r="B860" s="63" t="s">
-        <v>555</v>
-      </c>
-      <c r="C860" s="24" t="s">
-        <v>691</v>
+        <v>759</v>
+      </c>
+      <c r="C860" s="5" t="s">
+        <v>760</v>
       </c>
       <c r="D860" s="14" t="s">
-        <v>19</v>
+        <v>752</v>
       </c>
       <c r="E860" s="14" t="s">
-        <v>13</v>
+        <v>129</v>
       </c>
       <c r="F860" s="14" t="s">
+        <v>753</v>
+      </c>
+      <c r="G860" s="65">
+        <v>0</v>
+      </c>
+      <c r="H860" s="65">
+        <v>0</v>
+      </c>
+      <c r="I860" s="65">
+        <v>0</v>
+      </c>
+      <c r="J860" s="65">
+        <v>0</v>
+      </c>
+      <c r="K860" s="65">
+        <v>0</v>
+      </c>
+      <c r="L860" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861" spans="1:12">
+      <c r="A861" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="B861" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="C861" s="70" t="s">
+        <v>699</v>
+      </c>
+      <c r="D861" s="14" t="s">
+        <v>749</v>
+      </c>
+      <c r="E861" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F861" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G861" s="65">
+        <v>116648.98</v>
+      </c>
+      <c r="H861" s="65">
+        <v>118474.12</v>
+      </c>
+      <c r="I861" s="65">
+        <v>118915.05</v>
+      </c>
+      <c r="J861" s="65">
+        <v>120933.46</v>
+      </c>
+      <c r="K861" s="65">
+        <v>120933.46</v>
+      </c>
+      <c r="L861" s="65">
+        <v>120933.46</v>
+      </c>
+    </row>
+    <row r="862" spans="1:12">
+      <c r="A862" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="B862" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C862" s="70" t="s">
+        <v>701</v>
+      </c>
+      <c r="D862" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E862" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F862" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G860" s="65">
-        <v>142799.35</v>
-      </c>
-      <c r="H860" s="65">
-        <v>200631.22</v>
-      </c>
-      <c r="I860" s="65">
-        <v>260124.32</v>
-      </c>
-      <c r="J860" s="65">
-        <v>313433.53000000003</v>
-      </c>
-      <c r="K860" s="65">
-        <v>313433.53000000003</v>
-      </c>
-      <c r="L860" s="65">
-        <v>313433.53000000003</v>
-      </c>
-    </row>
-    <row r="861" spans="1:12">
-      <c r="A861" s="34" t="s">
+      <c r="G862" s="65">
+        <v>0</v>
+      </c>
+      <c r="H862" s="65">
+        <v>0</v>
+      </c>
+      <c r="I862" s="65">
+        <v>0</v>
+      </c>
+      <c r="J862" s="65">
+        <v>0</v>
+      </c>
+      <c r="K862" s="65">
+        <v>0</v>
+      </c>
+      <c r="L862" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863" spans="1:12">
+      <c r="A863" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B861" s="61" t="s">
-        <v>180</v>
-      </c>
-      <c r="C861" s="60" t="s">
-        <v>692</v>
-      </c>
-      <c r="D861" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E861" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F861" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="G861" s="58">
-        <v>0</v>
-      </c>
-      <c r="H861" s="58">
-        <v>0</v>
-      </c>
-      <c r="I861" s="58">
-        <v>17721.21</v>
-      </c>
-      <c r="J861" s="58">
-        <v>17737.8</v>
-      </c>
-      <c r="K861" s="58">
-        <v>17737.8</v>
-      </c>
-      <c r="L861" s="58">
-        <v>17737.8</v>
-      </c>
-    </row>
-    <row r="862" spans="1:12">
-      <c r="A862" s="59" t="s">
+      <c r="B863" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C863" s="70" t="s">
+        <v>703</v>
+      </c>
+      <c r="D863" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E863" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F863" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G863" s="65">
+        <v>16134.05</v>
+      </c>
+      <c r="H863" s="65">
+        <v>16067.17</v>
+      </c>
+      <c r="I863" s="65">
+        <v>21047.88</v>
+      </c>
+      <c r="J863" s="65">
+        <v>0</v>
+      </c>
+      <c r="K863" s="65">
+        <v>0</v>
+      </c>
+      <c r="L863" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864" spans="1:12">
+      <c r="A864" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B862" s="59" t="s">
-        <v>693</v>
-      </c>
-      <c r="C862" s="60" t="s">
-        <v>694</v>
-      </c>
-      <c r="D862" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E862" s="14" t="s">
+      <c r="B864" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C864" s="70" t="s">
+        <v>704</v>
+      </c>
+      <c r="D864" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E864" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F862" s="32" t="s">
+      <c r="F864" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G862" s="58"/>
-      <c r="H862" s="58"/>
-      <c r="I862" s="58"/>
-      <c r="J862" s="58"/>
-      <c r="K862" s="58"/>
-      <c r="L862" s="58"/>
-    </row>
-    <row r="863" spans="1:12">
-      <c r="A863" s="59" t="s">
-        <v>682</v>
-      </c>
-      <c r="B863" s="59" t="s">
-        <v>184</v>
-      </c>
-      <c r="C863" s="60" t="s">
-        <v>695</v>
-      </c>
-      <c r="D863" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E863" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F863" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="G863" s="58">
-        <v>0</v>
-      </c>
-      <c r="H863" s="58">
-        <v>0</v>
-      </c>
-      <c r="I863" s="58">
-        <v>0</v>
-      </c>
-      <c r="J863" s="58">
-        <v>0</v>
-      </c>
-      <c r="K863" s="58">
-        <v>0</v>
-      </c>
-      <c r="L863" s="58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="864" spans="1:12">
-      <c r="A864" s="61" t="s">
-        <v>682</v>
-      </c>
-      <c r="B864" s="61" t="s">
-        <v>696</v>
-      </c>
-      <c r="C864" s="62" t="s">
-        <v>697</v>
-      </c>
-      <c r="D864" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E864" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F864" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="G864" s="58">
-        <v>0</v>
-      </c>
-      <c r="H864" s="58">
-        <v>0</v>
-      </c>
-      <c r="I864" s="58">
-        <v>161361.94</v>
-      </c>
-      <c r="J864" s="58">
-        <v>163040.57999999999</v>
-      </c>
-      <c r="K864" s="58">
-        <v>163040.57999999999</v>
-      </c>
-      <c r="L864" s="58">
-        <v>163040.57999999999</v>
+      <c r="G864" s="65"/>
+      <c r="H864" s="65"/>
+      <c r="I864" s="65"/>
+      <c r="J864" s="65">
+        <v>9859.2000000000007</v>
+      </c>
+      <c r="K864" s="65">
+        <v>9859.2000000000007</v>
+      </c>
+      <c r="L864" s="65">
+        <v>9859.2000000000007</v>
       </c>
     </row>
     <row r="865" spans="1:12">
       <c r="A865" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B865" s="16" t="s">
-        <v>757</v>
-      </c>
-      <c r="C865" s="24" t="s">
-        <v>758</v>
+      <c r="B865" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C865" s="70" t="s">
+        <v>706</v>
       </c>
       <c r="D865" s="14" t="s">
-        <v>752</v>
+        <v>48</v>
       </c>
       <c r="E865" s="14" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="F865" s="14" t="s">
-        <v>753</v>
-      </c>
-      <c r="G865" s="65">
-        <v>0</v>
-      </c>
-      <c r="H865" s="65">
-        <v>0</v>
-      </c>
-      <c r="I865" s="65">
-        <v>0</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G865" s="65"/>
+      <c r="H865" s="65"/>
+      <c r="I865" s="65"/>
       <c r="J865" s="65">
-        <v>0</v>
+        <v>9799.82</v>
       </c>
       <c r="K865" s="65">
-        <v>0</v>
+        <v>9799.82</v>
       </c>
       <c r="L865" s="65">
-        <v>0</v>
+        <v>9799.82</v>
       </c>
     </row>
     <row r="866" spans="1:12">
       <c r="A866" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="B866" s="63" t="s">
-        <v>759</v>
-      </c>
-      <c r="C866" s="5" t="s">
-        <v>760</v>
+      <c r="B866" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C866" s="70" t="s">
+        <v>708</v>
       </c>
       <c r="D866" s="14" t="s">
-        <v>752</v>
+        <v>19</v>
       </c>
       <c r="E866" s="14" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="F866" s="14" t="s">
-        <v>753</v>
+        <v>19</v>
       </c>
       <c r="G866" s="65">
-        <v>0</v>
+        <v>94014.26</v>
       </c>
       <c r="H866" s="65">
-        <v>0</v>
+        <v>93849.4</v>
       </c>
       <c r="I866" s="65">
-        <v>0</v>
+        <v>94254.86</v>
       </c>
       <c r="J866" s="65">
-        <v>0</v>
+        <v>95397.98</v>
       </c>
       <c r="K866" s="65">
-        <v>0</v>
+        <v>95397.98</v>
       </c>
       <c r="L866" s="65">
-        <v>0</v>
+        <v>95397.98</v>
       </c>
     </row>
     <row r="867" spans="1:12">
@@ -35652,48 +35616,36 @@
         <v>682</v>
       </c>
       <c r="B867" s="3" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="C867" s="70" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="D867" s="14" t="s">
-        <v>749</v>
+        <v>19</v>
       </c>
       <c r="E867" s="14" t="s">
         <v>20</v>
       </c>
       <c r="F867" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G867" s="65">
-        <v>116648.98</v>
-      </c>
-      <c r="H867" s="65">
-        <v>118474.12</v>
-      </c>
-      <c r="I867" s="65">
-        <v>118915.05</v>
-      </c>
-      <c r="J867" s="65">
-        <v>120933.46</v>
-      </c>
-      <c r="K867" s="65">
-        <v>120933.46</v>
-      </c>
-      <c r="L867" s="65">
-        <v>120933.46</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G867" s="65"/>
+      <c r="H867" s="65"/>
+      <c r="I867" s="65"/>
+      <c r="J867" s="65"/>
+      <c r="K867" s="65"/>
+      <c r="L867" s="65"/>
     </row>
     <row r="868" spans="1:12">
       <c r="A868" s="11" t="s">
         <v>682</v>
       </c>
       <c r="B868" s="3" t="s">
-        <v>700</v>
+        <v>775</v>
       </c>
       <c r="C868" s="70" t="s">
-        <v>701</v>
+        <v>848</v>
       </c>
       <c r="D868" s="14" t="s">
         <v>19</v>
@@ -35702,7 +35654,7 @@
         <v>13</v>
       </c>
       <c r="F868" s="14" t="s">
-        <v>34</v>
+        <v>766</v>
       </c>
       <c r="G868" s="65">
         <v>0</v>
@@ -35728,28 +35680,28 @@
         <v>682</v>
       </c>
       <c r="B869" s="3" t="s">
-        <v>702</v>
+        <v>778</v>
       </c>
       <c r="C869" s="70" t="s">
-        <v>703</v>
+        <v>849</v>
       </c>
       <c r="D869" s="14" t="s">
-        <v>19</v>
+        <v>761</v>
       </c>
       <c r="E869" s="14" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="F869" s="14" t="s">
-        <v>130</v>
+        <v>762</v>
       </c>
       <c r="G869" s="65">
-        <v>16134.05</v>
+        <v>0</v>
       </c>
       <c r="H869" s="65">
-        <v>16067.17</v>
+        <v>0</v>
       </c>
       <c r="I869" s="65">
-        <v>21047.88</v>
+        <v>0</v>
       </c>
       <c r="J869" s="65">
         <v>0</v>
@@ -35766,31 +35718,37 @@
         <v>682</v>
       </c>
       <c r="B870" s="3" t="s">
-        <v>309</v>
+        <v>850</v>
       </c>
       <c r="C870" s="70" t="s">
-        <v>704</v>
+        <v>851</v>
       </c>
       <c r="D870" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E870" s="14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F870" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G870" s="65"/>
-      <c r="H870" s="65"/>
-      <c r="I870" s="65"/>
+        <v>766</v>
+      </c>
+      <c r="G870" s="65">
+        <v>0</v>
+      </c>
+      <c r="H870" s="65">
+        <v>0</v>
+      </c>
+      <c r="I870" s="65">
+        <v>0</v>
+      </c>
       <c r="J870" s="65">
-        <v>9859.2000000000007</v>
+        <v>0</v>
       </c>
       <c r="K870" s="65">
-        <v>9859.2000000000007</v>
+        <v>0</v>
       </c>
       <c r="L870" s="65">
-        <v>9859.2000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="871" spans="1:12">
@@ -35798,31 +35756,37 @@
         <v>682</v>
       </c>
       <c r="B871" s="3" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C871" s="70" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="D871" s="14" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E871" s="14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F871" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G871" s="65"/>
-      <c r="H871" s="65"/>
-      <c r="I871" s="65"/>
+        <v>34</v>
+      </c>
+      <c r="G871" s="65">
+        <v>439231.76</v>
+      </c>
+      <c r="H871" s="65">
+        <v>439525.45</v>
+      </c>
+      <c r="I871" s="65">
+        <v>549702.69999999995</v>
+      </c>
       <c r="J871" s="65">
-        <v>9799.82</v>
+        <v>551448.99</v>
       </c>
       <c r="K871" s="65">
-        <v>9799.82</v>
+        <v>551448.99</v>
       </c>
       <c r="L871" s="65">
-        <v>9799.82</v>
+        <v>551448.99</v>
       </c>
     </row>
     <row r="872" spans="1:12">
@@ -35830,10 +35794,10 @@
         <v>682</v>
       </c>
       <c r="B872" s="3" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="C872" s="70" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="D872" s="14" t="s">
         <v>19</v>
@@ -35842,25 +35806,25 @@
         <v>13</v>
       </c>
       <c r="F872" s="14" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G872" s="65">
-        <v>94014.26</v>
+        <v>299289.07</v>
       </c>
       <c r="H872" s="65">
-        <v>93849.4</v>
+        <v>301225.59000000003</v>
       </c>
       <c r="I872" s="65">
-        <v>94254.86</v>
+        <v>303430.18</v>
       </c>
       <c r="J872" s="65">
-        <v>95397.98</v>
+        <v>306139.03999999998</v>
       </c>
       <c r="K872" s="65">
-        <v>95397.98</v>
+        <v>306139.03999999998</v>
       </c>
       <c r="L872" s="65">
-        <v>95397.98</v>
+        <v>306139.03999999998</v>
       </c>
     </row>
     <row r="873" spans="1:12">
@@ -35868,36 +35832,48 @@
         <v>682</v>
       </c>
       <c r="B873" s="3" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="C873" s="70" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="D873" s="14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E873" s="14" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="F873" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G873" s="65"/>
-      <c r="H873" s="65"/>
-      <c r="I873" s="65"/>
-      <c r="J873" s="65"/>
-      <c r="K873" s="65"/>
-      <c r="L873" s="65"/>
+        <v>717</v>
+      </c>
+      <c r="G873" s="65">
+        <v>80340.39</v>
+      </c>
+      <c r="H873" s="65">
+        <v>0</v>
+      </c>
+      <c r="I873" s="65">
+        <v>0</v>
+      </c>
+      <c r="J873" s="65">
+        <v>0</v>
+      </c>
+      <c r="K873" s="65">
+        <v>0</v>
+      </c>
+      <c r="L873" s="65">
+        <v>0</v>
+      </c>
     </row>
     <row r="874" spans="1:12">
       <c r="A874" s="11" t="s">
         <v>682</v>
       </c>
       <c r="B874" s="3" t="s">
-        <v>776</v>
+        <v>852</v>
       </c>
       <c r="C874" s="70" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D874" s="14" t="s">
         <v>19</v>
@@ -35932,19 +35908,19 @@
         <v>682</v>
       </c>
       <c r="B875" s="3" t="s">
-        <v>779</v>
+        <v>496</v>
       </c>
       <c r="C875" s="70" t="s">
-        <v>857</v>
+        <v>718</v>
       </c>
       <c r="D875" s="14" t="s">
-        <v>761</v>
+        <v>19</v>
       </c>
       <c r="E875" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F875" s="14" t="s">
-        <v>762</v>
+        <v>39</v>
       </c>
       <c r="G875" s="65">
         <v>0</v>
@@ -35967,13 +35943,13 @@
     </row>
     <row r="876" spans="1:12">
       <c r="A876" s="11" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="B876" s="3" t="s">
-        <v>858</v>
+        <v>151</v>
       </c>
       <c r="C876" s="70" t="s">
-        <v>859</v>
+        <v>720</v>
       </c>
       <c r="D876" s="14" t="s">
         <v>19</v>
@@ -35982,7 +35958,7 @@
         <v>13</v>
       </c>
       <c r="F876" s="14" t="s">
-        <v>766</v>
+        <v>34</v>
       </c>
       <c r="G876" s="65">
         <v>0</v>
@@ -36005,13 +35981,13 @@
     </row>
     <row r="877" spans="1:12">
       <c r="A877" s="11" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="B877" s="3" t="s">
-        <v>711</v>
+        <v>255</v>
       </c>
       <c r="C877" s="70" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="D877" s="14" t="s">
         <v>19</v>
@@ -36023,327 +35999,183 @@
         <v>34</v>
       </c>
       <c r="G877" s="65">
-        <v>439231.76</v>
+        <v>537221.23</v>
       </c>
       <c r="H877" s="65">
-        <v>439525.45</v>
+        <v>534084.6</v>
       </c>
       <c r="I877" s="65">
-        <v>549702.69999999995</v>
+        <v>549859.68999999994</v>
       </c>
       <c r="J877" s="65">
-        <v>551448.99</v>
+        <v>557240.99</v>
       </c>
       <c r="K877" s="65">
-        <v>551448.99</v>
+        <v>557240.99</v>
       </c>
       <c r="L877" s="65">
-        <v>551448.99</v>
+        <v>557240.99</v>
       </c>
     </row>
     <row r="878" spans="1:12">
       <c r="A878" s="11" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="B878" s="3" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="C878" s="70" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="D878" s="14" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="E878" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F878" s="14" t="s">
-        <v>39</v>
+        <v>724</v>
       </c>
       <c r="G878" s="65">
-        <v>299289.07</v>
+        <v>0</v>
       </c>
       <c r="H878" s="65">
-        <v>301225.59000000003</v>
+        <v>0</v>
       </c>
       <c r="I878" s="65">
-        <v>303430.18</v>
+        <v>30010.87</v>
       </c>
       <c r="J878" s="65">
-        <v>306139.03999999998</v>
+        <v>30531.01</v>
       </c>
       <c r="K878" s="65">
-        <v>306139.03999999998</v>
+        <v>30531.01</v>
       </c>
       <c r="L878" s="65">
-        <v>306139.03999999998</v>
+        <v>30531.01</v>
       </c>
     </row>
     <row r="879" spans="1:12">
       <c r="A879" s="11" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="B879" s="3" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C879" s="70" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="D879" s="14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E879" s="14" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="F879" s="14" t="s">
-        <v>717</v>
+        <v>34</v>
       </c>
       <c r="G879" s="65">
-        <v>80340.39</v>
+        <v>0</v>
       </c>
       <c r="H879" s="65">
         <v>0</v>
       </c>
       <c r="I879" s="65">
-        <v>0</v>
+        <v>219000</v>
       </c>
       <c r="J879" s="65">
-        <v>0</v>
+        <v>219000</v>
       </c>
       <c r="K879" s="65">
-        <v>0</v>
+        <v>219000</v>
       </c>
       <c r="L879" s="65">
-        <v>0</v>
+        <v>219000</v>
       </c>
     </row>
     <row r="880" spans="1:12">
-      <c r="A880" s="11" t="s">
-        <v>682</v>
-      </c>
-      <c r="B880" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="C880" s="70" t="s">
-        <v>861</v>
-      </c>
-      <c r="D880" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E880" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F880" s="14" t="s">
-        <v>766</v>
-      </c>
-      <c r="G880" s="65">
-        <v>0</v>
-      </c>
-      <c r="H880" s="65">
-        <v>0</v>
-      </c>
-      <c r="I880" s="65">
-        <v>0</v>
-      </c>
-      <c r="J880" s="65">
-        <v>0</v>
-      </c>
-      <c r="K880" s="65">
-        <v>0</v>
-      </c>
-      <c r="L880" s="65">
-        <v>0</v>
-      </c>
+      <c r="A880" s="11"/>
+      <c r="B880" s="3"/>
+      <c r="C880" s="70"/>
+      <c r="D880" s="14"/>
+      <c r="E880" s="14"/>
+      <c r="F880" s="14"/>
+      <c r="G880" s="65"/>
+      <c r="H880" s="65"/>
+      <c r="I880" s="65"/>
+      <c r="J880" s="65"/>
+      <c r="K880" s="65"/>
+      <c r="L880" s="65"/>
     </row>
     <row r="881" spans="1:12">
-      <c r="A881" s="11" t="s">
-        <v>682</v>
-      </c>
-      <c r="B881" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="C881" s="70" t="s">
-        <v>718</v>
-      </c>
-      <c r="D881" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E881" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F881" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G881" s="65">
-        <v>0</v>
-      </c>
-      <c r="H881" s="65">
-        <v>0</v>
-      </c>
-      <c r="I881" s="65">
-        <v>0</v>
-      </c>
-      <c r="J881" s="65">
-        <v>0</v>
-      </c>
-      <c r="K881" s="65">
-        <v>0</v>
-      </c>
-      <c r="L881" s="65">
-        <v>0</v>
-      </c>
+      <c r="A881" s="11"/>
+      <c r="B881" s="3"/>
+      <c r="C881" s="70"/>
+      <c r="D881" s="14"/>
+      <c r="E881" s="14"/>
+      <c r="F881" s="14"/>
+      <c r="G881" s="65"/>
+      <c r="H881" s="65"/>
+      <c r="I881" s="65"/>
+      <c r="J881" s="65"/>
+      <c r="K881" s="65"/>
+      <c r="L881" s="65"/>
     </row>
     <row r="882" spans="1:12">
-      <c r="A882" s="11" t="s">
-        <v>719</v>
-      </c>
-      <c r="B882" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C882" s="70" t="s">
-        <v>720</v>
-      </c>
-      <c r="D882" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E882" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F882" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G882" s="65">
-        <v>0</v>
-      </c>
-      <c r="H882" s="65">
-        <v>0</v>
-      </c>
-      <c r="I882" s="65">
-        <v>0</v>
-      </c>
-      <c r="J882" s="65">
-        <v>0</v>
-      </c>
-      <c r="K882" s="65">
-        <v>0</v>
-      </c>
-      <c r="L882" s="65">
-        <v>0</v>
-      </c>
+      <c r="A882" s="11"/>
+      <c r="B882" s="3"/>
+      <c r="C882" s="70"/>
+      <c r="D882" s="14"/>
+      <c r="E882" s="14"/>
+      <c r="F882" s="14"/>
+      <c r="G882" s="65"/>
+      <c r="H882" s="65"/>
+      <c r="I882" s="65"/>
+      <c r="J882" s="65"/>
+      <c r="K882" s="65"/>
+      <c r="L882" s="65"/>
     </row>
     <row r="883" spans="1:12">
-      <c r="A883" s="11" t="s">
-        <v>719</v>
-      </c>
-      <c r="B883" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C883" s="70" t="s">
-        <v>721</v>
-      </c>
-      <c r="D883" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E883" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F883" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G883" s="65">
-        <v>537221.23</v>
-      </c>
-      <c r="H883" s="65">
-        <v>534084.6</v>
-      </c>
-      <c r="I883" s="65">
-        <v>549859.68999999994</v>
-      </c>
-      <c r="J883" s="65">
-        <v>557240.99</v>
-      </c>
-      <c r="K883" s="65">
-        <v>557240.99</v>
-      </c>
-      <c r="L883" s="65">
-        <v>557240.99</v>
-      </c>
+      <c r="A883" s="11"/>
+      <c r="B883" s="3"/>
+      <c r="C883" s="70"/>
+      <c r="D883" s="14"/>
+      <c r="E883" s="14"/>
+      <c r="F883" s="14"/>
+      <c r="G883" s="65"/>
+      <c r="H883" s="65"/>
+      <c r="I883" s="65"/>
+      <c r="J883" s="65"/>
+      <c r="K883" s="65"/>
+      <c r="L883" s="65"/>
     </row>
     <row r="884" spans="1:12">
-      <c r="A884" s="11" t="s">
-        <v>719</v>
-      </c>
-      <c r="B884" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="C884" s="70" t="s">
-        <v>723</v>
-      </c>
-      <c r="D884" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="E884" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F884" s="14" t="s">
-        <v>724</v>
-      </c>
-      <c r="G884" s="65">
-        <v>0</v>
-      </c>
-      <c r="H884" s="65">
-        <v>0</v>
-      </c>
-      <c r="I884" s="65">
-        <v>30010.87</v>
-      </c>
-      <c r="J884" s="65">
-        <v>30531.01</v>
-      </c>
-      <c r="K884" s="65">
-        <v>30531.01</v>
-      </c>
-      <c r="L884" s="65">
-        <v>30531.01</v>
-      </c>
+      <c r="A884" s="11"/>
+      <c r="B884" s="3"/>
+      <c r="C884" s="70"/>
+      <c r="D884" s="14"/>
+      <c r="E884" s="14"/>
+      <c r="F884" s="14"/>
+      <c r="G884" s="65"/>
+      <c r="H884" s="65"/>
+      <c r="I884" s="65"/>
+      <c r="J884" s="65"/>
+      <c r="K884" s="65"/>
+      <c r="L884" s="65"/>
     </row>
     <row r="885" spans="1:12">
-      <c r="A885" s="11" t="s">
-        <v>719</v>
-      </c>
-      <c r="B885" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="C885" s="70" t="s">
-        <v>725</v>
-      </c>
-      <c r="D885" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E885" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F885" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G885" s="65">
-        <v>0</v>
-      </c>
-      <c r="H885" s="65">
-        <v>0</v>
-      </c>
-      <c r="I885" s="65">
-        <v>219000</v>
-      </c>
-      <c r="J885" s="65">
-        <v>219000</v>
-      </c>
-      <c r="K885" s="65">
-        <v>219000</v>
-      </c>
-      <c r="L885" s="65">
-        <v>219000</v>
-      </c>
+      <c r="A885" s="11"/>
+      <c r="B885" s="3"/>
+      <c r="C885" s="70"/>
+      <c r="D885" s="14"/>
+      <c r="E885" s="14"/>
+      <c r="F885" s="14"/>
+      <c r="G885" s="65"/>
+      <c r="H885" s="65"/>
+      <c r="I885" s="65"/>
+      <c r="J885" s="65"/>
+      <c r="K885" s="65"/>
+      <c r="L885" s="65"/>
     </row>
     <row r="886" spans="1:12">
       <c r="A886" s="11"/>
@@ -36415,93 +36247,9 @@
       <c r="K890" s="65"/>
       <c r="L890" s="65"/>
     </row>
-    <row r="891" spans="1:12">
-      <c r="A891" s="11"/>
-      <c r="B891" s="3"/>
-      <c r="C891" s="70"/>
-      <c r="D891" s="14"/>
-      <c r="E891" s="14"/>
-      <c r="F891" s="14"/>
-      <c r="G891" s="65"/>
-      <c r="H891" s="65"/>
-      <c r="I891" s="65"/>
-      <c r="J891" s="65"/>
-      <c r="K891" s="65"/>
-      <c r="L891" s="65"/>
-    </row>
-    <row r="892" spans="1:12">
-      <c r="A892" s="11"/>
-      <c r="B892" s="3"/>
-      <c r="C892" s="70"/>
-      <c r="D892" s="14"/>
-      <c r="E892" s="14"/>
-      <c r="F892" s="14"/>
-      <c r="G892" s="65"/>
-      <c r="H892" s="65"/>
-      <c r="I892" s="65"/>
-      <c r="J892" s="65"/>
-      <c r="K892" s="65"/>
-      <c r="L892" s="65"/>
-    </row>
-    <row r="893" spans="1:12">
-      <c r="A893" s="11"/>
-      <c r="B893" s="3"/>
-      <c r="C893" s="70"/>
-      <c r="D893" s="14"/>
-      <c r="E893" s="14"/>
-      <c r="F893" s="14"/>
-      <c r="G893" s="65"/>
-      <c r="H893" s="65"/>
-      <c r="I893" s="65"/>
-      <c r="J893" s="65"/>
-      <c r="K893" s="65"/>
-      <c r="L893" s="65"/>
-    </row>
-    <row r="894" spans="1:12">
-      <c r="A894" s="11"/>
-      <c r="B894" s="3"/>
-      <c r="C894" s="70"/>
-      <c r="D894" s="14"/>
-      <c r="E894" s="14"/>
-      <c r="F894" s="14"/>
-      <c r="G894" s="65"/>
-      <c r="H894" s="65"/>
-      <c r="I894" s="65"/>
-      <c r="J894" s="65"/>
-      <c r="K894" s="65"/>
-      <c r="L894" s="65"/>
-    </row>
-    <row r="895" spans="1:12">
-      <c r="A895" s="11"/>
-      <c r="B895" s="3"/>
-      <c r="C895" s="70"/>
-      <c r="D895" s="14"/>
-      <c r="E895" s="14"/>
-      <c r="F895" s="14"/>
-      <c r="G895" s="65"/>
-      <c r="H895" s="65"/>
-      <c r="I895" s="65"/>
-      <c r="J895" s="65"/>
-      <c r="K895" s="65"/>
-      <c r="L895" s="65"/>
-    </row>
-    <row r="896" spans="1:12">
-      <c r="A896" s="11"/>
-      <c r="B896" s="3"/>
-      <c r="C896" s="70"/>
-      <c r="D896" s="14"/>
-      <c r="E896" s="14"/>
-      <c r="F896" s="14"/>
-      <c r="G896" s="65"/>
-      <c r="H896" s="65"/>
-      <c r="I896" s="65"/>
-      <c r="J896" s="65"/>
-      <c r="K896" s="65"/>
-      <c r="L896" s="65"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K991" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}"/>
-  <conditionalFormatting sqref="E817:E896 E2:E744">
+  <autoFilter ref="A1:K985" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}"/>
+  <conditionalFormatting sqref="E811:E890 E2:E744">
     <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"Conquest"</formula>
     </cfRule>
@@ -36510,40 +36258,40 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E865:E868" xr:uid="{72EDC058-3E3C-49E1-936D-9932A64D9F7A}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E859:E862" xr:uid="{72EDC058-3E3C-49E1-936D-9932A64D9F7A}">
       <formula1>"DF,SP,GO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D865:D868" xr:uid="{63162FC0-551C-41B4-9FF1-4FB808C0BB8F}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D859:D862" xr:uid="{63162FC0-551C-41B4-9FF1-4FB808C0BB8F}">
       <formula1>"Bluemetrix,Vcinvest,Nexco"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D843 D652:D654 D656:D662 D664:D667 D669:D672 D674:D677 D679:D685 D687:D689 D699:D703 D705:D707 D709:D716 D718:D719 D721:D727 D729:D733 D734:D736 D738:D744 D691:D697" xr:uid="{6A5D231E-B566-4115-9576-FADE5EAE7812}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D837 D652:D654 D656:D662 D664:D667 D669:D672 D674:D677 D679:D685 D687:D689 D699:D703 D705:D707 D709:D716 D718:D719 D721:D727 D729:D733 D734:D736 D738:D744 D691:D697" xr:uid="{6A5D231E-B566-4115-9576-FADE5EAE7812}">
       <formula1>"Bluemetrix,Voga,Conquest,VcInvest,MI Smart,Altum,Poupinvista,Solution For Life,Miura,Expert"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E843 E2:E744" xr:uid="{F39B2570-ABED-44A4-8455-549202B9E600}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E837 E2:E744" xr:uid="{F39B2570-ABED-44A4-8455-549202B9E600}">
       <formula1>"DF,GO,SUL,SP,RJ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D846:D853 D855:D864" xr:uid="{F71C9748-C47B-4272-B33B-489DA77C73B5}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D840:D847 D849:D858" xr:uid="{F71C9748-C47B-4272-B33B-489DA77C73B5}">
       <formula1>"Bluemetrix,Vcinvest,Voga,Bullside,Bluemetrix (MI),Expert"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E844:E864" xr:uid="{628CE6A5-8E94-4F22-86A1-9AC855CDDE39}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E838:E858" xr:uid="{628CE6A5-8E94-4F22-86A1-9AC855CDDE39}">
       <formula1>"DF,SP,GO,SUL,RJ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D831:D842" xr:uid="{EB4BF0E4-97E6-4475-B2F0-FCBC6C505140}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D825:D836" xr:uid="{EB4BF0E4-97E6-4475-B2F0-FCBC6C505140}">
       <formula1>"Bluemetrix,Voga,Conquest,MI Smart"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D817:D830" xr:uid="{1AC7FE93-2511-4B37-AF10-3CC38784E0E9}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D811:D824" xr:uid="{1AC7FE93-2511-4B37-AF10-3CC38784E0E9}">
       <formula1>"Bluemetrix,Voga,Conquest"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E817:E842" xr:uid="{BD5F991D-A742-4459-A90C-B34FC62754E6}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E811:E836" xr:uid="{BD5F991D-A742-4459-A90C-B34FC62754E6}">
       <formula1>"DF,GO,SUL,SP"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D655 D663 D668 D673 D678 D686 D690 D698 D704 D708 D717 D720 D728 D737 D844:D845 D854 D2:D651" xr:uid="{AE28F127-2FA0-493C-9E38-854F40AA73EF}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D655 D663 D668 D673 D678 D686 D690 D698 D704 D708 D717 D720 D728 D737 D838:D839 D848 D2:D651" xr:uid="{AE28F127-2FA0-493C-9E38-854F40AA73EF}">
       <formula1>"Bluemetrix,Voga,Conquest,VcInvest,Miura,Altum,Poupinvista,Solution For Life,MI Smart,Expert,OP Club,Nexco"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E745:E816" xr:uid="{50119A26-3145-48AB-AFC5-2644D42930EF}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E745:E810" xr:uid="{50119A26-3145-48AB-AFC5-2644D42930EF}">
       <formula1>"DF,SUL,GO,BH"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D745:D816" xr:uid="{CCC37560-827A-47EF-971E-E36215518929}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D745:D810" xr:uid="{CCC37560-827A-47EF-971E-E36215518929}">
       <formula1>"Bluemetrix,Blanchor,Conquest,Voga,Matrice,Miura"</formula1>
     </dataValidation>
   </dataValidations>

--- a/dados/Campanha Captação.xlsx
+++ b/dados/Campanha Captação.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BRUNO.SILVA\Downloads\App campanha\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216263ED-B368-4A0A-A687-08CAD454B7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76F5173-7478-49E8-B1C2-F6F1D16E3463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28875" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{65BC80B7-CA5D-453E-A132-5DB34208399A}"/>
+    <workbookView xWindow="75" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{65BC80B7-CA5D-453E-A132-5DB34208399A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$K$985</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$K$879</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3433,7 +3433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}">
-  <dimension ref="A1:L890"/>
+  <dimension ref="A1:L879"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -34817,10 +34817,10 @@
         <v>65726.7</v>
       </c>
       <c r="K844" s="58">
-        <v>65726.7</v>
+        <v>67206.37</v>
       </c>
       <c r="L844" s="58">
-        <v>65726.7</v>
+        <v>67206.37</v>
       </c>
     </row>
     <row r="845" spans="1:12">
@@ -34893,10 +34893,10 @@
         <v>125168.34</v>
       </c>
       <c r="K846" s="58">
-        <v>125168.34</v>
+        <v>131942.32</v>
       </c>
       <c r="L846" s="58">
-        <v>125168.34</v>
+        <v>131942.32</v>
       </c>
     </row>
     <row r="847" spans="1:12">
@@ -34922,8 +34922,12 @@
       <c r="H847" s="58"/>
       <c r="I847" s="65"/>
       <c r="J847" s="65"/>
-      <c r="K847" s="65"/>
-      <c r="L847" s="65"/>
+      <c r="K847" s="65">
+        <v>1000</v>
+      </c>
+      <c r="L847" s="65">
+        <v>1000</v>
+      </c>
     </row>
     <row r="848" spans="1:12">
       <c r="A848" s="59" t="s">
@@ -35138,8 +35142,12 @@
       <c r="H853" s="58"/>
       <c r="I853" s="58"/>
       <c r="J853" s="58"/>
-      <c r="K853" s="58"/>
-      <c r="L853" s="58"/>
+      <c r="K853" s="58">
+        <v>0</v>
+      </c>
+      <c r="L853" s="58">
+        <v>0</v>
+      </c>
     </row>
     <row r="854" spans="1:12">
       <c r="A854" s="11" t="s">
@@ -35173,10 +35181,10 @@
         <v>313433.53000000003</v>
       </c>
       <c r="K854" s="65">
-        <v>313433.53000000003</v>
+        <v>315102</v>
       </c>
       <c r="L854" s="65">
-        <v>313433.53000000003</v>
+        <v>315102</v>
       </c>
     </row>
     <row r="855" spans="1:12">
@@ -35211,10 +35219,10 @@
         <v>17737.8</v>
       </c>
       <c r="K855" s="58">
-        <v>17737.8</v>
+        <v>17924.73</v>
       </c>
       <c r="L855" s="58">
-        <v>17737.8</v>
+        <v>17924.73</v>
       </c>
     </row>
     <row r="856" spans="1:12">
@@ -35240,8 +35248,12 @@
       <c r="H856" s="58"/>
       <c r="I856" s="58"/>
       <c r="J856" s="58"/>
-      <c r="K856" s="58"/>
-      <c r="L856" s="58"/>
+      <c r="K856" s="58">
+        <v>0</v>
+      </c>
+      <c r="L856" s="58">
+        <v>0</v>
+      </c>
     </row>
     <row r="857" spans="1:12">
       <c r="A857" s="59" t="s">
@@ -35313,10 +35325,10 @@
         <v>163040.57999999999</v>
       </c>
       <c r="K858" s="58">
-        <v>163040.57999999999</v>
+        <v>162864.82999999999</v>
       </c>
       <c r="L858" s="58">
-        <v>163040.57999999999</v>
+        <v>162864.82999999999</v>
       </c>
     </row>
     <row r="859" spans="1:12">
@@ -35427,10 +35439,10 @@
         <v>120933.46</v>
       </c>
       <c r="K861" s="65">
-        <v>120933.46</v>
+        <v>121791.84</v>
       </c>
       <c r="L861" s="65">
-        <v>120933.46</v>
+        <v>121791.84</v>
       </c>
     </row>
     <row r="862" spans="1:12">
@@ -35535,10 +35547,10 @@
         <v>9859.2000000000007</v>
       </c>
       <c r="K864" s="65">
-        <v>9859.2000000000007</v>
+        <v>9864.1299999999992</v>
       </c>
       <c r="L864" s="65">
-        <v>9859.2000000000007</v>
+        <v>9864.1299999999992</v>
       </c>
     </row>
     <row r="865" spans="1:12">
@@ -35567,10 +35579,10 @@
         <v>9799.82</v>
       </c>
       <c r="K865" s="65">
-        <v>9799.82</v>
+        <v>9804.7900000000009</v>
       </c>
       <c r="L865" s="65">
-        <v>9799.82</v>
+        <v>9804.7900000000009</v>
       </c>
     </row>
     <row r="866" spans="1:12">
@@ -35605,10 +35617,10 @@
         <v>95397.98</v>
       </c>
       <c r="K866" s="65">
-        <v>95397.98</v>
+        <v>95642.02</v>
       </c>
       <c r="L866" s="65">
-        <v>95397.98</v>
+        <v>95642.02</v>
       </c>
     </row>
     <row r="867" spans="1:12">
@@ -35634,8 +35646,12 @@
       <c r="H867" s="65"/>
       <c r="I867" s="65"/>
       <c r="J867" s="65"/>
-      <c r="K867" s="65"/>
-      <c r="L867" s="65"/>
+      <c r="K867" s="65">
+        <v>0</v>
+      </c>
+      <c r="L867" s="65">
+        <v>0</v>
+      </c>
     </row>
     <row r="868" spans="1:12">
       <c r="A868" s="11" t="s">
@@ -35783,10 +35799,10 @@
         <v>551448.99</v>
       </c>
       <c r="K871" s="65">
-        <v>551448.99</v>
+        <v>551673.94999999995</v>
       </c>
       <c r="L871" s="65">
-        <v>551448.99</v>
+        <v>551673.94999999995</v>
       </c>
     </row>
     <row r="872" spans="1:12">
@@ -35821,10 +35837,10 @@
         <v>306139.03999999998</v>
       </c>
       <c r="K872" s="65">
-        <v>306139.03999999998</v>
+        <v>307847.58</v>
       </c>
       <c r="L872" s="65">
-        <v>306139.03999999998</v>
+        <v>307847.58</v>
       </c>
     </row>
     <row r="873" spans="1:12">
@@ -35859,10 +35875,10 @@
         <v>0</v>
       </c>
       <c r="K873" s="65">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="L873" s="65">
-        <v>0</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="874" spans="1:12">
@@ -36093,163 +36109,9 @@
         <v>219000</v>
       </c>
     </row>
-    <row r="880" spans="1:12">
-      <c r="A880" s="11"/>
-      <c r="B880" s="3"/>
-      <c r="C880" s="70"/>
-      <c r="D880" s="14"/>
-      <c r="E880" s="14"/>
-      <c r="F880" s="14"/>
-      <c r="G880" s="65"/>
-      <c r="H880" s="65"/>
-      <c r="I880" s="65"/>
-      <c r="J880" s="65"/>
-      <c r="K880" s="65"/>
-      <c r="L880" s="65"/>
-    </row>
-    <row r="881" spans="1:12">
-      <c r="A881" s="11"/>
-      <c r="B881" s="3"/>
-      <c r="C881" s="70"/>
-      <c r="D881" s="14"/>
-      <c r="E881" s="14"/>
-      <c r="F881" s="14"/>
-      <c r="G881" s="65"/>
-      <c r="H881" s="65"/>
-      <c r="I881" s="65"/>
-      <c r="J881" s="65"/>
-      <c r="K881" s="65"/>
-      <c r="L881" s="65"/>
-    </row>
-    <row r="882" spans="1:12">
-      <c r="A882" s="11"/>
-      <c r="B882" s="3"/>
-      <c r="C882" s="70"/>
-      <c r="D882" s="14"/>
-      <c r="E882" s="14"/>
-      <c r="F882" s="14"/>
-      <c r="G882" s="65"/>
-      <c r="H882" s="65"/>
-      <c r="I882" s="65"/>
-      <c r="J882" s="65"/>
-      <c r="K882" s="65"/>
-      <c r="L882" s="65"/>
-    </row>
-    <row r="883" spans="1:12">
-      <c r="A883" s="11"/>
-      <c r="B883" s="3"/>
-      <c r="C883" s="70"/>
-      <c r="D883" s="14"/>
-      <c r="E883" s="14"/>
-      <c r="F883" s="14"/>
-      <c r="G883" s="65"/>
-      <c r="H883" s="65"/>
-      <c r="I883" s="65"/>
-      <c r="J883" s="65"/>
-      <c r="K883" s="65"/>
-      <c r="L883" s="65"/>
-    </row>
-    <row r="884" spans="1:12">
-      <c r="A884" s="11"/>
-      <c r="B884" s="3"/>
-      <c r="C884" s="70"/>
-      <c r="D884" s="14"/>
-      <c r="E884" s="14"/>
-      <c r="F884" s="14"/>
-      <c r="G884" s="65"/>
-      <c r="H884" s="65"/>
-      <c r="I884" s="65"/>
-      <c r="J884" s="65"/>
-      <c r="K884" s="65"/>
-      <c r="L884" s="65"/>
-    </row>
-    <row r="885" spans="1:12">
-      <c r="A885" s="11"/>
-      <c r="B885" s="3"/>
-      <c r="C885" s="70"/>
-      <c r="D885" s="14"/>
-      <c r="E885" s="14"/>
-      <c r="F885" s="14"/>
-      <c r="G885" s="65"/>
-      <c r="H885" s="65"/>
-      <c r="I885" s="65"/>
-      <c r="J885" s="65"/>
-      <c r="K885" s="65"/>
-      <c r="L885" s="65"/>
-    </row>
-    <row r="886" spans="1:12">
-      <c r="A886" s="11"/>
-      <c r="B886" s="3"/>
-      <c r="C886" s="70"/>
-      <c r="D886" s="14"/>
-      <c r="E886" s="14"/>
-      <c r="F886" s="14"/>
-      <c r="G886" s="65"/>
-      <c r="H886" s="65"/>
-      <c r="I886" s="65"/>
-      <c r="J886" s="65"/>
-      <c r="K886" s="65"/>
-      <c r="L886" s="65"/>
-    </row>
-    <row r="887" spans="1:12">
-      <c r="A887" s="11"/>
-      <c r="B887" s="3"/>
-      <c r="C887" s="70"/>
-      <c r="D887" s="14"/>
-      <c r="E887" s="14"/>
-      <c r="F887" s="14"/>
-      <c r="G887" s="65"/>
-      <c r="H887" s="65"/>
-      <c r="I887" s="65"/>
-      <c r="J887" s="65"/>
-      <c r="K887" s="65"/>
-      <c r="L887" s="65"/>
-    </row>
-    <row r="888" spans="1:12">
-      <c r="A888" s="11"/>
-      <c r="B888" s="3"/>
-      <c r="C888" s="70"/>
-      <c r="D888" s="14"/>
-      <c r="E888" s="14"/>
-      <c r="F888" s="14"/>
-      <c r="G888" s="65"/>
-      <c r="H888" s="65"/>
-      <c r="I888" s="65"/>
-      <c r="J888" s="65"/>
-      <c r="K888" s="65"/>
-      <c r="L888" s="65"/>
-    </row>
-    <row r="889" spans="1:12">
-      <c r="A889" s="11"/>
-      <c r="B889" s="3"/>
-      <c r="C889" s="70"/>
-      <c r="D889" s="14"/>
-      <c r="E889" s="14"/>
-      <c r="F889" s="14"/>
-      <c r="G889" s="65"/>
-      <c r="H889" s="65"/>
-      <c r="I889" s="65"/>
-      <c r="J889" s="65"/>
-      <c r="K889" s="65"/>
-      <c r="L889" s="65"/>
-    </row>
-    <row r="890" spans="1:12">
-      <c r="A890" s="11"/>
-      <c r="B890" s="3"/>
-      <c r="C890" s="70"/>
-      <c r="D890" s="14"/>
-      <c r="E890" s="14"/>
-      <c r="F890" s="14"/>
-      <c r="G890" s="65"/>
-      <c r="H890" s="65"/>
-      <c r="I890" s="65"/>
-      <c r="J890" s="65"/>
-      <c r="K890" s="65"/>
-      <c r="L890" s="65"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K985" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}"/>
-  <conditionalFormatting sqref="E811:E890 E2:E744">
+  <autoFilter ref="A1:K879" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}"/>
+  <conditionalFormatting sqref="E2:E744 E811:E879">
     <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"Conquest"</formula>
     </cfRule>

--- a/dados/Campanha Captação.xlsx
+++ b/dados/Campanha Captação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BRUNO.SILVA\Downloads\App campanha\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084D8588-68D1-48B8-91F3-F938A9116C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D23626B-A3F6-450F-AB32-F79E193F257B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28875" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{65BC80B7-CA5D-453E-A132-5DB34208399A}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="813">
   <si>
     <t>Corretora</t>
   </si>
@@ -567,9 +567,6 @@
   </si>
   <si>
     <t>Diego Henrique Lopes Ribeiro</t>
-  </si>
-  <si>
-    <t>thiago Canabrava</t>
   </si>
   <si>
     <t>Diogo Salomão Pontes</t>
@@ -2491,8 +2488,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="165" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -2807,22 +2804,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8228,10 +8225,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -8389,7 +8386,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C6" s="5">
         <v>16322281</v>
@@ -8927,7 +8924,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C20" s="10">
         <v>5024046</v>
@@ -8966,7 +8963,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C21" s="5">
         <v>4890599</v>
@@ -9005,7 +9002,7 @@
         <v>10</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C22" s="11">
         <v>8227566</v>
@@ -9017,7 +9014,7 @@
         <v>13</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G22" s="56">
         <v>0</v>
@@ -9740,7 +9737,7 @@
         <v>10</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C41" s="19">
         <v>4384131</v>
@@ -9779,7 +9776,7 @@
         <v>10</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C42" s="5">
         <v>4514241</v>
@@ -10555,7 +10552,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C62" s="5">
         <v>4279859</v>
@@ -10567,7 +10564,7 @@
         <v>13</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G62" s="56">
         <v>0</v>
@@ -11939,7 +11936,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C98" s="5">
         <v>4360431</v>
@@ -12407,7 +12404,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C110" s="5">
         <v>4332544</v>
@@ -12873,7 +12870,7 @@
         <v>10</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C122" s="5">
         <v>2697806</v>
@@ -13380,7 +13377,7 @@
         <v>10</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C135" s="5">
         <v>5696595</v>
@@ -13392,7 +13389,7 @@
         <v>13</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G135" s="56">
         <v>0</v>
@@ -14396,7 +14393,7 @@
         <v>13</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>175</v>
+        <v>33</v>
       </c>
       <c r="G161" s="56"/>
       <c r="H161" s="56">
@@ -14421,7 +14418,7 @@
         <v>10</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C162" s="5">
         <v>4550415</v>
@@ -14460,7 +14457,7 @@
         <v>10</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C163" s="5">
         <v>8762237</v>
@@ -14499,7 +14496,7 @@
         <v>10</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C164" s="5">
         <v>4490636</v>
@@ -14538,7 +14535,7 @@
         <v>10</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C165" s="5">
         <v>4467773</v>
@@ -14577,7 +14574,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C166" s="5">
         <v>15231285</v>
@@ -14610,7 +14607,7 @@
         <v>10</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C167" s="28">
         <v>5077648</v>
@@ -14649,7 +14646,7 @@
         <v>10</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C168" s="5">
         <v>4335144</v>
@@ -14688,7 +14685,7 @@
         <v>10</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C169" s="5">
         <v>3301389</v>
@@ -14727,7 +14724,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C170" s="5">
         <v>4335251</v>
@@ -14766,7 +14763,7 @@
         <v>10</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C171" s="5">
         <v>4335031</v>
@@ -14805,7 +14802,7 @@
         <v>10</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C172" s="6">
         <v>5009026</v>
@@ -14844,7 +14841,7 @@
         <v>10</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C173" s="6">
         <v>3895497</v>
@@ -14883,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C174" s="5">
         <v>4229526</v>
@@ -14922,7 +14919,7 @@
         <v>10</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C175" s="13">
         <v>9118696</v>
@@ -14959,7 +14956,7 @@
         <v>10</v>
       </c>
       <c r="B176" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C176" s="13">
         <v>9268477</v>
@@ -14990,7 +14987,7 @@
         <v>10</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C177" s="5">
         <v>4508516</v>
@@ -15029,7 +15026,7 @@
         <v>10</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C178" s="5">
         <v>4461070</v>
@@ -15068,7 +15065,7 @@
         <v>10</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C179" s="11">
         <v>8223177</v>
@@ -15107,7 +15104,7 @@
         <v>10</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C180" s="5">
         <v>4946997</v>
@@ -15146,7 +15143,7 @@
         <v>10</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C181" s="5">
         <v>8110684</v>
@@ -15185,7 +15182,7 @@
         <v>10</v>
       </c>
       <c r="B182" s="30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C182" s="31">
         <v>5064544</v>
@@ -15224,7 +15221,7 @@
         <v>10</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C183" s="13">
         <v>8115265</v>
@@ -15263,7 +15260,7 @@
         <v>10</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C184" s="13">
         <v>5018038</v>
@@ -15302,7 +15299,7 @@
         <v>10</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C185" s="13">
         <v>8384472</v>
@@ -15341,7 +15338,7 @@
         <v>10</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C186" s="10">
         <v>8385898</v>
@@ -15353,7 +15350,7 @@
         <v>29</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G186" s="56">
         <v>0</v>
@@ -15380,7 +15377,7 @@
         <v>10</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C187" s="5">
         <v>4380749</v>
@@ -15419,7 +15416,7 @@
         <v>10</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C188" s="5">
         <v>5654122</v>
@@ -15458,7 +15455,7 @@
         <v>10</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C189" s="5">
         <v>4213943</v>
@@ -15497,7 +15494,7 @@
         <v>10</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C190" s="5">
         <v>8399947</v>
@@ -15536,7 +15533,7 @@
         <v>10</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C191" s="11">
         <v>8297098</v>
@@ -15548,7 +15545,7 @@
         <v>108</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G191" s="56">
         <v>36230.620000000003</v>
@@ -15575,7 +15572,7 @@
         <v>10</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C192" s="11">
         <v>11725850</v>
@@ -15610,7 +15607,7 @@
         <v>10</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C193" s="9">
         <v>5535788</v>
@@ -15649,7 +15646,7 @@
         <v>10</v>
       </c>
       <c r="B194" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C194" s="5">
         <v>5304669</v>
@@ -15688,7 +15685,7 @@
         <v>10</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C195" s="11">
         <v>4260002</v>
@@ -15727,7 +15724,7 @@
         <v>10</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C196" s="9">
         <v>5995120</v>
@@ -15766,7 +15763,7 @@
         <v>10</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C197" s="9">
         <v>5641874</v>
@@ -15805,7 +15802,7 @@
         <v>10</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C198" s="20">
         <v>4971783</v>
@@ -15844,7 +15841,7 @@
         <v>10</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C199" s="5">
         <v>4924605</v>
@@ -15883,7 +15880,7 @@
         <v>10</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C200" s="5">
         <v>4587320</v>
@@ -15922,7 +15919,7 @@
         <v>10</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C201" s="5">
         <v>4399832</v>
@@ -15961,7 +15958,7 @@
         <v>10</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C202" s="5">
         <v>4398253</v>
@@ -16000,7 +15997,7 @@
         <v>10</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C203" s="5">
         <v>5437764</v>
@@ -16039,7 +16036,7 @@
         <v>10</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C204" s="5">
         <v>4755083</v>
@@ -16078,7 +16075,7 @@
         <v>10</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C205" s="5">
         <v>5701765</v>
@@ -16117,7 +16114,7 @@
         <v>10</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C206" s="5">
         <v>9038731</v>
@@ -16154,7 +16151,7 @@
         <v>10</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C207" s="5">
         <v>8178151</v>
@@ -16193,7 +16190,7 @@
         <v>10</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C208" s="5">
         <v>4499920</v>
@@ -16232,7 +16229,7 @@
         <v>10</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C209" s="5">
         <v>9174932</v>
@@ -16267,7 +16264,7 @@
         <v>10</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C210" s="5">
         <v>4912314</v>
@@ -16306,7 +16303,7 @@
         <v>10</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C211" s="5">
         <v>4570632</v>
@@ -16345,7 +16342,7 @@
         <v>10</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C212" s="5">
         <v>8405339</v>
@@ -16384,7 +16381,7 @@
         <v>10</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C213" s="5">
         <v>4508159</v>
@@ -16423,7 +16420,7 @@
         <v>10</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C214" s="5">
         <v>18513002</v>
@@ -16452,7 +16449,7 @@
         <v>10</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C215" s="5">
         <v>4400640</v>
@@ -16491,7 +16488,7 @@
         <v>10</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C216" s="5">
         <v>4400969</v>
@@ -16530,7 +16527,7 @@
         <v>10</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C217" s="11">
         <v>5135532</v>
@@ -16569,7 +16566,7 @@
         <v>10</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C218" s="11">
         <v>626491</v>
@@ -16608,7 +16605,7 @@
         <v>10</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C219" s="11">
         <v>8598562</v>
@@ -16645,7 +16642,7 @@
         <v>10</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C220" s="27">
         <v>8412872</v>
@@ -16684,7 +16681,7 @@
         <v>10</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C221" s="27">
         <v>5726697</v>
@@ -16723,7 +16720,7 @@
         <v>10</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C222" s="27">
         <v>8298906</v>
@@ -16735,7 +16732,7 @@
         <v>108</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G222" s="56">
         <v>509614.89</v>
@@ -16762,7 +16759,7 @@
         <v>10</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C223" s="5">
         <v>4895776</v>
@@ -16801,7 +16798,7 @@
         <v>10</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C224" s="5">
         <v>4508504</v>
@@ -16840,7 +16837,7 @@
         <v>10</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C225" s="5">
         <v>4563237</v>
@@ -16879,7 +16876,7 @@
         <v>10</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C226" s="5">
         <v>4563252</v>
@@ -16918,7 +16915,7 @@
         <v>10</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C227" s="5">
         <v>8716830</v>
@@ -16957,7 +16954,7 @@
         <v>10</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C228" s="5">
         <v>4515548</v>
@@ -16996,7 +16993,7 @@
         <v>10</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C229" s="5">
         <v>4484207</v>
@@ -17035,7 +17032,7 @@
         <v>10</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C230" s="5">
         <v>5883672</v>
@@ -17074,7 +17071,7 @@
         <v>10</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C231" s="5">
         <v>4281300</v>
@@ -17113,7 +17110,7 @@
         <v>10</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C232" s="5">
         <v>8499705</v>
@@ -17152,7 +17149,7 @@
         <v>10</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C233" s="5">
         <v>4503381</v>
@@ -17191,7 +17188,7 @@
         <v>10</v>
       </c>
       <c r="B234" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C234" s="5">
         <v>5047946</v>
@@ -17230,19 +17227,19 @@
         <v>10</v>
       </c>
       <c r="B235" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C235" s="5">
         <v>8858739</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F235" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G235" s="56"/>
       <c r="H235" s="56"/>
@@ -17261,7 +17258,7 @@
         <v>10</v>
       </c>
       <c r="B236" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C236" s="5">
         <v>8090243</v>
@@ -17272,7 +17269,7 @@
       <c r="E236" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F236" s="10" t="s">
+      <c r="F236" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G236" s="56">
@@ -17300,7 +17297,7 @@
         <v>10</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C237" s="5">
         <v>4643880</v>
@@ -17339,7 +17336,7 @@
         <v>10</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C238" s="5">
         <v>4472386</v>
@@ -17378,7 +17375,7 @@
         <v>10</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C239" s="5">
         <v>8323468</v>
@@ -17417,7 +17414,7 @@
         <v>10</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C240" s="5">
         <v>8353477</v>
@@ -17456,7 +17453,7 @@
         <v>10</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C241" s="9">
         <v>3175155</v>
@@ -17493,7 +17490,7 @@
         <v>10</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C242" s="5">
         <v>4839302</v>
@@ -17532,7 +17529,7 @@
         <v>10</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C243" s="5">
         <v>4827315</v>
@@ -17571,7 +17568,7 @@
         <v>10</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C244" s="13">
         <v>4998717</v>
@@ -17610,7 +17607,7 @@
         <v>10</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C245" s="9">
         <v>4322719</v>
@@ -17649,7 +17646,7 @@
         <v>10</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C246" s="5">
         <v>5981575</v>
@@ -17688,7 +17685,7 @@
         <v>10</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C247" s="5">
         <v>5631648</v>
@@ -17727,7 +17724,7 @@
         <v>10</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C248" s="5">
         <v>5221565</v>
@@ -17766,7 +17763,7 @@
         <v>10</v>
       </c>
       <c r="B249" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C249" s="13">
         <v>4948033</v>
@@ -17805,7 +17802,7 @@
         <v>10</v>
       </c>
       <c r="B250" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C250" s="10">
         <v>5087681</v>
@@ -17844,7 +17841,7 @@
         <v>10</v>
       </c>
       <c r="B251" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C251" s="9">
         <v>5637820</v>
@@ -17922,7 +17919,7 @@
         <v>10</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C253" s="11">
         <v>2350362</v>
@@ -17961,7 +17958,7 @@
         <v>10</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C254" s="5">
         <v>4452790</v>
@@ -18000,7 +17997,7 @@
         <v>10</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C255" s="5">
         <v>4444605</v>
@@ -18039,7 +18036,7 @@
         <v>10</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C256" s="5">
         <v>4565146</v>
@@ -18078,7 +18075,7 @@
         <v>10</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C257" s="27">
         <v>4313254</v>
@@ -18117,7 +18114,7 @@
         <v>10</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C258" s="27">
         <v>4228090</v>
@@ -18156,7 +18153,7 @@
         <v>10</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C259" s="27">
         <v>5591536</v>
@@ -18195,7 +18192,7 @@
         <v>10</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C260" s="27">
         <v>5588581</v>
@@ -18234,7 +18231,7 @@
         <v>10</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C261" s="27">
         <v>18511501</v>
@@ -18263,7 +18260,7 @@
         <v>10</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C262" s="5">
         <v>4565108</v>
@@ -18302,7 +18299,7 @@
         <v>10</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C263" s="32">
         <v>4830355</v>
@@ -18341,7 +18338,7 @@
         <v>10</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C264" s="5">
         <v>5967015</v>
@@ -18380,7 +18377,7 @@
         <v>10</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C265" s="5">
         <v>17775289</v>
@@ -18409,7 +18406,7 @@
         <v>10</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C266" s="5">
         <v>4363250</v>
@@ -18448,7 +18445,7 @@
         <v>10</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C267" s="5">
         <v>5698866</v>
@@ -18460,7 +18457,7 @@
         <v>13</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G267" s="56">
         <v>331843.55</v>
@@ -18487,7 +18484,7 @@
         <v>10</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C268" s="5">
         <v>5709269</v>
@@ -18499,7 +18496,7 @@
         <v>13</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G268" s="56">
         <v>0</v>
@@ -18526,7 +18523,7 @@
         <v>10</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C269" s="5">
         <v>4468717</v>
@@ -18565,7 +18562,7 @@
         <v>10</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C270" s="5">
         <v>4479463</v>
@@ -18604,7 +18601,7 @@
         <v>10</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C271" s="5">
         <v>4479464</v>
@@ -18643,7 +18640,7 @@
         <v>10</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C272" s="5">
         <v>4497875</v>
@@ -18682,7 +18679,7 @@
         <v>10</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C273" s="5">
         <v>4359408</v>
@@ -18721,7 +18718,7 @@
         <v>10</v>
       </c>
       <c r="B274" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C274" s="10">
         <v>8054285</v>
@@ -18760,7 +18757,7 @@
         <v>10</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C275" s="5">
         <v>4459461</v>
@@ -18799,7 +18796,7 @@
         <v>10</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C276" s="5">
         <v>4332207</v>
@@ -18838,7 +18835,7 @@
         <v>10</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C277" s="5">
         <v>4332783</v>
@@ -18877,7 +18874,7 @@
         <v>10</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C278" s="5">
         <v>4467016</v>
@@ -18916,7 +18913,7 @@
         <v>10</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C279" s="5">
         <v>4240014</v>
@@ -18955,7 +18952,7 @@
         <v>10</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C280" s="5">
         <v>4767746</v>
@@ -18994,7 +18991,7 @@
         <v>10</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C281" s="5">
         <v>8519963</v>
@@ -19033,7 +19030,7 @@
         <v>10</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C282" s="5">
         <v>4452476</v>
@@ -19072,7 +19069,7 @@
         <v>10</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C283" s="5">
         <v>8335477</v>
@@ -19111,7 +19108,7 @@
         <v>10</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C284" s="5">
         <v>4216434</v>
@@ -19150,7 +19147,7 @@
         <v>10</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C285" s="5">
         <v>5224125</v>
@@ -19189,7 +19186,7 @@
         <v>10</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C286" s="5">
         <v>4500087</v>
@@ -19228,7 +19225,7 @@
         <v>10</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C287" s="5">
         <v>4245232</v>
@@ -19240,7 +19237,7 @@
         <v>13</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G287" s="56">
         <v>0</v>
@@ -19267,7 +19264,7 @@
         <v>10</v>
       </c>
       <c r="B288" s="24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C288" s="10">
         <v>5324981</v>
@@ -19306,7 +19303,7 @@
         <v>10</v>
       </c>
       <c r="B289" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C289" s="10">
         <v>8328831</v>
@@ -19345,7 +19342,7 @@
         <v>10</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C290" s="5">
         <v>8026930</v>
@@ -19384,7 +19381,7 @@
         <v>10</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C291" s="5">
         <v>9260320</v>
@@ -19421,7 +19418,7 @@
         <v>10</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C292" s="5">
         <v>4381415</v>
@@ -19460,7 +19457,7 @@
         <v>10</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C293" s="5">
         <v>5651698</v>
@@ -19472,7 +19469,7 @@
         <v>29</v>
       </c>
       <c r="F293" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G293" s="56">
         <v>0</v>
@@ -19499,7 +19496,7 @@
         <v>10</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C294" s="5">
         <v>5604917</v>
@@ -19538,7 +19535,7 @@
         <v>10</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C295" s="5">
         <v>4381328</v>
@@ -19577,7 +19574,7 @@
         <v>10</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C296" s="5">
         <v>4216657</v>
@@ -19616,7 +19613,7 @@
         <v>10</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C297" s="9">
         <v>5606985</v>
@@ -19655,7 +19652,7 @@
         <v>10</v>
       </c>
       <c r="B298" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C298" s="11">
         <v>9028014</v>
@@ -19694,7 +19691,7 @@
         <v>10</v>
       </c>
       <c r="B299" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C299" s="11">
         <v>9290406</v>
@@ -19729,7 +19726,7 @@
         <v>10</v>
       </c>
       <c r="B300" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C300" s="18">
         <v>5079458</v>
@@ -19768,7 +19765,7 @@
         <v>10</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C301" s="20">
         <v>5720146</v>
@@ -19807,7 +19804,7 @@
         <v>10</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C302" s="5">
         <v>5121919</v>
@@ -19846,7 +19843,7 @@
         <v>10</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C303" s="10">
         <v>5068961</v>
@@ -19885,7 +19882,7 @@
         <v>10</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C304" s="33">
         <v>5599726</v>
@@ -19924,7 +19921,7 @@
         <v>10</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C305" s="34">
         <v>8002502</v>
@@ -19963,7 +19960,7 @@
         <v>10</v>
       </c>
       <c r="B306" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C306" s="5">
         <v>4432935</v>
@@ -20002,7 +19999,7 @@
         <v>10</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C307" s="5">
         <v>8762622</v>
@@ -20041,7 +20038,7 @@
         <v>10</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C308" s="5">
         <v>4480134</v>
@@ -20080,7 +20077,7 @@
         <v>10</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C309" s="9">
         <v>5379541</v>
@@ -20119,19 +20116,19 @@
         <v>10</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C310" s="9">
         <v>8857042</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E310" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F310" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G310" s="56"/>
       <c r="H310" s="56"/>
@@ -20150,7 +20147,7 @@
         <v>10</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C311" s="5">
         <v>2687737</v>
@@ -20189,7 +20186,7 @@
         <v>10</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C312" s="5">
         <v>4453157</v>
@@ -20228,7 +20225,7 @@
         <v>10</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C313" s="5">
         <v>4332103</v>
@@ -20267,7 +20264,7 @@
         <v>10</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C314" s="5">
         <v>4332237</v>
@@ -20306,7 +20303,7 @@
         <v>10</v>
       </c>
       <c r="B315" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C315" s="18">
         <v>5079311</v>
@@ -20345,7 +20342,7 @@
         <v>10</v>
       </c>
       <c r="B316" s="16" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C316" s="18">
         <v>5861534</v>
@@ -20357,7 +20354,7 @@
         <v>13</v>
       </c>
       <c r="F316" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G316" s="56">
         <v>0</v>
@@ -20384,7 +20381,7 @@
         <v>10</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C317" s="10">
         <v>5348975</v>
@@ -20423,7 +20420,7 @@
         <v>10</v>
       </c>
       <c r="B318" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C318" s="5">
         <v>4453045</v>
@@ -20462,7 +20459,7 @@
         <v>10</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C319" s="5">
         <v>4813088</v>
@@ -20501,7 +20498,7 @@
         <v>10</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C320" s="5">
         <v>16618803</v>
@@ -20532,7 +20529,7 @@
         <v>10</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C321" s="5">
         <v>4813423</v>
@@ -20571,7 +20568,7 @@
         <v>10</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C322" s="5">
         <v>2401479</v>
@@ -20610,7 +20607,7 @@
         <v>10</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C323" s="5">
         <v>4405234</v>
@@ -20649,7 +20646,7 @@
         <v>10</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C324" s="11">
         <v>5210220</v>
@@ -20688,7 +20685,7 @@
         <v>10</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C325" s="5">
         <v>5878792</v>
@@ -20727,7 +20724,7 @@
         <v>10</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C326" s="5">
         <v>5690206</v>
@@ -20766,7 +20763,7 @@
         <v>10</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C327" s="5">
         <v>4556974</v>
@@ -20805,7 +20802,7 @@
         <v>10</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C328" s="5">
         <v>4504449</v>
@@ -20844,7 +20841,7 @@
         <v>10</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C329" s="5">
         <v>8402868</v>
@@ -20883,7 +20880,7 @@
         <v>10</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C330" s="5">
         <v>8622778</v>
@@ -20922,7 +20919,7 @@
         <v>10</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C331" s="5">
         <v>4212438</v>
@@ -20961,7 +20958,7 @@
         <v>10</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C332" s="5">
         <v>5169142</v>
@@ -20998,7 +20995,7 @@
         <v>10</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C333" s="5">
         <v>8939571</v>
@@ -21037,7 +21034,7 @@
         <v>10</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C334" s="5">
         <v>4505257</v>
@@ -21076,7 +21073,7 @@
         <v>10</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C335" s="5">
         <v>4511696</v>
@@ -21115,7 +21112,7 @@
         <v>10</v>
       </c>
       <c r="B336" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C336" s="5">
         <v>1882235</v>
@@ -21154,7 +21151,7 @@
         <v>10</v>
       </c>
       <c r="B337" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C337" s="5">
         <v>17085325</v>
@@ -21173,7 +21170,7 @@
       <c r="I337" s="56"/>
       <c r="J337" s="56"/>
       <c r="K337" s="56" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L337" s="56">
         <f>_xlfn.XLOOKUP(C337,'[1]PL TOTAL D0'!$A$3:$A$543,'[1]PL TOTAL D0'!$C$3:$C$543,"")</f>
@@ -21185,7 +21182,7 @@
         <v>10</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C338" s="5">
         <v>3512801</v>
@@ -21224,7 +21221,7 @@
         <v>10</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C339" s="5">
         <v>15437411</v>
@@ -21255,7 +21252,7 @@
         <v>10</v>
       </c>
       <c r="B340" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C340" s="5">
         <v>4452597</v>
@@ -21294,7 +21291,7 @@
         <v>10</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C341" s="5">
         <v>4450405</v>
@@ -21333,7 +21330,7 @@
         <v>10</v>
       </c>
       <c r="B342" s="16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C342" s="22">
         <v>8563668</v>
@@ -21372,7 +21369,7 @@
         <v>10</v>
       </c>
       <c r="B343" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C343" s="22">
         <v>12373627</v>
@@ -21407,7 +21404,7 @@
         <v>10</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C344" s="5">
         <v>4363260</v>
@@ -21446,7 +21443,7 @@
         <v>10</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C345" s="5">
         <v>8526206</v>
@@ -21485,7 +21482,7 @@
         <v>10</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C346" s="22">
         <v>4693308</v>
@@ -21524,7 +21521,7 @@
         <v>10</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C347" s="15">
         <v>5332720</v>
@@ -21563,7 +21560,7 @@
         <v>10</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C348" s="15">
         <v>2075217</v>
@@ -21602,7 +21599,7 @@
         <v>10</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C349" s="15">
         <v>8732520</v>
@@ -21641,7 +21638,7 @@
         <v>10</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C350" s="5">
         <v>2636063</v>
@@ -21680,7 +21677,7 @@
         <v>10</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C351" s="5">
         <v>12910501</v>
@@ -21715,7 +21712,7 @@
         <v>10</v>
       </c>
       <c r="B352" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C352" s="10">
         <v>5076418</v>
@@ -21754,7 +21751,7 @@
         <v>10</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C353" s="5">
         <v>4221506</v>
@@ -21793,7 +21790,7 @@
         <v>10</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C354" s="5">
         <v>4221536</v>
@@ -21832,7 +21829,7 @@
         <v>10</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C355" s="5">
         <v>4278212</v>
@@ -21871,7 +21868,7 @@
         <v>10</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C356" s="5">
         <v>4213139</v>
@@ -21910,7 +21907,7 @@
         <v>10</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C357" s="5">
         <v>4334158</v>
@@ -21949,7 +21946,7 @@
         <v>10</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C358" s="5">
         <v>5247042</v>
@@ -21988,7 +21985,7 @@
         <v>10</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C359" s="5">
         <v>8404765</v>
@@ -22027,7 +22024,7 @@
         <v>10</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C360" s="5">
         <v>8072033</v>
@@ -22066,7 +22063,7 @@
         <v>10</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C361" s="5">
         <v>5206566</v>
@@ -22105,7 +22102,7 @@
         <v>10</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C362" s="5">
         <v>8244362</v>
@@ -22144,7 +22141,7 @@
         <v>10</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C363" s="5">
         <v>3175828</v>
@@ -22183,7 +22180,7 @@
         <v>10</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C364" s="5">
         <v>4567880</v>
@@ -22222,7 +22219,7 @@
         <v>10</v>
       </c>
       <c r="B365" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C365" s="5">
         <v>8144040</v>
@@ -22261,7 +22258,7 @@
         <v>10</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C366" s="5">
         <v>4473829</v>
@@ -22300,7 +22297,7 @@
         <v>10</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C367" s="10">
         <v>5000656</v>
@@ -22339,7 +22336,7 @@
         <v>10</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C368" s="5">
         <v>4490955</v>
@@ -22378,7 +22375,7 @@
         <v>10</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C369" s="5">
         <v>8132035</v>
@@ -22390,7 +22387,7 @@
         <v>125</v>
       </c>
       <c r="F369" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G369" s="56">
         <v>162087.26</v>
@@ -22417,7 +22414,7 @@
         <v>10</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C370" s="5">
         <v>8004822</v>
@@ -22456,7 +22453,7 @@
         <v>10</v>
       </c>
       <c r="B371" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C371" s="5">
         <v>4432455</v>
@@ -22495,7 +22492,7 @@
         <v>10</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C372" s="5">
         <v>827730</v>
@@ -22534,7 +22531,7 @@
         <v>10</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C373" s="5">
         <v>4804036</v>
@@ -22573,7 +22570,7 @@
         <v>10</v>
       </c>
       <c r="B374" s="16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C374" s="10">
         <v>5002390</v>
@@ -22612,7 +22609,7 @@
         <v>10</v>
       </c>
       <c r="B375" s="16" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C375" s="10">
         <v>17180118</v>
@@ -22643,7 +22640,7 @@
         <v>10</v>
       </c>
       <c r="B376" s="16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C376" s="10">
         <v>8002057</v>
@@ -22682,7 +22679,7 @@
         <v>10</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C377" s="5">
         <v>678704</v>
@@ -22721,7 +22718,7 @@
         <v>10</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C378" s="5">
         <v>5749758</v>
@@ -22760,7 +22757,7 @@
         <v>10</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C379" s="5">
         <v>8007764</v>
@@ -22799,7 +22796,7 @@
         <v>10</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C380" s="5">
         <v>5268516</v>
@@ -22838,7 +22835,7 @@
         <v>10</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C381" s="5">
         <v>1719494</v>
@@ -22877,7 +22874,7 @@
         <v>10</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C382" s="5">
         <v>4754920</v>
@@ -22916,7 +22913,7 @@
         <v>10</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C383" s="5">
         <v>4472431</v>
@@ -22955,7 +22952,7 @@
         <v>10</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C384" s="5">
         <v>8466931</v>
@@ -22994,7 +22991,7 @@
         <v>10</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C385" s="5">
         <v>4369172</v>
@@ -23033,7 +23030,7 @@
         <v>10</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C386" s="5">
         <v>8158615</v>
@@ -23072,7 +23069,7 @@
         <v>10</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C387" s="5">
         <v>8437729</v>
@@ -23111,7 +23108,7 @@
         <v>10</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C388" s="5">
         <v>4207641</v>
@@ -23150,7 +23147,7 @@
         <v>10</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C389" s="6">
         <v>5313179</v>
@@ -23189,7 +23186,7 @@
         <v>10</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C390" s="5">
         <v>4556853</v>
@@ -23228,7 +23225,7 @@
         <v>10</v>
       </c>
       <c r="B391" s="16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C391" s="10">
         <v>5042222</v>
@@ -23267,7 +23264,7 @@
         <v>10</v>
       </c>
       <c r="B392" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C392" s="13">
         <v>4983378</v>
@@ -23306,7 +23303,7 @@
         <v>10</v>
       </c>
       <c r="B393" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C393" s="13">
         <v>4983395</v>
@@ -23345,7 +23342,7 @@
         <v>10</v>
       </c>
       <c r="B394" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C394" s="5">
         <v>4455356</v>
@@ -23384,7 +23381,7 @@
         <v>10</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C395" s="5">
         <v>4444380</v>
@@ -23423,7 +23420,7 @@
         <v>10</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C396" s="5">
         <v>17704511</v>
@@ -23452,7 +23449,7 @@
         <v>10</v>
       </c>
       <c r="B397" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C397" s="10">
         <v>3641655</v>
@@ -23491,7 +23488,7 @@
         <v>10</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C398" s="5">
         <v>2950732</v>
@@ -23530,7 +23527,7 @@
         <v>10</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C399" s="5">
         <v>4527606</v>
@@ -23569,7 +23566,7 @@
         <v>10</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C400" s="5">
         <v>4463586</v>
@@ -23608,7 +23605,7 @@
         <v>10</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C401" s="5">
         <v>9191511</v>
@@ -23645,7 +23642,7 @@
         <v>10</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C402" s="5">
         <v>8197156</v>
@@ -23684,7 +23681,7 @@
         <v>10</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C403" s="5">
         <v>8364902</v>
@@ -23723,7 +23720,7 @@
         <v>10</v>
       </c>
       <c r="B404" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C404" s="5">
         <v>4435987</v>
@@ -23762,7 +23759,7 @@
         <v>10</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C405" s="5">
         <v>4436055</v>
@@ -23801,7 +23798,7 @@
         <v>10</v>
       </c>
       <c r="B406" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C406" s="5">
         <v>4454491</v>
@@ -23840,7 +23837,7 @@
         <v>10</v>
       </c>
       <c r="B407" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C407" s="9">
         <v>8447728</v>
@@ -23852,7 +23849,7 @@
         <v>13</v>
       </c>
       <c r="F407" s="5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G407" s="56">
         <v>208523.6</v>
@@ -23879,7 +23876,7 @@
         <v>10</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C408" s="5">
         <v>4752519</v>
@@ -23918,7 +23915,7 @@
         <v>10</v>
       </c>
       <c r="B409" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C409" s="5">
         <v>834301</v>
@@ -23957,7 +23954,7 @@
         <v>10</v>
       </c>
       <c r="B410" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C410" s="9">
         <v>5381719</v>
@@ -23996,7 +23993,7 @@
         <v>10</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C411" s="5">
         <v>4212476</v>
@@ -24035,7 +24032,7 @@
         <v>10</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C412" s="5">
         <v>4214460</v>
@@ -24074,7 +24071,7 @@
         <v>10</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C413" s="5">
         <v>4204242</v>
@@ -24113,7 +24110,7 @@
         <v>10</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C414" s="5">
         <v>9045586</v>
@@ -24150,7 +24147,7 @@
         <v>10</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C415" s="5">
         <v>4541022</v>
@@ -24189,7 +24186,7 @@
         <v>10</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C416" s="5">
         <v>8887532</v>
@@ -24228,7 +24225,7 @@
         <v>10</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C417" s="5">
         <v>4395314</v>
@@ -24267,7 +24264,7 @@
         <v>10</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C418" s="5">
         <v>4214604</v>
@@ -24306,7 +24303,7 @@
         <v>10</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C419" s="5">
         <v>4212581</v>
@@ -24345,7 +24342,7 @@
         <v>10</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C420" s="5">
         <v>5616259</v>
@@ -24384,7 +24381,7 @@
         <v>10</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C421" s="5">
         <v>8457882</v>
@@ -24423,7 +24420,7 @@
         <v>10</v>
       </c>
       <c r="B422" s="16" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C422" s="13">
         <v>5000460</v>
@@ -24462,7 +24459,7 @@
         <v>10</v>
       </c>
       <c r="B423" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C423" s="5">
         <v>5046919</v>
@@ -24501,7 +24498,7 @@
         <v>10</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C424" s="11">
         <v>4525587</v>
@@ -24540,7 +24537,7 @@
         <v>10</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C425" s="5">
         <v>4920447</v>
@@ -24579,7 +24576,7 @@
         <v>10</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C426" s="5">
         <v>4979322</v>
@@ -24618,7 +24615,7 @@
         <v>10</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C427" s="5">
         <v>4556150</v>
@@ -24657,7 +24654,7 @@
         <v>10</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C428" s="5">
         <v>3249855</v>
@@ -24696,7 +24693,7 @@
         <v>10</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C429" s="5">
         <v>8070544</v>
@@ -24735,7 +24732,7 @@
         <v>10</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C430" s="5">
         <v>4405702</v>
@@ -24747,7 +24744,7 @@
         <v>20</v>
       </c>
       <c r="F430" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G430" s="56">
         <v>0</v>
@@ -24774,7 +24771,7 @@
         <v>10</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C431" s="5">
         <v>4431591</v>
@@ -24813,7 +24810,7 @@
         <v>10</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C432" s="5">
         <v>4428935</v>
@@ -24852,7 +24849,7 @@
         <v>10</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C433" s="5">
         <v>4395599</v>
@@ -24891,7 +24888,7 @@
         <v>10</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C434" s="5">
         <v>5140667</v>
@@ -24930,7 +24927,7 @@
         <v>10</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C435" s="5">
         <v>4756981</v>
@@ -24969,7 +24966,7 @@
         <v>10</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C436" s="5">
         <v>8364883</v>
@@ -25008,7 +25005,7 @@
         <v>10</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C437" s="22">
         <v>5681354</v>
@@ -25047,7 +25044,7 @@
         <v>10</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C438" s="22">
         <v>8834329</v>
@@ -25086,7 +25083,7 @@
         <v>10</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C439" s="22">
         <v>8407512</v>
@@ -25125,7 +25122,7 @@
         <v>10</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C440" s="22">
         <v>8558899</v>
@@ -25164,7 +25161,7 @@
         <v>10</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C441" s="5">
         <v>4165515</v>
@@ -25203,7 +25200,7 @@
         <v>10</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C442" s="5">
         <v>8565812</v>
@@ -25242,7 +25239,7 @@
         <v>10</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C443" s="11">
         <v>8037529</v>
@@ -25281,7 +25278,7 @@
         <v>10</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C444" s="11">
         <v>8615111</v>
@@ -25320,7 +25317,7 @@
         <v>10</v>
       </c>
       <c r="B445" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C445" s="27">
         <v>5761337</v>
@@ -25359,7 +25356,7 @@
         <v>10</v>
       </c>
       <c r="B446" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C446" s="27">
         <v>4224405</v>
@@ -25398,7 +25395,7 @@
         <v>10</v>
       </c>
       <c r="B447" s="24" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C447" s="10">
         <v>5660459</v>
@@ -25437,7 +25434,7 @@
         <v>10</v>
       </c>
       <c r="B448" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C448" s="10">
         <v>8054713</v>
@@ -25476,7 +25473,7 @@
         <v>10</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C449" s="5">
         <v>5170415</v>
@@ -25515,7 +25512,7 @@
         <v>10</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C450" s="5">
         <v>4813134</v>
@@ -25554,7 +25551,7 @@
         <v>10</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C451" s="5">
         <v>4387250</v>
@@ -25593,7 +25590,7 @@
         <v>10</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C452" s="5">
         <v>8620188</v>
@@ -25632,7 +25629,7 @@
         <v>10</v>
       </c>
       <c r="B453" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C453" s="10">
         <v>5273382</v>
@@ -25671,7 +25668,7 @@
         <v>10</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C454" s="5">
         <v>4630773</v>
@@ -25710,7 +25707,7 @@
         <v>10</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C455" s="5">
         <v>4419782</v>
@@ -25749,7 +25746,7 @@
         <v>10</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C456" s="5">
         <v>4749928</v>
@@ -25788,7 +25785,7 @@
         <v>10</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C457" s="5">
         <v>1759765</v>
@@ -25827,7 +25824,7 @@
         <v>10</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C458" s="5">
         <v>4482102</v>
@@ -25866,7 +25863,7 @@
         <v>10</v>
       </c>
       <c r="B459" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C459" s="11">
         <v>4479450</v>
@@ -25905,7 +25902,7 @@
         <v>10</v>
       </c>
       <c r="B460" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C460" s="27">
         <v>5547702</v>
@@ -25944,7 +25941,7 @@
         <v>10</v>
       </c>
       <c r="B461" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C461" s="10">
         <v>5075382</v>
@@ -25983,7 +25980,7 @@
         <v>10</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C462" s="5">
         <v>4371857</v>
@@ -26022,7 +26019,7 @@
         <v>10</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C463" s="5">
         <v>5905713</v>
@@ -26061,7 +26058,7 @@
         <v>10</v>
       </c>
       <c r="B464" s="16" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C464" s="13">
         <v>5073033</v>
@@ -26100,7 +26097,7 @@
         <v>10</v>
       </c>
       <c r="B465" s="16" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C465" s="13">
         <v>8115273</v>
@@ -26139,7 +26136,7 @@
         <v>10</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C466" s="5">
         <v>4239624</v>
@@ -26178,7 +26175,7 @@
         <v>10</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C467" s="10">
         <v>5277762</v>
@@ -26217,7 +26214,7 @@
         <v>10</v>
       </c>
       <c r="B468" s="26" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C468" s="28">
         <v>5055239</v>
@@ -26256,7 +26253,7 @@
         <v>10</v>
       </c>
       <c r="B469" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C469" s="5">
         <v>4935287</v>
@@ -26295,7 +26292,7 @@
         <v>10</v>
       </c>
       <c r="B470" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C470" s="5">
         <v>8004799</v>
@@ -26334,7 +26331,7 @@
         <v>10</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C471" s="5">
         <v>8171590</v>
@@ -26373,7 +26370,7 @@
         <v>10</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C472" s="5">
         <v>3398766</v>
@@ -26412,7 +26409,7 @@
         <v>10</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C473" s="5">
         <v>13958806</v>
@@ -26445,7 +26442,7 @@
         <v>10</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C474" s="5">
         <v>4452946</v>
@@ -26484,7 +26481,7 @@
         <v>10</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C475" s="5">
         <v>4268684</v>
@@ -26523,7 +26520,7 @@
         <v>10</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C476" s="5">
         <v>5255637</v>
@@ -26562,7 +26559,7 @@
         <v>10</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C477" s="5">
         <v>4267044</v>
@@ -26601,7 +26598,7 @@
         <v>10</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C478" s="5">
         <v>8615899</v>
@@ -26640,7 +26637,7 @@
         <v>10</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C479" s="5">
         <v>4471893</v>
@@ -26679,7 +26676,7 @@
         <v>10</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C480" s="5">
         <v>4479429</v>
@@ -26718,7 +26715,7 @@
         <v>10</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C481" s="5">
         <v>4503374</v>
@@ -26757,7 +26754,7 @@
         <v>10</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C482" s="5">
         <v>5920340</v>
@@ -26796,7 +26793,7 @@
         <v>10</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C483" s="5">
         <v>4500057</v>
@@ -26835,7 +26832,7 @@
         <v>10</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C484" s="5">
         <v>4404248</v>
@@ -26874,7 +26871,7 @@
         <v>10</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C485" s="5">
         <v>2786022</v>
@@ -26913,7 +26910,7 @@
         <v>10</v>
       </c>
       <c r="B486" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C486" s="20">
         <v>5133039</v>
@@ -26952,7 +26949,7 @@
         <v>10</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C487" s="22">
         <v>4482439</v>
@@ -26991,7 +26988,7 @@
         <v>10</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C488" s="22">
         <v>4480336</v>
@@ -27030,7 +27027,7 @@
         <v>10</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C489" s="22">
         <v>5880628</v>
@@ -27069,7 +27066,7 @@
         <v>10</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C490" s="5">
         <v>5232019</v>
@@ -27108,7 +27105,7 @@
         <v>10</v>
       </c>
       <c r="B491" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C491" s="10">
         <v>8177213</v>
@@ -27147,7 +27144,7 @@
         <v>10</v>
       </c>
       <c r="B492" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C492" s="5">
         <v>4460487</v>
@@ -27186,7 +27183,7 @@
         <v>10</v>
       </c>
       <c r="B493" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C493" s="5">
         <v>4458624</v>
@@ -27225,7 +27222,7 @@
         <v>10</v>
       </c>
       <c r="B494" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C494" s="5">
         <v>4460491</v>
@@ -27264,7 +27261,7 @@
         <v>10</v>
       </c>
       <c r="B495" s="24" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C495" s="10">
         <v>8353082</v>
@@ -27303,7 +27300,7 @@
         <v>10</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C496" s="5">
         <v>4381359</v>
@@ -27342,7 +27339,7 @@
         <v>10</v>
       </c>
       <c r="B497" s="24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C497" s="10">
         <v>5324840</v>
@@ -27381,7 +27378,7 @@
         <v>10</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C498" s="5">
         <v>4224284</v>
@@ -27420,7 +27417,7 @@
         <v>10</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C499" s="5">
         <v>4497825</v>
@@ -27459,7 +27456,7 @@
         <v>10</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C500" s="5">
         <v>8123677</v>
@@ -27498,7 +27495,7 @@
         <v>10</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C501" s="5">
         <v>4940699</v>
@@ -27537,7 +27534,7 @@
         <v>10</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C502" s="5">
         <v>4222784</v>
@@ -27576,7 +27573,7 @@
         <v>10</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C503" s="5">
         <v>5994261</v>
@@ -27615,7 +27612,7 @@
         <v>10</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C504" s="5">
         <v>5135281</v>
@@ -27654,7 +27651,7 @@
         <v>10</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C505" s="5">
         <v>4500804</v>
@@ -27693,7 +27690,7 @@
         <v>10</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C506" s="5">
         <v>13837034</v>
@@ -27726,7 +27723,7 @@
         <v>10</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C507" s="5">
         <v>4457389</v>
@@ -27765,7 +27762,7 @@
         <v>10</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C508" s="5">
         <v>5274028</v>
@@ -27804,7 +27801,7 @@
         <v>10</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C509" s="5">
         <v>4801481</v>
@@ -27843,7 +27840,7 @@
         <v>10</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C510" s="5">
         <v>2064834</v>
@@ -27882,7 +27879,7 @@
         <v>10</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C511" s="5">
         <v>11660107</v>
@@ -27917,7 +27914,7 @@
         <v>10</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C512" s="5">
         <v>13960059</v>
@@ -27929,7 +27926,7 @@
         <v>13</v>
       </c>
       <c r="F512" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G512" s="56"/>
       <c r="H512" s="56"/>
@@ -27950,7 +27947,7 @@
         <v>10</v>
       </c>
       <c r="B513" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C513" s="5">
         <v>9101398</v>
@@ -27985,7 +27982,7 @@
         <v>10</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C514" s="5">
         <v>9008080</v>
@@ -28024,7 +28021,7 @@
         <v>10</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C515" s="5">
         <v>4466350</v>
@@ -28063,7 +28060,7 @@
         <v>10</v>
       </c>
       <c r="B516" s="25" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C516" s="5">
         <v>4550605</v>
@@ -28102,7 +28099,7 @@
         <v>10</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C517" s="5">
         <v>5216881</v>
@@ -28141,7 +28138,7 @@
         <v>10</v>
       </c>
       <c r="B518" s="16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C518" s="5">
         <v>2828327</v>
@@ -28180,7 +28177,7 @@
         <v>10</v>
       </c>
       <c r="B519" s="16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C519" s="5">
         <v>4318604</v>
@@ -28219,7 +28216,7 @@
         <v>10</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C520" s="5">
         <v>4886366</v>
@@ -28258,7 +28255,7 @@
         <v>10</v>
       </c>
       <c r="B521" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C521" s="5">
         <v>8001858</v>
@@ -28270,7 +28267,7 @@
         <v>29</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G521" s="56">
         <v>236704.14</v>
@@ -28297,7 +28294,7 @@
         <v>10</v>
       </c>
       <c r="B522" s="24" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C522" s="10">
         <v>330949</v>
@@ -28336,7 +28333,7 @@
         <v>10</v>
       </c>
       <c r="B523" s="24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C523" s="10">
         <v>8153800</v>
@@ -28375,7 +28372,7 @@
         <v>10</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C524" s="10">
         <v>8712353</v>
@@ -28414,7 +28411,7 @@
         <v>10</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C525" s="5">
         <v>4539779</v>
@@ -28453,7 +28450,7 @@
         <v>10</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C526" s="5">
         <v>4505474</v>
@@ -28492,7 +28489,7 @@
         <v>10</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C527" s="5">
         <v>8711062</v>
@@ -28531,7 +28528,7 @@
         <v>10</v>
       </c>
       <c r="B528" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C528" s="5">
         <v>4462543</v>
@@ -28570,7 +28567,7 @@
         <v>10</v>
       </c>
       <c r="B529" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C529" s="5">
         <v>4470679</v>
@@ -28609,7 +28606,7 @@
         <v>10</v>
       </c>
       <c r="B530" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C530" s="5">
         <v>4472538</v>
@@ -28648,7 +28645,7 @@
         <v>10</v>
       </c>
       <c r="B531" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C531" s="9">
         <v>4213929</v>
@@ -28687,7 +28684,7 @@
         <v>10</v>
       </c>
       <c r="B532" s="16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C532" s="13">
         <v>5152037</v>
@@ -28726,7 +28723,7 @@
         <v>10</v>
       </c>
       <c r="B533" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C533" s="9">
         <v>4272426</v>
@@ -28765,7 +28762,7 @@
         <v>10</v>
       </c>
       <c r="B534" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C534" s="5">
         <v>8514508</v>
@@ -28804,7 +28801,7 @@
         <v>10</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C535" s="5">
         <v>4392159</v>
@@ -28816,7 +28813,7 @@
         <v>13</v>
       </c>
       <c r="F535" s="5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G535" s="56">
         <v>0</v>
@@ -28843,7 +28840,7 @@
         <v>10</v>
       </c>
       <c r="B536" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C536" s="5">
         <v>4487016</v>
@@ -28882,7 +28879,7 @@
         <v>10</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C537" s="5">
         <v>4924222</v>
@@ -28921,7 +28918,7 @@
         <v>10</v>
       </c>
       <c r="B538" s="16" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C538" s="10">
         <v>5002457</v>
@@ -28960,7 +28957,7 @@
         <v>10</v>
       </c>
       <c r="B539" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C539" s="9">
         <v>5428871</v>
@@ -28999,7 +28996,7 @@
         <v>10</v>
       </c>
       <c r="B540" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C540" s="5">
         <v>8188457</v>
@@ -29038,7 +29035,7 @@
         <v>10</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C541" s="5">
         <v>4472076</v>
@@ -29077,7 +29074,7 @@
         <v>10</v>
       </c>
       <c r="B542" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C542" s="5">
         <v>8470048</v>
@@ -29116,7 +29113,7 @@
         <v>10</v>
       </c>
       <c r="B543" s="16" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C543" s="13">
         <v>4975924</v>
@@ -29155,7 +29152,7 @@
         <v>10</v>
       </c>
       <c r="B544" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C544" s="5">
         <v>4752461</v>
@@ -29194,7 +29191,7 @@
         <v>10</v>
       </c>
       <c r="B545" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C545" s="5">
         <v>4752494</v>
@@ -29233,7 +29230,7 @@
         <v>10</v>
       </c>
       <c r="B546" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C546" s="5">
         <v>13882576</v>
@@ -29264,7 +29261,7 @@
         <v>10</v>
       </c>
       <c r="B547" s="16" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C547" s="13">
         <v>8004835</v>
@@ -29276,7 +29273,7 @@
         <v>13</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G547" s="56">
         <v>339648.68</v>
@@ -29303,7 +29300,7 @@
         <v>10</v>
       </c>
       <c r="B548" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C548" s="5">
         <v>5305965</v>
@@ -29315,7 +29312,7 @@
         <v>20</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G548" s="56">
         <v>0</v>
@@ -29342,7 +29339,7 @@
         <v>10</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C549" s="5">
         <v>5283421</v>
@@ -29381,7 +29378,7 @@
         <v>10</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C550" s="5">
         <v>4207955</v>
@@ -29420,7 +29417,7 @@
         <v>10</v>
       </c>
       <c r="B551" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C551" s="9">
         <v>5547703</v>
@@ -29459,7 +29456,7 @@
         <v>10</v>
       </c>
       <c r="B552" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C552" s="5">
         <v>9068371</v>
@@ -29471,7 +29468,7 @@
         <v>20</v>
       </c>
       <c r="F552" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G552" s="56"/>
       <c r="H552" s="56">
@@ -29496,7 +29493,7 @@
         <v>10</v>
       </c>
       <c r="B553" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C553" s="5">
         <v>4450760</v>
@@ -29535,7 +29532,7 @@
         <v>10</v>
       </c>
       <c r="B554" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C554" s="5">
         <v>8197302</v>
@@ -29574,7 +29571,7 @@
         <v>10</v>
       </c>
       <c r="B555" s="16" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C555" s="13">
         <v>1922009</v>
@@ -29613,7 +29610,7 @@
         <v>10</v>
       </c>
       <c r="B556" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C556" s="5">
         <v>8030888</v>
@@ -29652,7 +29649,7 @@
         <v>10</v>
       </c>
       <c r="B557" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C557" s="5">
         <v>8328804</v>
@@ -29691,7 +29688,7 @@
         <v>10</v>
       </c>
       <c r="B558" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C558" s="5">
         <v>4945203</v>
@@ -29730,7 +29727,7 @@
         <v>10</v>
       </c>
       <c r="B559" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C559" s="5">
         <v>4945161</v>
@@ -29769,7 +29766,7 @@
         <v>10</v>
       </c>
       <c r="B560" s="16" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C560" s="13">
         <v>4999410</v>
@@ -29808,7 +29805,7 @@
         <v>10</v>
       </c>
       <c r="B561" s="16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C561" s="13">
         <v>8420189</v>
@@ -29847,7 +29844,7 @@
         <v>10</v>
       </c>
       <c r="B562" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C562" s="5">
         <v>4216401</v>
@@ -29886,7 +29883,7 @@
         <v>10</v>
       </c>
       <c r="B563" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C563" s="5">
         <v>4331477</v>
@@ -29925,7 +29922,7 @@
         <v>10</v>
       </c>
       <c r="B564" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C564" s="11">
         <v>5683532</v>
@@ -29964,7 +29961,7 @@
         <v>10</v>
       </c>
       <c r="B565" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C565" s="11">
         <v>16267437</v>
@@ -29976,7 +29973,7 @@
         <v>29</v>
       </c>
       <c r="F565" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G565" s="56"/>
       <c r="H565" s="56"/>
@@ -29995,7 +29992,7 @@
         <v>10</v>
       </c>
       <c r="B566" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C566" s="11">
         <v>8733105</v>
@@ -30034,7 +30031,7 @@
         <v>10</v>
       </c>
       <c r="B567" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C567" s="5">
         <v>4517080</v>
@@ -30073,7 +30070,7 @@
         <v>10</v>
       </c>
       <c r="B568" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C568" s="5">
         <v>4202332</v>
@@ -30112,7 +30109,7 @@
         <v>10</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C569" s="10">
         <v>5348011</v>
@@ -30151,7 +30148,7 @@
         <v>10</v>
       </c>
       <c r="B570" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C570" s="5">
         <v>8458289</v>
@@ -30190,7 +30187,7 @@
         <v>10</v>
       </c>
       <c r="B571" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C571" s="5">
         <v>4536602</v>
@@ -30229,7 +30226,7 @@
         <v>10</v>
       </c>
       <c r="B572" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C572" s="9">
         <v>5890232</v>
@@ -30268,7 +30265,7 @@
         <v>10</v>
       </c>
       <c r="B573" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C573" s="5">
         <v>9150609</v>
@@ -30305,7 +30302,7 @@
         <v>10</v>
       </c>
       <c r="B574" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C574" s="5">
         <v>8371468</v>
@@ -30344,7 +30341,7 @@
         <v>10</v>
       </c>
       <c r="B575" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C575" s="5">
         <v>1879977</v>
@@ -30383,7 +30380,7 @@
         <v>10</v>
       </c>
       <c r="B576" s="35" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C576" s="36">
         <v>4550289</v>
@@ -30422,7 +30419,7 @@
         <v>10</v>
       </c>
       <c r="B577" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C577" s="20">
         <v>8311056</v>
@@ -30461,7 +30458,7 @@
         <v>10</v>
       </c>
       <c r="B578" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C578" s="5">
         <v>4425261</v>
@@ -30500,7 +30497,7 @@
         <v>10</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C579" s="5">
         <v>1368670</v>
@@ -30539,7 +30536,7 @@
         <v>10</v>
       </c>
       <c r="B580" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C580" s="5">
         <v>8588044</v>
@@ -30578,7 +30575,7 @@
         <v>10</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C581" s="5">
         <v>8610229</v>
@@ -30617,7 +30614,7 @@
         <v>10</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C582" s="5">
         <v>4224011</v>
@@ -30656,7 +30653,7 @@
         <v>10</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C583" s="5">
         <v>8026942</v>
@@ -30695,7 +30692,7 @@
         <v>10</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C584" s="5">
         <v>13737887</v>
@@ -30728,7 +30725,7 @@
         <v>10</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C585" s="5">
         <v>8418454</v>
@@ -30757,7 +30754,7 @@
         <v>10</v>
       </c>
       <c r="B586" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C586" s="5">
         <v>4498637</v>
@@ -30796,7 +30793,7 @@
         <v>10</v>
       </c>
       <c r="B587" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C587" s="5">
         <v>8443638</v>
@@ -30835,7 +30832,7 @@
         <v>10</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C588" s="5">
         <v>4238126</v>
@@ -30874,7 +30871,7 @@
         <v>10</v>
       </c>
       <c r="B589" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C589" s="5">
         <v>16237695</v>
@@ -30905,7 +30902,7 @@
         <v>10</v>
       </c>
       <c r="B590" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C590" s="5">
         <v>5105172</v>
@@ -30944,7 +30941,7 @@
         <v>10</v>
       </c>
       <c r="B591" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C591" s="9">
         <v>5440756</v>
@@ -30983,7 +30980,7 @@
         <v>10</v>
       </c>
       <c r="B592" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C592" s="9">
         <v>5599277</v>
@@ -31022,7 +31019,7 @@
         <v>10</v>
       </c>
       <c r="B593" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C593" s="9">
         <v>4211533</v>
@@ -31061,7 +31058,7 @@
         <v>10</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C594" s="5">
         <v>4487140</v>
@@ -31100,7 +31097,7 @@
         <v>10</v>
       </c>
       <c r="B595" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C595" s="5">
         <v>5173958</v>
@@ -31139,7 +31136,7 @@
         <v>10</v>
       </c>
       <c r="B596" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C596" s="5">
         <v>4813166</v>
@@ -31178,7 +31175,7 @@
         <v>10</v>
       </c>
       <c r="B597" s="4" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C597" s="5">
         <v>4806286</v>
@@ -31217,7 +31214,7 @@
         <v>10</v>
       </c>
       <c r="B598" s="47" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C598" s="13">
         <v>5009947</v>
@@ -31256,7 +31253,7 @@
         <v>10</v>
       </c>
       <c r="B599" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C599" s="9">
         <v>4274441</v>
@@ -31295,7 +31292,7 @@
         <v>10</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C600" s="11">
         <v>4400000</v>
@@ -31307,7 +31304,7 @@
         <v>20</v>
       </c>
       <c r="F600" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G600" s="56">
         <v>0</v>
@@ -31334,7 +31331,7 @@
         <v>10</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C601" s="5">
         <v>5886225</v>
@@ -31373,7 +31370,7 @@
         <v>10</v>
       </c>
       <c r="B602" s="16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C602" s="22">
         <v>4967702</v>
@@ -31412,7 +31409,7 @@
         <v>10</v>
       </c>
       <c r="B603" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C603" s="5">
         <v>17384165</v>
@@ -31443,7 +31440,7 @@
         <v>10</v>
       </c>
       <c r="B604" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C604" s="5">
         <v>8119302</v>
@@ -31482,7 +31479,7 @@
         <v>10</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C605" s="5">
         <v>5293480</v>
@@ -31521,7 +31518,7 @@
         <v>10</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C606" s="5">
         <v>1804114</v>
@@ -31560,7 +31557,7 @@
         <v>10</v>
       </c>
       <c r="B607" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C607" s="5">
         <v>5103059</v>
@@ -31599,7 +31596,7 @@
         <v>10</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C608" s="5">
         <v>4419765</v>
@@ -31638,7 +31635,7 @@
         <v>10</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C609" s="5">
         <v>4466221</v>
@@ -31677,7 +31674,7 @@
         <v>10</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C610" s="5">
         <v>4462930</v>
@@ -31716,7 +31713,7 @@
         <v>10</v>
       </c>
       <c r="B611" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C611" s="5">
         <v>8894569</v>
@@ -31755,7 +31752,7 @@
         <v>10</v>
       </c>
       <c r="B612" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C612" s="13">
         <v>4981655</v>
@@ -31794,7 +31791,7 @@
         <v>10</v>
       </c>
       <c r="B613" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C613" s="5">
         <v>8831393</v>
@@ -31833,7 +31830,7 @@
         <v>10</v>
       </c>
       <c r="B614" s="38" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C614" s="39">
         <v>4223226</v>
@@ -31844,7 +31841,7 @@
       <c r="E614" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F614" s="39" t="s">
+      <c r="F614" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G614" s="56">
@@ -31872,7 +31869,7 @@
         <v>10</v>
       </c>
       <c r="B615" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C615" s="9">
         <v>4612043</v>
@@ -31911,7 +31908,7 @@
         <v>10</v>
       </c>
       <c r="B616" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C616" s="9">
         <v>8218514</v>
@@ -31950,7 +31947,7 @@
         <v>10</v>
       </c>
       <c r="B617" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C617" s="9">
         <v>4552944</v>
@@ -31989,7 +31986,7 @@
         <v>10</v>
       </c>
       <c r="B618" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C618" s="9">
         <v>4211911</v>
@@ -32028,7 +32025,7 @@
         <v>10</v>
       </c>
       <c r="B619" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C619" s="9">
         <v>5581299</v>
@@ -32064,10 +32061,10 @@
     </row>
     <row r="620" spans="1:12">
       <c r="A620" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B620" s="4" t="s">
         <v>528</v>
-      </c>
-      <c r="B620" s="4" t="s">
-        <v>529</v>
       </c>
       <c r="C620" s="5">
         <v>3757672</v>
@@ -32101,10 +32098,10 @@
     </row>
     <row r="621" spans="1:12">
       <c r="A621" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B621" s="4" t="s">
         <v>528</v>
-      </c>
-      <c r="B621" s="4" t="s">
-        <v>529</v>
       </c>
       <c r="C621" s="5">
         <v>18408485</v>
@@ -32138,10 +32135,10 @@
     </row>
     <row r="622" spans="1:12">
       <c r="A622" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B622" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C622" s="5">
         <v>3227135</v>
@@ -32177,10 +32174,10 @@
     </row>
     <row r="623" spans="1:12">
       <c r="A623" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B623" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C623" s="5">
         <v>3345620</v>
@@ -32216,10 +32213,10 @@
     </row>
     <row r="624" spans="1:12">
       <c r="A624" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B624" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C624" s="5">
         <v>6853541</v>
@@ -32255,10 +32252,10 @@
     </row>
     <row r="625" spans="1:12">
       <c r="A625" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B625" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C625" s="5">
         <v>15466228</v>
@@ -32294,10 +32291,10 @@
     </row>
     <row r="626" spans="1:12">
       <c r="A626" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B626" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C626" s="5">
         <v>3437690</v>
@@ -32333,10 +32330,10 @@
     </row>
     <row r="627" spans="1:12">
       <c r="A627" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B627" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C627" s="5">
         <v>17005019</v>
@@ -32370,10 +32367,10 @@
     </row>
     <row r="628" spans="1:12">
       <c r="A628" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B628" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C628" s="5">
         <v>4427733</v>
@@ -32409,10 +32406,10 @@
     </row>
     <row r="629" spans="1:12">
       <c r="A629" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B629" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C629" s="5">
         <v>15705827</v>
@@ -32448,10 +32445,10 @@
     </row>
     <row r="630" spans="1:12">
       <c r="A630" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B630" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C630" s="5">
         <v>7656240</v>
@@ -32463,7 +32460,7 @@
         <v>20</v>
       </c>
       <c r="F630" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G630" s="56">
         <v>500044.62079999998</v>
@@ -32487,10 +32484,10 @@
     </row>
     <row r="631" spans="1:12">
       <c r="A631" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B631" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C631" s="5">
         <v>8580102</v>
@@ -32502,7 +32499,7 @@
         <v>20</v>
       </c>
       <c r="F631" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G631" s="56">
         <v>710643.39870000002</v>
@@ -32526,10 +32523,10 @@
     </row>
     <row r="632" spans="1:12">
       <c r="A632" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B632" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C632" s="5">
         <v>9023091</v>
@@ -32565,7 +32562,7 @@
     </row>
     <row r="633" spans="1:12">
       <c r="A633" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B633" s="4" t="s">
         <v>96</v>
@@ -32604,10 +32601,10 @@
     </row>
     <row r="634" spans="1:12">
       <c r="A634" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B634" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C634" s="5">
         <v>8424641</v>
@@ -32643,7 +32640,7 @@
     </row>
     <row r="635" spans="1:12">
       <c r="A635" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B635" s="4" t="s">
         <v>107</v>
@@ -32682,10 +32679,10 @@
     </row>
     <row r="636" spans="1:12">
       <c r="A636" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B636" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C636" s="5">
         <v>11451861</v>
@@ -32719,10 +32716,10 @@
     </row>
     <row r="637" spans="1:12">
       <c r="A637" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B637" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C637" s="5">
         <v>3732278</v>
@@ -32758,10 +32755,10 @@
     </row>
     <row r="638" spans="1:12">
       <c r="A638" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B638" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C638" s="5">
         <v>3144426</v>
@@ -32797,10 +32794,10 @@
     </row>
     <row r="639" spans="1:12">
       <c r="A639" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B639" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C639" s="5">
         <v>2738150</v>
@@ -32834,10 +32831,10 @@
     </row>
     <row r="640" spans="1:12">
       <c r="A640" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B640" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C640" s="5">
         <v>3723914</v>
@@ -32873,10 +32870,10 @@
     </row>
     <row r="641" spans="1:12">
       <c r="A641" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B641" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C641" s="5">
         <v>3862487</v>
@@ -32912,10 +32909,10 @@
     </row>
     <row r="642" spans="1:12">
       <c r="A642" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B642" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C642" s="5">
         <v>3977611</v>
@@ -32951,10 +32948,10 @@
     </row>
     <row r="643" spans="1:12">
       <c r="A643" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B643" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C643" s="5">
         <v>2209353</v>
@@ -32988,10 +32985,10 @@
     </row>
     <row r="644" spans="1:12">
       <c r="A644" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B644" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C644" s="5">
         <v>2570963</v>
@@ -33027,10 +33024,10 @@
     </row>
     <row r="645" spans="1:12">
       <c r="A645" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B645" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C645" s="5">
         <v>7294113</v>
@@ -33058,10 +33055,10 @@
     </row>
     <row r="646" spans="1:12">
       <c r="A646" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B646" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C646" s="5">
         <v>297338</v>
@@ -33097,10 +33094,10 @@
     </row>
     <row r="647" spans="1:12">
       <c r="A647" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B647" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C647" s="5">
         <v>18826594</v>
@@ -33126,10 +33123,10 @@
     </row>
     <row r="648" spans="1:12">
       <c r="A648" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B648" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C648" s="5">
         <v>9290248</v>
@@ -33165,10 +33162,10 @@
     </row>
     <row r="649" spans="1:12">
       <c r="A649" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B649" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C649" s="5">
         <v>4097264</v>
@@ -33204,10 +33201,10 @@
     </row>
     <row r="650" spans="1:12">
       <c r="A650" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B650" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C650" s="5">
         <v>3237400</v>
@@ -33243,10 +33240,10 @@
     </row>
     <row r="651" spans="1:12">
       <c r="A651" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B651" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C651" s="5">
         <v>89660</v>
@@ -33282,10 +33279,10 @@
     </row>
     <row r="652" spans="1:12">
       <c r="A652" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B652" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C652" s="5">
         <v>2375512</v>
@@ -33321,10 +33318,10 @@
     </row>
     <row r="653" spans="1:12">
       <c r="A653" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C653" s="5">
         <v>18446216</v>
@@ -33358,10 +33355,10 @@
     </row>
     <row r="654" spans="1:12">
       <c r="A654" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B654" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C654" s="5">
         <v>3917632</v>
@@ -33373,7 +33370,7 @@
         <v>20</v>
       </c>
       <c r="F654" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G654" s="56"/>
       <c r="H654" s="57">
@@ -33395,10 +33392,10 @@
     </row>
     <row r="655" spans="1:12">
       <c r="A655" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B655" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C655" s="5">
         <v>5282208</v>
@@ -33432,10 +33429,10 @@
     </row>
     <row r="656" spans="1:12">
       <c r="A656" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B656" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C656" s="5">
         <v>12398948</v>
@@ -33471,10 +33468,10 @@
     </row>
     <row r="657" spans="1:12">
       <c r="A657" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B657" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C657" s="5">
         <v>3426143</v>
@@ -33510,10 +33507,10 @@
     </row>
     <row r="658" spans="1:12">
       <c r="A658" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B658" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C658" s="5">
         <v>750425</v>
@@ -33549,10 +33546,10 @@
     </row>
     <row r="659" spans="1:12">
       <c r="A659" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B659" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C659" s="5">
         <v>8961166</v>
@@ -33588,10 +33585,10 @@
     </row>
     <row r="660" spans="1:12">
       <c r="A660" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B660" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C660" s="5">
         <v>8406743</v>
@@ -33603,7 +33600,7 @@
         <v>20</v>
       </c>
       <c r="F660" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G660" s="56">
         <v>1016864.952</v>
@@ -33627,10 +33624,10 @@
     </row>
     <row r="661" spans="1:12">
       <c r="A661" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B661" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C661" s="5">
         <v>5698370</v>
@@ -33666,10 +33663,10 @@
     </row>
     <row r="662" spans="1:12">
       <c r="A662" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B662" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C662" s="5">
         <v>2570762</v>
@@ -33705,10 +33702,10 @@
     </row>
     <row r="663" spans="1:12">
       <c r="A663" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B663" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C663" s="5">
         <v>18718220</v>
@@ -33736,10 +33733,10 @@
     </row>
     <row r="664" spans="1:12">
       <c r="A664" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B664" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C664" s="5">
         <v>17033260</v>
@@ -33751,7 +33748,7 @@
         <v>13</v>
       </c>
       <c r="F664" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G664" s="56"/>
       <c r="H664" s="57">
@@ -33773,10 +33770,10 @@
     </row>
     <row r="665" spans="1:12">
       <c r="A665" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B665" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C665" s="5">
         <v>2044321</v>
@@ -33812,10 +33809,10 @@
     </row>
     <row r="666" spans="1:12">
       <c r="A666" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B666" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C666" s="5">
         <v>516643</v>
@@ -33851,10 +33848,10 @@
     </row>
     <row r="667" spans="1:12">
       <c r="A667" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B667" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C667" s="5">
         <v>18610732</v>
@@ -33888,10 +33885,10 @@
     </row>
     <row r="668" spans="1:12">
       <c r="A668" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B668" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C668" s="5">
         <v>17684846</v>
@@ -33927,10 +33924,10 @@
     </row>
     <row r="669" spans="1:12">
       <c r="A669" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B669" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C669" s="5">
         <v>15919404</v>
@@ -33966,10 +33963,10 @@
     </row>
     <row r="670" spans="1:12">
       <c r="A670" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B670" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C670" s="5">
         <v>4340593</v>
@@ -34005,10 +34002,10 @@
     </row>
     <row r="671" spans="1:12">
       <c r="A671" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B671" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C671" s="5">
         <v>8625760</v>
@@ -34044,10 +34041,10 @@
     </row>
     <row r="672" spans="1:12">
       <c r="A672" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B672" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C672" s="5">
         <v>390262</v>
@@ -34083,10 +34080,10 @@
     </row>
     <row r="673" spans="1:12">
       <c r="A673" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B673" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C673" s="5">
         <v>11371496</v>
@@ -34098,7 +34095,7 @@
         <v>20</v>
       </c>
       <c r="F673" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G673" s="56"/>
       <c r="H673" s="57">
@@ -34120,10 +34117,10 @@
     </row>
     <row r="674" spans="1:12">
       <c r="A674" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B674" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C674" s="5">
         <v>5745802</v>
@@ -34159,10 +34156,10 @@
     </row>
     <row r="675" spans="1:12">
       <c r="A675" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B675" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C675" s="5">
         <v>17448472</v>
@@ -34198,10 +34195,10 @@
     </row>
     <row r="676" spans="1:12">
       <c r="A676" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B676" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C676" s="5">
         <v>8759647</v>
@@ -34213,7 +34210,7 @@
         <v>125</v>
       </c>
       <c r="F676" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G676" s="56">
         <v>1421475.0989999999</v>
@@ -34237,10 +34234,10 @@
     </row>
     <row r="677" spans="1:12">
       <c r="A677" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B677" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C677" s="5">
         <v>12630126</v>
@@ -34276,10 +34273,10 @@
     </row>
     <row r="678" spans="1:12">
       <c r="A678" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B678" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C678" s="5">
         <v>9851852</v>
@@ -34313,10 +34310,10 @@
     </row>
     <row r="679" spans="1:12">
       <c r="A679" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B679" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C679" s="5">
         <v>3709188</v>
@@ -34352,22 +34349,22 @@
     </row>
     <row r="680" spans="1:12">
       <c r="A680" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B680" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C680" s="5">
         <v>18801240</v>
       </c>
       <c r="D680" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E680" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F680" s="5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G680" s="56"/>
       <c r="H680" s="57"/>
@@ -34383,13 +34380,13 @@
     </row>
     <row r="681" spans="1:12">
       <c r="A681" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B681" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C681" s="46" t="s">
         <v>733</v>
-      </c>
-      <c r="C681" s="46" t="s">
-        <v>734</v>
       </c>
       <c r="D681" s="5" t="s">
         <v>12</v>
@@ -34414,10 +34411,10 @@
     </row>
     <row r="682" spans="1:12">
       <c r="A682" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B682" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C682" s="5">
         <v>17159452</v>
@@ -34453,10 +34450,10 @@
     </row>
     <row r="683" spans="1:12">
       <c r="A683" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B683" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C683" s="5">
         <v>2679780</v>
@@ -34492,10 +34489,10 @@
     </row>
     <row r="684" spans="1:12">
       <c r="A684" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B684" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C684" s="5">
         <v>15733167</v>
@@ -34507,7 +34504,7 @@
         <v>20</v>
       </c>
       <c r="F684" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G684" s="56"/>
       <c r="H684" s="57">
@@ -34529,10 +34526,10 @@
     </row>
     <row r="685" spans="1:12">
       <c r="A685" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B685" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C685" s="5">
         <v>2872613</v>
@@ -34544,7 +34541,7 @@
         <v>20</v>
       </c>
       <c r="F685" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G685" s="56">
         <v>4432164.0729999999</v>
@@ -34568,10 +34565,10 @@
     </row>
     <row r="686" spans="1:12">
       <c r="A686" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B686" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C686" s="5">
         <v>17319807</v>
@@ -34583,7 +34580,7 @@
         <v>20</v>
       </c>
       <c r="F686" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G686" s="56">
         <v>112559.35</v>
@@ -34607,10 +34604,10 @@
     </row>
     <row r="687" spans="1:12">
       <c r="A687" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B687" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C687" s="5">
         <v>16286158</v>
@@ -34622,7 +34619,7 @@
         <v>20</v>
       </c>
       <c r="F687" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G687" s="56">
         <v>844539.6483</v>
@@ -34646,10 +34643,10 @@
     </row>
     <row r="688" spans="1:12">
       <c r="A688" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B688" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C688" s="5">
         <v>2037686</v>
@@ -34685,10 +34682,10 @@
     </row>
     <row r="689" spans="1:12">
       <c r="A689" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B689" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C689" s="5">
         <v>2146957</v>
@@ -34724,10 +34721,10 @@
     </row>
     <row r="690" spans="1:12">
       <c r="A690" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B690" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C690" s="5">
         <v>4334650</v>
@@ -34763,10 +34760,10 @@
     </row>
     <row r="691" spans="1:12">
       <c r="A691" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B691" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C691" s="5">
         <v>9071920</v>
@@ -34802,10 +34799,10 @@
     </row>
     <row r="692" spans="1:12">
       <c r="A692" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B692" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C692" s="5">
         <v>47176</v>
@@ -34839,10 +34836,10 @@
     </row>
     <row r="693" spans="1:12">
       <c r="A693" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B693" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C693" s="5">
         <v>15463905</v>
@@ -34878,10 +34875,10 @@
     </row>
     <row r="694" spans="1:12">
       <c r="A694" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B694" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C694" s="5">
         <v>2427743</v>
@@ -34917,10 +34914,10 @@
     </row>
     <row r="695" spans="1:12">
       <c r="A695" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B695" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C695" s="5">
         <v>4862996</v>
@@ -34956,10 +34953,10 @@
     </row>
     <row r="696" spans="1:12">
       <c r="A696" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B696" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C696" s="5">
         <v>4114582</v>
@@ -34995,10 +34992,10 @@
     </row>
     <row r="697" spans="1:12">
       <c r="A697" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B697" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C697" s="5">
         <v>2182451</v>
@@ -35032,10 +35029,10 @@
     </row>
     <row r="698" spans="1:12">
       <c r="A698" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B698" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C698" s="5">
         <v>15218743</v>
@@ -35071,10 +35068,10 @@
     </row>
     <row r="699" spans="1:12">
       <c r="A699" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B699" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C699" s="5">
         <v>17006336</v>
@@ -35086,7 +35083,7 @@
         <v>13</v>
       </c>
       <c r="F699" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G699" s="56">
         <v>0</v>
@@ -35110,10 +35107,10 @@
     </row>
     <row r="700" spans="1:12">
       <c r="A700" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B700" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C700" s="5">
         <v>4329986</v>
@@ -35147,10 +35144,10 @@
     </row>
     <row r="701" spans="1:12">
       <c r="A701" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B701" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C701" s="5">
         <v>2569205</v>
@@ -35186,10 +35183,10 @@
     </row>
     <row r="702" spans="1:12">
       <c r="A702" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B702" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C702" s="5">
         <v>287927</v>
@@ -35225,10 +35222,10 @@
     </row>
     <row r="703" spans="1:12">
       <c r="A703" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B703" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C703" s="5">
         <v>3709756</v>
@@ -35264,10 +35261,10 @@
     </row>
     <row r="704" spans="1:12">
       <c r="A704" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B704" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C704" s="5">
         <v>18397250</v>
@@ -35301,10 +35298,10 @@
     </row>
     <row r="705" spans="1:12">
       <c r="A705" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B705" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C705" s="5">
         <v>4743435</v>
@@ -35316,7 +35313,7 @@
         <v>20</v>
       </c>
       <c r="F705" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G705" s="56"/>
       <c r="H705" s="57">
@@ -35338,10 +35335,10 @@
     </row>
     <row r="706" spans="1:12">
       <c r="A706" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B706" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C706" s="5">
         <v>3671989</v>
@@ -35377,10 +35374,10 @@
     </row>
     <row r="707" spans="1:12">
       <c r="A707" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B707" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C707" s="5">
         <v>14411211</v>
@@ -35416,10 +35413,10 @@
     </row>
     <row r="708" spans="1:12">
       <c r="A708" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B708" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C708" s="5">
         <v>750733</v>
@@ -35455,10 +35452,10 @@
     </row>
     <row r="709" spans="1:12">
       <c r="A709" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B709" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C709" s="5">
         <v>4574738</v>
@@ -35494,10 +35491,10 @@
     </row>
     <row r="710" spans="1:12">
       <c r="A710" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B710" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C710" s="5">
         <v>18718124</v>
@@ -35527,10 +35524,10 @@
     </row>
     <row r="711" spans="1:12">
       <c r="A711" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B711" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C711" s="5">
         <v>9389773</v>
@@ -35566,10 +35563,10 @@
     </row>
     <row r="712" spans="1:12">
       <c r="A712" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C712" s="5">
         <v>5612032</v>
@@ -35605,10 +35602,10 @@
     </row>
     <row r="713" spans="1:12">
       <c r="A713" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B713" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C713" s="5">
         <v>4660824</v>
@@ -35644,10 +35641,10 @@
     </row>
     <row r="714" spans="1:12">
       <c r="A714" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B714" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C714" s="5">
         <v>4627761</v>
@@ -35683,10 +35680,10 @@
     </row>
     <row r="715" spans="1:12">
       <c r="A715" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B715" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C715" s="5">
         <v>474990</v>
@@ -35722,10 +35719,10 @@
     </row>
     <row r="716" spans="1:12">
       <c r="A716" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B716" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C716" s="5">
         <v>18809506</v>
@@ -35753,10 +35750,10 @@
     </row>
     <row r="717" spans="1:12">
       <c r="A717" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B717" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C717" s="5">
         <v>9602680</v>
@@ -35792,10 +35789,10 @@
     </row>
     <row r="718" spans="1:12">
       <c r="A718" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B718" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C718" s="5">
         <v>2694253</v>
@@ -35825,10 +35822,10 @@
     </row>
     <row r="719" spans="1:12">
       <c r="A719" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B719" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C719" s="5">
         <v>87474</v>
@@ -35864,10 +35861,10 @@
     </row>
     <row r="720" spans="1:12">
       <c r="A720" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B720" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C720" s="5">
         <v>3821522</v>
@@ -35903,10 +35900,10 @@
     </row>
     <row r="721" spans="1:12">
       <c r="A721" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="B721" s="4" t="s">
         <v>607</v>
-      </c>
-      <c r="B721" s="4" t="s">
-        <v>608</v>
       </c>
       <c r="C721" s="10">
         <v>3251756</v>
@@ -35941,7 +35938,7 @@
     </row>
     <row r="722" spans="1:12">
       <c r="A722" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B722" s="4" t="s">
         <v>42</v>
@@ -35979,10 +35976,10 @@
     </row>
     <row r="723" spans="1:12">
       <c r="A723" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B723" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C723" s="10">
         <v>3252311</v>
@@ -35993,7 +35990,7 @@
       <c r="E723" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F723" s="10" t="s">
+      <c r="F723" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G723" s="56">
@@ -36017,7 +36014,7 @@
     </row>
     <row r="724" spans="1:12">
       <c r="A724" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B724" s="4" t="s">
         <v>53</v>
@@ -36055,10 +36052,10 @@
     </row>
     <row r="725" spans="1:12">
       <c r="A725" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B725" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C725" s="10">
         <v>3252477</v>
@@ -36093,7 +36090,7 @@
     </row>
     <row r="726" spans="1:12">
       <c r="A726" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B726" s="4" t="s">
         <v>57</v>
@@ -36131,10 +36128,10 @@
     </row>
     <row r="727" spans="1:12">
       <c r="A727" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B727" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C727" s="10">
         <v>3252531</v>
@@ -36169,7 +36166,7 @@
     </row>
     <row r="728" spans="1:12">
       <c r="A728" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B728" s="4" t="s">
         <v>75</v>
@@ -36207,10 +36204,10 @@
     </row>
     <row r="729" spans="1:12">
       <c r="A729" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B729" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C729" s="10">
         <v>3250091</v>
@@ -36219,10 +36216,10 @@
         <v>19</v>
       </c>
       <c r="E729" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="F729" s="10" t="s">
         <v>613</v>
-      </c>
-      <c r="F729" s="10" t="s">
-        <v>614</v>
       </c>
       <c r="G729" s="56">
         <v>0</v>
@@ -36245,10 +36242,10 @@
     </row>
     <row r="730" spans="1:12">
       <c r="A730" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B730" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C730" s="10">
         <v>3252094</v>
@@ -36283,10 +36280,10 @@
     </row>
     <row r="731" spans="1:12">
       <c r="A731" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B731" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C731" s="10">
         <v>3251811</v>
@@ -36321,10 +36318,10 @@
     </row>
     <row r="732" spans="1:12">
       <c r="A732" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B732" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C732" s="10">
         <v>3252001</v>
@@ -36359,10 +36356,10 @@
     </row>
     <row r="733" spans="1:12">
       <c r="A733" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B733" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C733" s="10">
         <v>3259382</v>
@@ -36397,7 +36394,7 @@
     </row>
     <row r="734" spans="1:12">
       <c r="A734" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B734" s="4" t="s">
         <v>164</v>
@@ -36435,7 +36432,7 @@
     </row>
     <row r="735" spans="1:12">
       <c r="A735" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B735" s="4" t="s">
         <v>169</v>
@@ -36450,7 +36447,7 @@
         <v>29</v>
       </c>
       <c r="F735" s="10" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G735" s="56">
         <v>20.27</v>
@@ -36473,7 +36470,7 @@
     </row>
     <row r="736" spans="1:12">
       <c r="A736" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B736" s="4" t="s">
         <v>173</v>
@@ -36511,10 +36508,10 @@
     </row>
     <row r="737" spans="1:12">
       <c r="A737" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B737" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C737" s="10">
         <v>3251683</v>
@@ -36549,10 +36546,10 @@
     </row>
     <row r="738" spans="1:12">
       <c r="A738" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B738" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C738" s="10">
         <v>3252540</v>
@@ -36563,7 +36560,7 @@
       <c r="E738" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F738" s="10" t="s">
+      <c r="F738" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G738" s="56">
@@ -36587,10 +36584,10 @@
     </row>
     <row r="739" spans="1:12">
       <c r="A739" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B739" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C739" s="10">
         <v>3252523</v>
@@ -36601,7 +36598,7 @@
       <c r="E739" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F739" s="10" t="s">
+      <c r="F739" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G739" s="56">
@@ -36625,10 +36622,10 @@
     </row>
     <row r="740" spans="1:12">
       <c r="A740" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B740" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C740" s="10">
         <v>3252329</v>
@@ -36663,10 +36660,10 @@
     </row>
     <row r="741" spans="1:12">
       <c r="A741" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B741" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C741" s="10">
         <v>3251624</v>
@@ -36701,10 +36698,10 @@
     </row>
     <row r="742" spans="1:12">
       <c r="A742" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B742" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C742" s="10">
         <v>3252019</v>
@@ -36739,10 +36736,10 @@
     </row>
     <row r="743" spans="1:12">
       <c r="A743" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B743" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C743" s="10">
         <v>3251829</v>
@@ -36777,10 +36774,10 @@
     </row>
     <row r="744" spans="1:12">
       <c r="A744" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B744" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C744" s="10">
         <v>3252281</v>
@@ -36815,10 +36812,10 @@
     </row>
     <row r="745" spans="1:12">
       <c r="A745" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B745" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C745" s="10">
         <v>3251781</v>
@@ -36853,10 +36850,10 @@
     </row>
     <row r="746" spans="1:12">
       <c r="A746" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B746" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C746" s="10">
         <v>3251667</v>
@@ -36891,10 +36888,10 @@
     </row>
     <row r="747" spans="1:12">
       <c r="A747" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B747" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C747" s="10">
         <v>3251691</v>
@@ -36929,10 +36926,10 @@
     </row>
     <row r="748" spans="1:12">
       <c r="A748" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B748" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C748" s="10">
         <v>3251721</v>
@@ -36967,10 +36964,10 @@
     </row>
     <row r="749" spans="1:12">
       <c r="A749" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B749" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C749" s="10">
         <v>3252566</v>
@@ -37005,10 +37002,10 @@
     </row>
     <row r="750" spans="1:12">
       <c r="A750" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B750" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C750" s="10">
         <v>3258459</v>
@@ -37043,10 +37040,10 @@
     </row>
     <row r="751" spans="1:12">
       <c r="A751" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B751" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C751" s="10">
         <v>3251837</v>
@@ -37081,10 +37078,10 @@
     </row>
     <row r="752" spans="1:12">
       <c r="A752" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B752" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C752" s="10">
         <v>3252051</v>
@@ -37095,7 +37092,7 @@
       <c r="E752" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F752" s="10" t="s">
+      <c r="F752" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G752" s="56">
@@ -37119,10 +37116,10 @@
     </row>
     <row r="753" spans="1:12">
       <c r="A753" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B753" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C753" s="10">
         <v>3252043</v>
@@ -37133,7 +37130,7 @@
       <c r="E753" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F753" s="10" t="s">
+      <c r="F753" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G753" s="56">
@@ -37157,10 +37154,10 @@
     </row>
     <row r="754" spans="1:12">
       <c r="A754" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B754" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C754" s="10">
         <v>3251969</v>
@@ -37195,10 +37192,10 @@
     </row>
     <row r="755" spans="1:12">
       <c r="A755" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B755" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C755" s="10">
         <v>3251748</v>
@@ -37233,10 +37230,10 @@
     </row>
     <row r="756" spans="1:12">
       <c r="A756" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B756" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C756" s="10">
         <v>3252230</v>
@@ -37271,10 +37268,10 @@
     </row>
     <row r="757" spans="1:12">
       <c r="A757" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B757" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C757" s="10">
         <v>3252604</v>
@@ -37309,10 +37306,10 @@
     </row>
     <row r="758" spans="1:12">
       <c r="A758" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B758" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C758" s="10">
         <v>3251730</v>
@@ -37347,10 +37344,10 @@
     </row>
     <row r="759" spans="1:12">
       <c r="A759" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B759" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C759" s="10">
         <v>3252400</v>
@@ -37385,10 +37382,10 @@
     </row>
     <row r="760" spans="1:12">
       <c r="A760" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B760" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C760" s="10">
         <v>3251764</v>
@@ -37423,10 +37420,10 @@
     </row>
     <row r="761" spans="1:12">
       <c r="A761" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B761" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C761" s="10">
         <v>3251802</v>
@@ -37461,10 +37458,10 @@
     </row>
     <row r="762" spans="1:12">
       <c r="A762" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B762" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C762" s="10">
         <v>3252060</v>
@@ -37475,7 +37472,7 @@
       <c r="E762" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F762" s="10" t="s">
+      <c r="F762" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G762" s="56">
@@ -37499,10 +37496,10 @@
     </row>
     <row r="763" spans="1:12">
       <c r="A763" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B763" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C763" s="10">
         <v>3252078</v>
@@ -37513,7 +37510,7 @@
       <c r="E763" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F763" s="10" t="s">
+      <c r="F763" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G763" s="56">
@@ -37537,10 +37534,10 @@
     </row>
     <row r="764" spans="1:12">
       <c r="A764" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B764" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C764" s="10">
         <v>3252141</v>
@@ -37551,7 +37548,7 @@
       <c r="E764" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F764" s="10" t="s">
+      <c r="F764" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G764" s="56">
@@ -37575,10 +37572,10 @@
     </row>
     <row r="765" spans="1:12">
       <c r="A765" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B765" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C765" s="10">
         <v>3252299</v>
@@ -37589,7 +37586,7 @@
       <c r="E765" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F765" s="10" t="s">
+      <c r="F765" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G765" s="56">
@@ -37613,10 +37610,10 @@
     </row>
     <row r="766" spans="1:12">
       <c r="A766" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B766" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C766" s="10">
         <v>3252370</v>
@@ -37651,10 +37648,10 @@
     </row>
     <row r="767" spans="1:12">
       <c r="A767" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B767" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C767" s="10">
         <v>3252264</v>
@@ -37665,7 +37662,7 @@
       <c r="E767" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F767" s="10" t="s">
+      <c r="F767" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G767" s="56">
@@ -37689,10 +37686,10 @@
     </row>
     <row r="768" spans="1:12">
       <c r="A768" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B768" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C768" s="10">
         <v>3251641</v>
@@ -37704,7 +37701,7 @@
         <v>29</v>
       </c>
       <c r="F768" s="10" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G768" s="56">
         <v>0</v>
@@ -37727,10 +37724,10 @@
     </row>
     <row r="769" spans="1:12">
       <c r="A769" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B769" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C769" s="10">
         <v>3252353</v>
@@ -37765,10 +37762,10 @@
     </row>
     <row r="770" spans="1:12">
       <c r="A770" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B770" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C770" s="10">
         <v>3252302</v>
@@ -37803,10 +37800,10 @@
     </row>
     <row r="771" spans="1:12">
       <c r="A771" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C771" s="10">
         <v>3251845</v>
@@ -37841,10 +37838,10 @@
     </row>
     <row r="772" spans="1:12">
       <c r="A772" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B772" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C772" s="10">
         <v>3252132</v>
@@ -37855,7 +37852,7 @@
       <c r="E772" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F772" s="10" t="s">
+      <c r="F772" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G772" s="56">
@@ -37879,10 +37876,10 @@
     </row>
     <row r="773" spans="1:12">
       <c r="A773" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B773" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C773" s="10">
         <v>3251977</v>
@@ -37917,10 +37914,10 @@
     </row>
     <row r="774" spans="1:12">
       <c r="A774" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B774" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C774" s="10">
         <v>3252035</v>
@@ -37955,10 +37952,10 @@
     </row>
     <row r="775" spans="1:12">
       <c r="A775" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B775" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C775" s="10">
         <v>3251861</v>
@@ -37993,10 +37990,10 @@
     </row>
     <row r="776" spans="1:12">
       <c r="A776" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B776" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C776" s="10">
         <v>3251616</v>
@@ -38031,10 +38028,10 @@
     </row>
     <row r="777" spans="1:12">
       <c r="A777" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B777" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C777" s="10">
         <v>3251632</v>
@@ -38069,10 +38066,10 @@
     </row>
     <row r="778" spans="1:12">
       <c r="A778" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B778" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C778" s="10">
         <v>3252337</v>
@@ -38083,7 +38080,7 @@
       <c r="E778" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F778" s="10" t="s">
+      <c r="F778" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G778" s="56">
@@ -38107,10 +38104,10 @@
     </row>
     <row r="779" spans="1:12">
       <c r="A779" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B779" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C779" s="10">
         <v>3252671</v>
@@ -38121,7 +38118,7 @@
       <c r="E779" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F779" s="10" t="s">
+      <c r="F779" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G779" s="56">
@@ -38145,10 +38142,10 @@
     </row>
     <row r="780" spans="1:12">
       <c r="A780" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B780" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C780" s="10">
         <v>3258475</v>
@@ -38183,10 +38180,10 @@
     </row>
     <row r="781" spans="1:12">
       <c r="A781" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B781" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C781" s="10">
         <v>3252256</v>
@@ -38221,10 +38218,10 @@
     </row>
     <row r="782" spans="1:12">
       <c r="A782" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B782" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C782" s="10">
         <v>3252086</v>
@@ -38235,7 +38232,7 @@
       <c r="E782" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F782" s="10" t="s">
+      <c r="F782" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G782" s="56">
@@ -38259,10 +38256,10 @@
     </row>
     <row r="783" spans="1:12">
       <c r="A783" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B783" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C783" s="10">
         <v>3251934</v>
@@ -38297,10 +38294,10 @@
     </row>
     <row r="784" spans="1:12">
       <c r="A784" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B784" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C784" s="10">
         <v>3251853</v>
@@ -38335,10 +38332,10 @@
     </row>
     <row r="785" spans="1:12">
       <c r="A785" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B785" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C785" s="10">
         <v>3251870</v>
@@ -38373,10 +38370,10 @@
     </row>
     <row r="786" spans="1:12">
       <c r="A786" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B786" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C786" s="10">
         <v>3251888</v>
@@ -38411,10 +38408,10 @@
     </row>
     <row r="787" spans="1:12">
       <c r="A787" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B787" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C787" s="10">
         <v>3251926</v>
@@ -38449,10 +38446,10 @@
     </row>
     <row r="788" spans="1:12">
       <c r="A788" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B788" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C788" s="10">
         <v>3251942</v>
@@ -38487,10 +38484,10 @@
     </row>
     <row r="789" spans="1:12">
       <c r="A789" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B789" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C789" s="10">
         <v>3251659</v>
@@ -38525,10 +38522,10 @@
     </row>
     <row r="790" spans="1:12">
       <c r="A790" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B790" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C790" s="10">
         <v>3251772</v>
@@ -38563,10 +38560,10 @@
     </row>
     <row r="791" spans="1:12">
       <c r="A791" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B791" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C791" s="10">
         <v>3251896</v>
@@ -38601,13 +38598,13 @@
     </row>
     <row r="792" spans="1:12">
       <c r="A792" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B792" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B792" s="3" t="s">
-        <v>645</v>
-      </c>
       <c r="C792" s="48" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D792" s="10" t="s">
         <v>19</v>
@@ -38639,13 +38636,13 @@
     </row>
     <row r="793" spans="1:12">
       <c r="A793" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B793" s="40" t="s">
         <v>48</v>
       </c>
       <c r="C793" s="49" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D793" s="10" t="s">
         <v>19</v>
@@ -38653,7 +38650,7 @@
       <c r="E793" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F793" s="50" t="s">
+      <c r="F793" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G793" s="59">
@@ -38677,13 +38674,13 @@
     </row>
     <row r="794" spans="1:12">
       <c r="A794" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B794" s="40" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C794" s="49" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D794" s="10" t="s">
         <v>19</v>
@@ -38692,7 +38689,7 @@
         <v>13</v>
       </c>
       <c r="F794" s="52" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G794" s="59">
         <v>0</v>
@@ -38715,13 +38712,13 @@
     </row>
     <row r="795" spans="1:12">
       <c r="A795" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B795" s="40" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C795" s="49" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D795" s="10" t="s">
         <v>19</v>
@@ -38730,7 +38727,7 @@
         <v>13</v>
       </c>
       <c r="F795" s="50" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G795" s="59">
         <v>0</v>
@@ -38753,13 +38750,13 @@
     </row>
     <row r="796" spans="1:12">
       <c r="A796" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B796" s="40" t="s">
         <v>89</v>
       </c>
       <c r="C796" s="49" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D796" s="10" t="s">
         <v>19</v>
@@ -38767,7 +38764,7 @@
       <c r="E796" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F796" s="50" t="s">
+      <c r="F796" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G796" s="59">
@@ -38791,13 +38788,13 @@
     </row>
     <row r="797" spans="1:12">
       <c r="A797" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B797" s="40" t="s">
         <v>93</v>
       </c>
       <c r="C797" s="49" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D797" s="10" t="s">
         <v>19</v>
@@ -38806,7 +38803,7 @@
         <v>13</v>
       </c>
       <c r="F797" s="50" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G797" s="59">
         <v>0</v>
@@ -38829,13 +38826,13 @@
     </row>
     <row r="798" spans="1:12">
       <c r="A798" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B798" s="40" t="s">
+        <v>807</v>
+      </c>
+      <c r="C798" s="51" t="s">
         <v>808</v>
-      </c>
-      <c r="C798" s="51" t="s">
-        <v>809</v>
       </c>
       <c r="D798" s="10" t="s">
         <v>19</v>
@@ -38844,7 +38841,7 @@
         <v>13</v>
       </c>
       <c r="F798" s="50" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G798" s="59">
         <v>0</v>
@@ -38867,13 +38864,13 @@
     </row>
     <row r="799" spans="1:12">
       <c r="A799" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B799" s="40" t="s">
+        <v>809</v>
+      </c>
+      <c r="C799" s="51" t="s">
         <v>810</v>
-      </c>
-      <c r="C799" s="51" t="s">
-        <v>811</v>
       </c>
       <c r="D799" s="10" t="s">
         <v>19</v>
@@ -38882,7 +38879,7 @@
         <v>13</v>
       </c>
       <c r="F799" s="50" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G799" s="59">
         <v>0</v>
@@ -38905,13 +38902,13 @@
     </row>
     <row r="800" spans="1:12">
       <c r="A800" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B800" s="40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C800" s="49" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D800" s="10" t="s">
         <v>19</v>
@@ -38920,7 +38917,7 @@
         <v>13</v>
       </c>
       <c r="F800" s="50" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G800" s="59">
         <v>0</v>
@@ -38943,13 +38940,13 @@
     </row>
     <row r="801" spans="1:12">
       <c r="A801" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B801" s="40" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C801" s="49" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D801" s="10" t="s">
         <v>19</v>
@@ -38957,7 +38954,7 @@
       <c r="E801" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F801" s="52" t="s">
+      <c r="F801" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G801" s="59">
@@ -38981,13 +38978,13 @@
     </row>
     <row r="802" spans="1:12">
       <c r="A802" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B802" s="40" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C802" s="49" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D802" s="10" t="s">
         <v>19</v>
@@ -38996,7 +38993,7 @@
         <v>13</v>
       </c>
       <c r="F802" s="52" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G802" s="59">
         <v>0</v>
@@ -39019,13 +39016,13 @@
     </row>
     <row r="803" spans="1:12">
       <c r="A803" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B803" s="40" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C803" s="49" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D803" s="10" t="s">
         <v>19</v>
@@ -39057,13 +39054,13 @@
     </row>
     <row r="804" spans="1:12">
       <c r="A804" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B804" s="40" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C804" s="49" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D804" s="10" t="s">
         <v>19</v>
@@ -39072,7 +39069,7 @@
         <v>13</v>
       </c>
       <c r="F804" s="52" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G804" s="59">
         <v>0</v>
@@ -39095,13 +39092,13 @@
     </row>
     <row r="805" spans="1:12">
       <c r="A805" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B805" s="40" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C805" s="49" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D805" s="10" t="s">
         <v>19</v>
@@ -39133,13 +39130,13 @@
     </row>
     <row r="806" spans="1:12">
       <c r="A806" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B806" s="40" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C806" s="49" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D806" s="10" t="s">
         <v>19</v>
@@ -39171,13 +39168,13 @@
     </row>
     <row r="807" spans="1:12">
       <c r="A807" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B807" s="40" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C807" s="49" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D807" s="10" t="s">
         <v>19</v>
@@ -39209,13 +39206,13 @@
     </row>
     <row r="808" spans="1:12">
       <c r="A808" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B808" s="40" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C808" s="49" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D808" s="10" t="s">
         <v>19</v>
@@ -39223,7 +39220,7 @@
       <c r="E808" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F808" s="50" t="s">
+      <c r="F808" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G808" s="59">
@@ -39247,13 +39244,13 @@
     </row>
     <row r="809" spans="1:12">
       <c r="A809" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B809" s="40" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C809" s="49" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D809" s="10" t="s">
         <v>19</v>
@@ -39262,7 +39259,7 @@
         <v>13</v>
       </c>
       <c r="F809" s="52" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G809" s="59">
         <v>0</v>
@@ -39285,13 +39282,13 @@
     </row>
     <row r="810" spans="1:12">
       <c r="A810" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B810" s="40" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C810" s="49" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D810" s="10" t="s">
         <v>19</v>
@@ -39300,7 +39297,7 @@
         <v>13</v>
       </c>
       <c r="F810" s="50" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G810" s="59">
         <v>0</v>
@@ -39323,13 +39320,13 @@
     </row>
     <row r="811" spans="1:12">
       <c r="A811" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B811" s="40" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C811" s="49" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D811" s="10" t="s">
         <v>19</v>
@@ -39338,7 +39335,7 @@
         <v>13</v>
       </c>
       <c r="F811" s="52" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G811" s="59">
         <v>0</v>
@@ -39361,13 +39358,13 @@
     </row>
     <row r="812" spans="1:12">
       <c r="A812" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B812" s="40" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C812" s="49" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D812" s="10" t="s">
         <v>19</v>
@@ -39375,7 +39372,7 @@
       <c r="E812" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F812" s="50" t="s">
+      <c r="F812" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G812" s="59">
@@ -39399,13 +39396,13 @@
     </row>
     <row r="813" spans="1:12">
       <c r="A813" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B813" s="40" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C813" s="49" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D813" s="10" t="s">
         <v>19</v>
@@ -39414,7 +39411,7 @@
         <v>13</v>
       </c>
       <c r="F813" s="52" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G813" s="59">
         <v>0</v>
@@ -39437,13 +39434,13 @@
     </row>
     <row r="814" spans="1:12">
       <c r="A814" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B814" s="40" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C814" s="49" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D814" s="10" t="s">
         <v>19</v>
@@ -39452,7 +39449,7 @@
         <v>13</v>
       </c>
       <c r="F814" s="52" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G814" s="59">
         <v>0</v>
@@ -39475,13 +39472,13 @@
     </row>
     <row r="815" spans="1:12">
       <c r="A815" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B815" s="40" t="s">
+        <v>811</v>
+      </c>
+      <c r="C815" s="49" t="s">
         <v>812</v>
-      </c>
-      <c r="C815" s="49" t="s">
-        <v>813</v>
       </c>
       <c r="D815" s="10" t="s">
         <v>19</v>
@@ -39490,7 +39487,7 @@
         <v>13</v>
       </c>
       <c r="F815" s="52" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G815" s="59">
         <v>0</v>
@@ -39513,7 +39510,7 @@
     </row>
     <row r="816" spans="1:12">
       <c r="A816" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B816" s="4" t="s">
         <v>107</v>
@@ -39551,16 +39548,16 @@
     </row>
     <row r="817" spans="1:12">
       <c r="A817" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B817" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C817" s="20" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D817" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E817" s="10" t="s">
         <v>20</v>
@@ -39589,22 +39586,22 @@
     </row>
     <row r="818" spans="1:12">
       <c r="A818" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B818" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="C818" s="20" t="s">
         <v>712</v>
       </c>
-      <c r="C818" s="20" t="s">
+      <c r="D818" s="10" t="s">
         <v>713</v>
-      </c>
-      <c r="D818" s="10" t="s">
-        <v>714</v>
       </c>
       <c r="E818" s="10" t="s">
         <v>125</v>
       </c>
       <c r="F818" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G818" s="55">
         <v>0</v>
@@ -39627,13 +39624,13 @@
     </row>
     <row r="819" spans="1:12">
       <c r="A819" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B819" s="41" t="s">
         <v>32</v>
       </c>
       <c r="C819" s="5" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D819" s="10" t="s">
         <v>19</v>
@@ -39642,7 +39639,7 @@
         <v>13</v>
       </c>
       <c r="F819" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G819" s="55">
         <v>117240.88</v>
@@ -39665,16 +39662,16 @@
     </row>
     <row r="820" spans="1:12">
       <c r="A820" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B820" s="41" t="s">
+        <v>657</v>
+      </c>
+      <c r="C820" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="C820" s="5" t="s">
-        <v>659</v>
-      </c>
       <c r="D820" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E820" s="10" t="s">
         <v>20</v>
@@ -39695,13 +39692,13 @@
     </row>
     <row r="821" spans="1:12">
       <c r="A821" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B821" s="41" t="s">
+        <v>659</v>
+      </c>
+      <c r="C821" s="5" t="s">
         <v>660</v>
-      </c>
-      <c r="C821" s="5" t="s">
-        <v>661</v>
       </c>
       <c r="D821" s="10" t="s">
         <v>19</v>
@@ -39733,22 +39730,22 @@
     </row>
     <row r="822" spans="1:12">
       <c r="A822" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B822" s="53" t="s">
+        <v>716</v>
+      </c>
+      <c r="C822" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="C822" s="5" t="s">
-        <v>718</v>
-      </c>
       <c r="D822" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E822" s="10" t="s">
         <v>125</v>
       </c>
       <c r="F822" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G822" s="55">
         <v>0</v>
@@ -39771,13 +39768,13 @@
     </row>
     <row r="823" spans="1:12">
       <c r="A823" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B823" s="3" t="s">
         <v>138</v>
       </c>
       <c r="C823" s="42" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D823" s="10" t="s">
         <v>19</v>
@@ -39801,13 +39798,13 @@
     </row>
     <row r="824" spans="1:12">
       <c r="A824" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B824" s="43" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C824" s="44" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D824" s="10" t="s">
         <v>19</v>
@@ -39815,7 +39812,7 @@
       <c r="E824" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F824" s="10" t="s">
+      <c r="F824" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G824" s="55">
@@ -39839,13 +39836,13 @@
     </row>
     <row r="825" spans="1:12">
       <c r="A825" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B825" s="43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C825" s="44" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D825" s="10" t="s">
         <v>19</v>
@@ -39853,7 +39850,7 @@
       <c r="E825" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F825" s="10" t="s">
+      <c r="F825" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G825" s="55">
@@ -39877,13 +39874,13 @@
     </row>
     <row r="826" spans="1:12">
       <c r="A826" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B826" s="43" t="s">
+        <v>664</v>
+      </c>
+      <c r="C826" s="44" t="s">
         <v>665</v>
-      </c>
-      <c r="C826" s="44" t="s">
-        <v>666</v>
       </c>
       <c r="D826" s="10" t="s">
         <v>19</v>
@@ -39907,13 +39904,13 @@
     </row>
     <row r="827" spans="1:12">
       <c r="A827" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B827" s="41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C827" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D827" s="10" t="s">
         <v>19</v>
@@ -39945,13 +39942,13 @@
     </row>
     <row r="828" spans="1:12">
       <c r="A828" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B828" s="41" t="s">
+        <v>667</v>
+      </c>
+      <c r="C828" s="5" t="s">
         <v>668</v>
-      </c>
-      <c r="C828" s="5" t="s">
-        <v>669</v>
       </c>
       <c r="D828" s="10" t="s">
         <v>19</v>
@@ -39959,7 +39956,7 @@
       <c r="E828" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F828" s="10" t="s">
+      <c r="F828" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G828" s="55">
@@ -39983,22 +39980,22 @@
     </row>
     <row r="829" spans="1:12">
       <c r="A829" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B829" s="41" t="s">
+        <v>718</v>
+      </c>
+      <c r="C829" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C829" s="5" t="s">
-        <v>720</v>
-      </c>
       <c r="D829" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E829" s="10" t="s">
         <v>125</v>
       </c>
       <c r="F829" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G829" s="55">
         <v>0</v>
@@ -40021,22 +40018,22 @@
     </row>
     <row r="830" spans="1:12">
       <c r="A830" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B830" s="41" t="s">
+        <v>720</v>
+      </c>
+      <c r="C830" s="20" t="s">
         <v>721</v>
       </c>
-      <c r="C830" s="20" t="s">
-        <v>722</v>
-      </c>
       <c r="D830" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E830" s="10" t="s">
         <v>125</v>
       </c>
       <c r="F830" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G830" s="55">
         <v>0</v>
@@ -40059,16 +40056,16 @@
     </row>
     <row r="831" spans="1:12">
       <c r="A831" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B831" s="41" t="s">
+        <v>669</v>
+      </c>
+      <c r="C831" s="45" t="s">
         <v>670</v>
       </c>
-      <c r="C831" s="45" t="s">
-        <v>671</v>
-      </c>
       <c r="D831" s="10" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E831" s="10" t="s">
         <v>20</v>
@@ -40097,13 +40094,13 @@
     </row>
     <row r="832" spans="1:12">
       <c r="A832" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B832" s="41" t="s">
+        <v>671</v>
+      </c>
+      <c r="C832" s="45" t="s">
         <v>672</v>
-      </c>
-      <c r="C832" s="45" t="s">
-        <v>673</v>
       </c>
       <c r="D832" s="10" t="s">
         <v>19</v>
@@ -40111,7 +40108,7 @@
       <c r="E832" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F832" s="10" t="s">
+      <c r="F832" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G832" s="55">
@@ -40135,13 +40132,13 @@
     </row>
     <row r="833" spans="1:12">
       <c r="A833" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B833" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="C833" s="42" t="s">
         <v>674</v>
-      </c>
-      <c r="C833" s="42" t="s">
-        <v>675</v>
       </c>
       <c r="D833" s="10" t="s">
         <v>19</v>
@@ -40173,13 +40170,13 @@
     </row>
     <row r="834" spans="1:12">
       <c r="A834" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B834" s="41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C834" s="45" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D834" s="10" t="s">
         <v>19</v>
@@ -40205,13 +40202,13 @@
     </row>
     <row r="835" spans="1:12">
       <c r="A835" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B835" s="41" t="s">
+        <v>676</v>
+      </c>
+      <c r="C835" s="45" t="s">
         <v>677</v>
-      </c>
-      <c r="C835" s="45" t="s">
-        <v>678</v>
       </c>
       <c r="D835" s="10" t="s">
         <v>46</v>
@@ -40237,13 +40234,13 @@
     </row>
     <row r="836" spans="1:12">
       <c r="A836" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B836" s="41" t="s">
+        <v>678</v>
+      </c>
+      <c r="C836" s="20" t="s">
         <v>679</v>
-      </c>
-      <c r="C836" s="20" t="s">
-        <v>680</v>
       </c>
       <c r="D836" s="10" t="s">
         <v>19</v>
@@ -40267,13 +40264,13 @@
     </row>
     <row r="837" spans="1:12">
       <c r="A837" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B837" s="41" t="s">
+        <v>680</v>
+      </c>
+      <c r="C837" s="20" t="s">
         <v>681</v>
-      </c>
-      <c r="C837" s="20" t="s">
-        <v>682</v>
       </c>
       <c r="D837" s="10" t="s">
         <v>19</v>
@@ -40281,7 +40278,7 @@
       <c r="E837" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F837" s="10" t="s">
+      <c r="F837" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G837" s="55">
@@ -40305,13 +40302,13 @@
     </row>
     <row r="838" spans="1:12">
       <c r="A838" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B838" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="C838" s="20" t="s">
         <v>683</v>
-      </c>
-      <c r="C838" s="20" t="s">
-        <v>684</v>
       </c>
       <c r="D838" s="10" t="s">
         <v>19</v>
@@ -40343,13 +40340,13 @@
     </row>
     <row r="839" spans="1:12">
       <c r="A839" s="41" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B839" s="41" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C839" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D839" s="10" t="s">
         <v>19</v>
@@ -40381,13 +40378,13 @@
     </row>
     <row r="840" spans="1:12">
       <c r="A840" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B840" s="12" t="s">
         <v>147</v>
       </c>
       <c r="C840" s="20" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D840" s="10" t="s">
         <v>19</v>
@@ -40395,7 +40392,7 @@
       <c r="E840" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F840" s="10" t="s">
+      <c r="F840" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G840" s="55">
@@ -40419,13 +40416,13 @@
     </row>
     <row r="841" spans="1:12">
       <c r="A841" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B841" s="41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C841" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D841" s="10" t="s">
         <v>19</v>
@@ -40433,7 +40430,7 @@
       <c r="E841" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F841" s="10" t="s">
+      <c r="F841" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G841" s="55">
@@ -40457,22 +40454,22 @@
     </row>
     <row r="842" spans="1:12">
       <c r="A842" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B842" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C842" s="46" t="s">
         <v>689</v>
       </c>
-      <c r="C842" s="46" t="s">
-        <v>690</v>
-      </c>
       <c r="D842" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E842" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F842" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G842" s="55">
         <v>0</v>
@@ -40495,13 +40492,13 @@
     </row>
     <row r="843" spans="1:12">
       <c r="A843" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B843" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C843" s="46" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D843" s="10" t="s">
         <v>19</v>
@@ -40509,7 +40506,7 @@
       <c r="E843" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F843" s="10" t="s">
+      <c r="F843" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G843" s="55">

--- a/dados/Campanha Captação.xlsx
+++ b/dados/Campanha Captação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BRUNO.SILVA\Downloads\App campanha\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D23626B-A3F6-450F-AB32-F79E193F257B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8F5233-42B2-4267-A9C9-681D235C0E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28875" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{65BC80B7-CA5D-453E-A132-5DB34208399A}"/>
+    <workbookView xWindow="75" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{65BC80B7-CA5D-453E-A132-5DB34208399A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$843</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$858</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4358" uniqueCount="829">
   <si>
     <t>Corretora</t>
   </si>
@@ -2481,6 +2481,54 @@
   </si>
   <si>
     <t>2245369</t>
+  </si>
+  <si>
+    <t>Ágora</t>
+  </si>
+  <si>
+    <t>Ampiezza Clinicas Integradas LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruno Cesar Pesquero Ponce Jaime </t>
+  </si>
+  <si>
+    <t>IMC Construções LTDA</t>
+  </si>
+  <si>
+    <t>11230050</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">J &amp; M Consultoria Empresarial LTDA  </t>
+  </si>
+  <si>
+    <t>José Henrique</t>
+  </si>
+  <si>
+    <t>Luis Fernando Leite Sabino de Oliveira</t>
+  </si>
+  <si>
+    <t>Márcia Carvalho Gazeta</t>
+  </si>
+  <si>
+    <t>10989041</t>
+  </si>
+  <si>
+    <t>Otávio Alves Forte</t>
+  </si>
+  <si>
+    <t>11339353</t>
+  </si>
+  <si>
+    <t>Silede Satyro de Sá Ribeiro</t>
+  </si>
+  <si>
+    <t>6116342</t>
+  </si>
+  <si>
+    <t>Norton Jr.</t>
   </si>
 </sst>
 </file>
@@ -8179,7 +8227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}">
-  <dimension ref="A1:L843"/>
+  <dimension ref="A1:L858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -39510,195 +39558,193 @@
     </row>
     <row r="816" spans="1:12">
       <c r="A816" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="B816" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C816" s="5">
-        <v>5637768</v>
-      </c>
-      <c r="D816" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E816" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F816" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G816" s="54">
-        <v>110396.14</v>
-      </c>
-      <c r="H816" s="54">
-        <v>111483.66</v>
-      </c>
-      <c r="I816" s="54">
-        <v>108075.3</v>
-      </c>
-      <c r="J816" s="54">
-        <v>108551.75</v>
-      </c>
-      <c r="K816" s="54">
-        <v>105789.27</v>
-      </c>
-      <c r="L816" s="54">
-        <v>105789.27</v>
+        <v>813</v>
+      </c>
+      <c r="B816" s="40" t="s">
+        <v>530</v>
+      </c>
+      <c r="C816" s="49">
+        <v>11005560</v>
+      </c>
+      <c r="D816" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E816" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F816" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G816" s="59">
+        <v>3547349.92</v>
+      </c>
+      <c r="H816" s="59">
+        <v>5584985.7199999997</v>
+      </c>
+      <c r="I816" s="59">
+        <v>5629373.79</v>
+      </c>
+      <c r="J816" s="59">
+        <v>5672338.3700000001</v>
+      </c>
+      <c r="K816" s="59">
+        <v>5736847.6799999997</v>
+      </c>
+      <c r="L816" s="59">
+        <v>5778639.4199999999</v>
       </c>
     </row>
     <row r="817" spans="1:12">
-      <c r="A817" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="B817" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C817" s="20" t="s">
-        <v>656</v>
+      <c r="A817" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B817" s="40" t="s">
+        <v>814</v>
+      </c>
+      <c r="C817" s="49">
+        <v>15667976</v>
       </c>
       <c r="D817" s="10" t="s">
-        <v>710</v>
+        <v>133</v>
       </c>
       <c r="E817" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F817" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G817" s="55">
-        <v>62476.1</v>
-      </c>
-      <c r="H817" s="55">
-        <v>63892.32</v>
-      </c>
-      <c r="I817" s="55">
-        <v>64778.33</v>
-      </c>
-      <c r="J817" s="55">
-        <v>65726.7</v>
-      </c>
-      <c r="K817" s="55">
-        <v>67206.37</v>
-      </c>
-      <c r="L817" s="55">
-        <v>67206.37</v>
+        <v>13</v>
+      </c>
+      <c r="F817" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="G817" s="59"/>
+      <c r="H817" s="59">
+        <v>0</v>
+      </c>
+      <c r="I817" s="59">
+        <v>601667.09</v>
+      </c>
+      <c r="J817" s="59">
+        <v>608802.88</v>
+      </c>
+      <c r="K817" s="59">
+        <v>814501</v>
+      </c>
+      <c r="L817" s="59">
+        <v>820692.24</v>
       </c>
     </row>
     <row r="818" spans="1:12">
-      <c r="A818" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="B818" s="12" t="s">
-        <v>711</v>
-      </c>
-      <c r="C818" s="20" t="s">
-        <v>712</v>
+      <c r="A818" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B818" s="40" t="s">
+        <v>815</v>
+      </c>
+      <c r="C818" s="49">
+        <v>10940590</v>
       </c>
       <c r="D818" s="10" t="s">
-        <v>713</v>
+        <v>19</v>
       </c>
       <c r="E818" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F818" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="G818" s="55">
-        <v>0</v>
-      </c>
-      <c r="H818" s="55">
-        <v>0</v>
-      </c>
-      <c r="I818" s="55">
-        <v>0</v>
-      </c>
-      <c r="J818" s="55">
-        <v>0</v>
-      </c>
-      <c r="K818" s="55">
-        <v>0</v>
-      </c>
-      <c r="L818" s="55">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F818" s="52" t="s">
+        <v>692</v>
+      </c>
+      <c r="G818" s="59">
+        <v>693260.12</v>
+      </c>
+      <c r="H818" s="59">
+        <v>693384.27</v>
+      </c>
+      <c r="I818" s="59">
+        <v>703513.4</v>
+      </c>
+      <c r="J818" s="59">
+        <v>712240.78</v>
+      </c>
+      <c r="K818" s="59">
+        <v>0</v>
+      </c>
+      <c r="L818" s="59">
+        <v>73.38</v>
       </c>
     </row>
     <row r="819" spans="1:12">
-      <c r="A819" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B819" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C819" s="5" t="s">
-        <v>715</v>
+      <c r="A819" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B819" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="C819" s="49">
+        <v>11830618</v>
       </c>
       <c r="D819" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E819" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F819" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G819" s="59"/>
+      <c r="H819" s="59"/>
+      <c r="I819" s="59"/>
+      <c r="J819" s="59"/>
+      <c r="K819" s="59">
+        <v>181600.49</v>
+      </c>
+      <c r="L819" s="59">
+        <v>183389.67</v>
+      </c>
+    </row>
+    <row r="820" spans="1:12">
+      <c r="A820" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B820" s="40" t="s">
+        <v>816</v>
+      </c>
+      <c r="C820" s="49" t="s">
+        <v>817</v>
+      </c>
+      <c r="D820" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E820" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F819" s="10" t="s">
-        <v>697</v>
-      </c>
-      <c r="G819" s="55">
-        <v>117240.88</v>
-      </c>
-      <c r="H819" s="55">
-        <v>120226.22</v>
-      </c>
-      <c r="I819" s="55">
-        <v>122541.13</v>
-      </c>
-      <c r="J819" s="55">
-        <v>125168.34</v>
-      </c>
-      <c r="K819" s="55">
-        <v>131942.32</v>
-      </c>
-      <c r="L819" s="55">
-        <v>131942.32</v>
-      </c>
-    </row>
-    <row r="820" spans="1:12">
-      <c r="A820" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B820" s="41" t="s">
-        <v>657</v>
-      </c>
-      <c r="C820" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="D820" s="10" t="s">
-        <v>710</v>
-      </c>
-      <c r="E820" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F820" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G820" s="55"/>
-      <c r="H820" s="55"/>
-      <c r="I820" s="55"/>
-      <c r="J820" s="55"/>
-      <c r="K820" s="55">
-        <v>1000</v>
-      </c>
-      <c r="L820" s="55">
-        <v>1000</v>
+      <c r="F820" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="G820" s="59">
+        <v>0</v>
+      </c>
+      <c r="H820" s="59">
+        <v>0</v>
+      </c>
+      <c r="I820" s="59">
+        <v>0</v>
+      </c>
+      <c r="J820" s="59">
+        <v>0</v>
+      </c>
+      <c r="K820" s="59">
+        <v>0</v>
+      </c>
+      <c r="L820" s="59" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="821" spans="1:12">
-      <c r="A821" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B821" s="41" t="s">
-        <v>659</v>
-      </c>
-      <c r="C821" s="5" t="s">
-        <v>660</v>
+      <c r="A821" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B821" s="40" t="s">
+        <v>819</v>
+      </c>
+      <c r="C821" s="49">
+        <v>10982276</v>
       </c>
       <c r="D821" s="10" t="s">
         <v>19</v>
@@ -39706,105 +39752,113 @@
       <c r="E821" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F821" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G821" s="55">
-        <v>0</v>
-      </c>
-      <c r="H821" s="55">
-        <v>0</v>
-      </c>
-      <c r="I821" s="55">
-        <v>0</v>
-      </c>
-      <c r="J821" s="55">
-        <v>0</v>
-      </c>
-      <c r="K821" s="55">
-        <v>0</v>
-      </c>
-      <c r="L821" s="55">
-        <v>0</v>
+      <c r="F821" s="52" t="s">
+        <v>820</v>
+      </c>
+      <c r="G821" s="59">
+        <v>9267874.1799999997</v>
+      </c>
+      <c r="H821" s="59">
+        <v>8895735.3000000007</v>
+      </c>
+      <c r="I821" s="59">
+        <v>9108114.6199999992</v>
+      </c>
+      <c r="J821" s="59">
+        <v>9228957.0899999999</v>
+      </c>
+      <c r="K821" s="59">
+        <v>9118300.2799999993</v>
+      </c>
+      <c r="L821" s="59">
+        <v>9083530.4299999997</v>
       </c>
     </row>
     <row r="822" spans="1:12">
-      <c r="A822" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B822" s="53" t="s">
-        <v>716</v>
-      </c>
-      <c r="C822" s="5" t="s">
-        <v>717</v>
+      <c r="A822" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B822" s="40" t="s">
+        <v>693</v>
+      </c>
+      <c r="C822" s="49">
+        <v>12307245</v>
       </c>
       <c r="D822" s="10" t="s">
-        <v>713</v>
+        <v>19</v>
       </c>
       <c r="E822" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F822" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="G822" s="55">
-        <v>0</v>
-      </c>
-      <c r="H822" s="55">
-        <v>0</v>
-      </c>
-      <c r="I822" s="55">
-        <v>0</v>
-      </c>
-      <c r="J822" s="55">
-        <v>0</v>
-      </c>
-      <c r="K822" s="55">
-        <v>0</v>
-      </c>
-      <c r="L822" s="55">
+        <v>13</v>
+      </c>
+      <c r="F822" s="52" t="s">
+        <v>692</v>
+      </c>
+      <c r="G822" s="59">
+        <v>0</v>
+      </c>
+      <c r="H822" s="59">
+        <v>0</v>
+      </c>
+      <c r="I822" s="59">
+        <v>0</v>
+      </c>
+      <c r="J822" s="59">
+        <v>0</v>
+      </c>
+      <c r="K822" s="59">
+        <v>0</v>
+      </c>
+      <c r="L822" s="59">
         <v>0</v>
       </c>
     </row>
     <row r="823" spans="1:12">
-      <c r="A823" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B823" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C823" s="42" t="s">
-        <v>661</v>
+      <c r="A823" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B823" s="40" t="s">
+        <v>821</v>
+      </c>
+      <c r="C823" s="49">
+        <v>3844136</v>
       </c>
       <c r="D823" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E823" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F823" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G823" s="55"/>
-      <c r="H823" s="55"/>
-      <c r="I823" s="55"/>
-      <c r="J823" s="55"/>
-      <c r="K823" s="55">
-        <v>0</v>
-      </c>
-      <c r="L823" s="55">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="F823" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G823" s="59">
+        <v>57774.21</v>
+      </c>
+      <c r="H823" s="59">
+        <v>57301.25</v>
+      </c>
+      <c r="I823" s="59">
+        <v>58201.73</v>
+      </c>
+      <c r="J823" s="59">
+        <v>58766.74</v>
+      </c>
+      <c r="K823" s="59">
+        <v>59670.1</v>
+      </c>
+      <c r="L823" s="59">
+        <v>60505.8</v>
       </c>
     </row>
     <row r="824" spans="1:12">
-      <c r="A824" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B824" s="43" t="s">
-        <v>545</v>
-      </c>
-      <c r="C824" s="44" t="s">
-        <v>662</v>
+      <c r="A824" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B824" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C824" s="49">
+        <v>10936630</v>
       </c>
       <c r="D824" s="10" t="s">
         <v>19</v>
@@ -39812,37 +39866,37 @@
       <c r="E824" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F824" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G824" s="55">
-        <v>142799.35</v>
-      </c>
-      <c r="H824" s="55">
-        <v>200631.22</v>
-      </c>
-      <c r="I824" s="55">
-        <v>260124.32</v>
-      </c>
-      <c r="J824" s="55">
-        <v>313433.53000000003</v>
-      </c>
-      <c r="K824" s="55">
-        <v>315102</v>
-      </c>
-      <c r="L824" s="55">
-        <v>315102</v>
+      <c r="F824" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="G824" s="59">
+        <v>0</v>
+      </c>
+      <c r="H824" s="59">
+        <v>0</v>
+      </c>
+      <c r="I824" s="59">
+        <v>0</v>
+      </c>
+      <c r="J824" s="59">
+        <v>0</v>
+      </c>
+      <c r="K824" s="59">
+        <v>0</v>
+      </c>
+      <c r="L824" s="59">
+        <v>0</v>
       </c>
     </row>
     <row r="825" spans="1:12">
-      <c r="A825" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B825" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="C825" s="44" t="s">
-        <v>663</v>
+      <c r="A825" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B825" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C825" s="49">
+        <v>10944986</v>
       </c>
       <c r="D825" s="10" t="s">
         <v>19</v>
@@ -39850,67 +39904,75 @@
       <c r="E825" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F825" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G825" s="55">
-        <v>0</v>
-      </c>
-      <c r="H825" s="55">
-        <v>0</v>
-      </c>
-      <c r="I825" s="55">
-        <v>17721.21</v>
-      </c>
-      <c r="J825" s="55">
-        <v>17737.8</v>
-      </c>
-      <c r="K825" s="55">
-        <v>17924.73</v>
-      </c>
-      <c r="L825" s="55">
-        <v>17924.73</v>
+      <c r="F825" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="G825" s="59">
+        <v>0</v>
+      </c>
+      <c r="H825" s="59">
+        <v>0</v>
+      </c>
+      <c r="I825" s="59">
+        <v>0</v>
+      </c>
+      <c r="J825" s="59">
+        <v>0</v>
+      </c>
+      <c r="K825" s="59">
+        <v>0</v>
+      </c>
+      <c r="L825" s="59">
+        <v>0</v>
       </c>
     </row>
     <row r="826" spans="1:12">
-      <c r="A826" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B826" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="C826" s="44" t="s">
-        <v>665</v>
+      <c r="A826" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B826" s="40" t="s">
+        <v>822</v>
+      </c>
+      <c r="C826" s="49">
+        <v>11071318</v>
       </c>
       <c r="D826" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E826" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F826" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G826" s="55"/>
-      <c r="H826" s="55"/>
-      <c r="I826" s="55"/>
-      <c r="J826" s="55"/>
-      <c r="K826" s="55">
-        <v>0</v>
-      </c>
-      <c r="L826" s="55">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F826" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G826" s="59">
+        <v>388119.7</v>
+      </c>
+      <c r="H826" s="59">
+        <v>453391.34</v>
+      </c>
+      <c r="I826" s="59">
+        <v>458010.44</v>
+      </c>
+      <c r="J826" s="59">
+        <v>463159.45</v>
+      </c>
+      <c r="K826" s="59">
+        <v>467745.11</v>
+      </c>
+      <c r="L826" s="59">
+        <v>525370.68000000005</v>
       </c>
     </row>
     <row r="827" spans="1:12">
-      <c r="A827" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B827" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="C827" s="5" t="s">
-        <v>666</v>
+      <c r="A827" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B827" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="C827" s="49" t="s">
+        <v>823</v>
       </c>
       <c r="D827" s="10" t="s">
         <v>19</v>
@@ -39918,37 +39980,37 @@
       <c r="E827" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F827" s="10" t="s">
+      <c r="F827" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="G827" s="55">
-        <v>0</v>
-      </c>
-      <c r="H827" s="55">
-        <v>0</v>
-      </c>
-      <c r="I827" s="55">
-        <v>0</v>
-      </c>
-      <c r="J827" s="55">
-        <v>0</v>
-      </c>
-      <c r="K827" s="55">
-        <v>0</v>
-      </c>
-      <c r="L827" s="55">
-        <v>0</v>
+      <c r="G827" s="59">
+        <v>0</v>
+      </c>
+      <c r="H827" s="59">
+        <v>0</v>
+      </c>
+      <c r="I827" s="59">
+        <v>0</v>
+      </c>
+      <c r="J827" s="59">
+        <v>0</v>
+      </c>
+      <c r="K827" s="59">
+        <v>0</v>
+      </c>
+      <c r="L827" s="59" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="828" spans="1:12">
-      <c r="A828" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B828" s="41" t="s">
-        <v>667</v>
-      </c>
-      <c r="C828" s="5" t="s">
-        <v>668</v>
+      <c r="A828" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B828" s="40" t="s">
+        <v>824</v>
+      </c>
+      <c r="C828" s="49">
+        <v>11026371</v>
       </c>
       <c r="D828" s="10" t="s">
         <v>19</v>
@@ -39956,207 +40018,207 @@
       <c r="E828" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F828" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G828" s="55">
-        <v>0</v>
-      </c>
-      <c r="H828" s="55">
-        <v>0</v>
-      </c>
-      <c r="I828" s="55">
-        <v>161361.94</v>
-      </c>
-      <c r="J828" s="55">
-        <v>163040.57999999999</v>
-      </c>
-      <c r="K828" s="55">
-        <v>162864.82999999999</v>
-      </c>
-      <c r="L828" s="55">
-        <v>162864.82999999999</v>
+      <c r="F828" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="G828" s="59">
+        <v>4007767.83</v>
+      </c>
+      <c r="H828" s="59">
+        <v>4183923.59</v>
+      </c>
+      <c r="I828" s="59">
+        <v>4337170.46</v>
+      </c>
+      <c r="J828" s="59">
+        <v>4490316.03</v>
+      </c>
+      <c r="K828" s="59">
+        <v>0</v>
+      </c>
+      <c r="L828" s="59">
+        <v>367.7</v>
       </c>
     </row>
     <row r="829" spans="1:12">
-      <c r="A829" s="41" t="s">
-        <v>655</v>
-      </c>
-      <c r="B829" s="41" t="s">
-        <v>718</v>
-      </c>
-      <c r="C829" s="5" t="s">
-        <v>719</v>
+      <c r="A829" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B829" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="C829" s="49" t="s">
+        <v>825</v>
       </c>
       <c r="D829" s="10" t="s">
-        <v>713</v>
+        <v>19</v>
       </c>
       <c r="E829" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F829" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="G829" s="55">
-        <v>0</v>
-      </c>
-      <c r="H829" s="55">
-        <v>0</v>
-      </c>
-      <c r="I829" s="55">
-        <v>0</v>
-      </c>
-      <c r="J829" s="55">
-        <v>0</v>
-      </c>
-      <c r="K829" s="55">
-        <v>0</v>
-      </c>
-      <c r="L829" s="55">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F829" s="52" t="s">
+        <v>692</v>
+      </c>
+      <c r="G829" s="59">
+        <v>91444.94</v>
+      </c>
+      <c r="H829" s="59">
+        <v>92329.17</v>
+      </c>
+      <c r="I829" s="59">
+        <v>94752.2</v>
+      </c>
+      <c r="J829" s="59">
+        <v>96388.33</v>
+      </c>
+      <c r="K829" s="59">
+        <v>98887.16</v>
+      </c>
+      <c r="L829" s="59" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="830" spans="1:12">
-      <c r="A830" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="B830" s="41" t="s">
-        <v>720</v>
-      </c>
-      <c r="C830" s="20" t="s">
-        <v>721</v>
+      <c r="A830" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B830" s="40" t="s">
+        <v>826</v>
+      </c>
+      <c r="C830" s="49" t="s">
+        <v>827</v>
       </c>
       <c r="D830" s="10" t="s">
-        <v>713</v>
+        <v>19</v>
       </c>
       <c r="E830" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F830" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="G830" s="55">
-        <v>0</v>
-      </c>
-      <c r="H830" s="55">
-        <v>0</v>
-      </c>
-      <c r="I830" s="55">
-        <v>0</v>
-      </c>
-      <c r="J830" s="55">
-        <v>0</v>
-      </c>
-      <c r="K830" s="55">
-        <v>0</v>
-      </c>
-      <c r="L830" s="55">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="F830" s="52" t="s">
+        <v>828</v>
+      </c>
+      <c r="G830" s="59">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="H830" s="59">
+        <v>0</v>
+      </c>
+      <c r="I830" s="59">
+        <v>0</v>
+      </c>
+      <c r="J830" s="59">
+        <v>0</v>
+      </c>
+      <c r="K830" s="59">
+        <v>0</v>
+      </c>
+      <c r="L830" s="59" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="831" spans="1:12">
-      <c r="A831" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="B831" s="41" t="s">
-        <v>669</v>
-      </c>
-      <c r="C831" s="45" t="s">
-        <v>670</v>
-      </c>
-      <c r="D831" s="10" t="s">
-        <v>710</v>
-      </c>
-      <c r="E831" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F831" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G831" s="55">
-        <v>116648.98</v>
-      </c>
-      <c r="H831" s="55">
-        <v>118474.12</v>
-      </c>
-      <c r="I831" s="55">
-        <v>118915.05</v>
-      </c>
-      <c r="J831" s="55">
-        <v>120933.46</v>
-      </c>
-      <c r="K831" s="55">
-        <v>121791.84</v>
-      </c>
-      <c r="L831" s="55">
-        <v>121791.84</v>
+      <c r="A831" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="B831" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C831" s="5">
+        <v>5637768</v>
+      </c>
+      <c r="D831" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E831" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F831" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G831" s="54">
+        <v>110396.14</v>
+      </c>
+      <c r="H831" s="54">
+        <v>111483.66</v>
+      </c>
+      <c r="I831" s="54">
+        <v>108075.3</v>
+      </c>
+      <c r="J831" s="54">
+        <v>108551.75</v>
+      </c>
+      <c r="K831" s="54">
+        <v>105789.27</v>
+      </c>
+      <c r="L831" s="54">
+        <v>105789.27</v>
       </c>
     </row>
     <row r="832" spans="1:12">
       <c r="A832" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="B832" s="41" t="s">
-        <v>671</v>
-      </c>
-      <c r="C832" s="45" t="s">
-        <v>672</v>
+      <c r="B832" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C832" s="20" t="s">
+        <v>656</v>
       </c>
       <c r="D832" s="10" t="s">
-        <v>19</v>
+        <v>710</v>
       </c>
       <c r="E832" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F832" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="F832" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="G832" s="55">
-        <v>0</v>
+        <v>62476.1</v>
       </c>
       <c r="H832" s="55">
-        <v>0</v>
+        <v>63892.32</v>
       </c>
       <c r="I832" s="55">
-        <v>0</v>
+        <v>64778.33</v>
       </c>
       <c r="J832" s="55">
-        <v>0</v>
+        <v>65726.7</v>
       </c>
       <c r="K832" s="55">
-        <v>0</v>
+        <v>67206.37</v>
       </c>
       <c r="L832" s="55">
-        <v>0</v>
+        <v>67206.37</v>
       </c>
     </row>
     <row r="833" spans="1:12">
       <c r="A833" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="B833" s="7" t="s">
-        <v>673</v>
-      </c>
-      <c r="C833" s="42" t="s">
-        <v>674</v>
+      <c r="B833" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="C833" s="20" t="s">
+        <v>712</v>
       </c>
       <c r="D833" s="10" t="s">
-        <v>19</v>
+        <v>713</v>
       </c>
       <c r="E833" s="10" t="s">
         <v>125</v>
       </c>
       <c r="F833" s="10" t="s">
-        <v>126</v>
+        <v>714</v>
       </c>
       <c r="G833" s="55">
-        <v>16134.05</v>
+        <v>0</v>
       </c>
       <c r="H833" s="55">
-        <v>16067.17</v>
+        <v>0</v>
       </c>
       <c r="I833" s="55">
-        <v>21047.88</v>
+        <v>0</v>
       </c>
       <c r="J833" s="55">
         <v>0</v>
@@ -40169,92 +40231,104 @@
       </c>
     </row>
     <row r="834" spans="1:12">
-      <c r="A834" s="7" t="s">
+      <c r="A834" s="41" t="s">
         <v>655</v>
       </c>
       <c r="B834" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="C834" s="45" t="s">
-        <v>675</v>
+        <v>32</v>
+      </c>
+      <c r="C834" s="5" t="s">
+        <v>715</v>
       </c>
       <c r="D834" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E834" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F834" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G834" s="55"/>
-      <c r="H834" s="55"/>
-      <c r="I834" s="55"/>
+        <v>697</v>
+      </c>
+      <c r="G834" s="55">
+        <v>117240.88</v>
+      </c>
+      <c r="H834" s="55">
+        <v>120226.22</v>
+      </c>
+      <c r="I834" s="55">
+        <v>122541.13</v>
+      </c>
       <c r="J834" s="55">
-        <v>9859.2000000000007</v>
+        <v>125168.34</v>
       </c>
       <c r="K834" s="55">
-        <v>9864.1299999999992</v>
+        <v>131942.32</v>
       </c>
       <c r="L834" s="55">
-        <v>9864.1299999999992</v>
+        <v>131942.32</v>
       </c>
     </row>
     <row r="835" spans="1:12">
-      <c r="A835" s="7" t="s">
+      <c r="A835" s="41" t="s">
         <v>655</v>
       </c>
       <c r="B835" s="41" t="s">
-        <v>676</v>
-      </c>
-      <c r="C835" s="45" t="s">
-        <v>677</v>
+        <v>657</v>
+      </c>
+      <c r="C835" s="5" t="s">
+        <v>658</v>
       </c>
       <c r="D835" s="10" t="s">
-        <v>46</v>
+        <v>710</v>
       </c>
       <c r="E835" s="10" t="s">
         <v>20</v>
       </c>
       <c r="F835" s="10" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G835" s="55"/>
       <c r="H835" s="55"/>
       <c r="I835" s="55"/>
-      <c r="J835" s="55">
-        <v>9799.82</v>
-      </c>
+      <c r="J835" s="55"/>
       <c r="K835" s="55">
-        <v>9804.7900000000009</v>
+        <v>1000</v>
       </c>
       <c r="L835" s="55">
-        <v>9804.7900000000009</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="836" spans="1:12">
-      <c r="A836" s="7" t="s">
+      <c r="A836" s="41" t="s">
         <v>655</v>
       </c>
       <c r="B836" s="41" t="s">
-        <v>678</v>
-      </c>
-      <c r="C836" s="20" t="s">
-        <v>679</v>
+        <v>659</v>
+      </c>
+      <c r="C836" s="5" t="s">
+        <v>660</v>
       </c>
       <c r="D836" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E836" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F836" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G836" s="55"/>
-      <c r="H836" s="55"/>
-      <c r="I836" s="55"/>
-      <c r="J836" s="55"/>
+        <v>38</v>
+      </c>
+      <c r="G836" s="55">
+        <v>0</v>
+      </c>
+      <c r="H836" s="55">
+        <v>0</v>
+      </c>
+      <c r="I836" s="55">
+        <v>0</v>
+      </c>
+      <c r="J836" s="55">
+        <v>0</v>
+      </c>
       <c r="K836" s="55">
         <v>0</v>
       </c>
@@ -40263,90 +40337,82 @@
       </c>
     </row>
     <row r="837" spans="1:12">
-      <c r="A837" s="12" t="s">
+      <c r="A837" s="41" t="s">
         <v>655</v>
       </c>
-      <c r="B837" s="41" t="s">
-        <v>680</v>
-      </c>
-      <c r="C837" s="20" t="s">
-        <v>681</v>
+      <c r="B837" s="53" t="s">
+        <v>716</v>
+      </c>
+      <c r="C837" s="5" t="s">
+        <v>717</v>
       </c>
       <c r="D837" s="10" t="s">
-        <v>19</v>
+        <v>713</v>
       </c>
       <c r="E837" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F837" s="5" t="s">
-        <v>33</v>
+        <v>125</v>
+      </c>
+      <c r="F837" s="10" t="s">
+        <v>714</v>
       </c>
       <c r="G837" s="55">
-        <v>439231.76</v>
+        <v>0</v>
       </c>
       <c r="H837" s="55">
-        <v>439525.45</v>
+        <v>0</v>
       </c>
       <c r="I837" s="55">
-        <v>549702.69999999995</v>
+        <v>0</v>
       </c>
       <c r="J837" s="55">
-        <v>551448.99</v>
+        <v>0</v>
       </c>
       <c r="K837" s="55">
-        <v>551673.94999999995</v>
+        <v>0</v>
       </c>
       <c r="L837" s="55">
-        <v>551673.94999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:12">
-      <c r="A838" s="7" t="s">
+      <c r="A838" s="41" t="s">
         <v>655</v>
       </c>
-      <c r="B838" s="7" t="s">
-        <v>682</v>
-      </c>
-      <c r="C838" s="20" t="s">
-        <v>683</v>
+      <c r="B838" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C838" s="42" t="s">
+        <v>661</v>
       </c>
       <c r="D838" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E838" s="10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F838" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G838" s="55">
-        <v>299289.07</v>
-      </c>
-      <c r="H838" s="55">
-        <v>301225.59000000003</v>
-      </c>
-      <c r="I838" s="55">
-        <v>303430.18</v>
-      </c>
-      <c r="J838" s="55">
-        <v>306139.03999999998</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G838" s="55"/>
+      <c r="H838" s="55"/>
+      <c r="I838" s="55"/>
+      <c r="J838" s="55"/>
       <c r="K838" s="55">
-        <v>307847.58</v>
+        <v>0</v>
       </c>
       <c r="L838" s="55">
-        <v>307847.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="839" spans="1:12">
       <c r="A839" s="41" t="s">
         <v>655</v>
       </c>
-      <c r="B839" s="41" t="s">
-        <v>487</v>
-      </c>
-      <c r="C839" s="5" t="s">
-        <v>684</v>
+      <c r="B839" s="43" t="s">
+        <v>545</v>
+      </c>
+      <c r="C839" s="44" t="s">
+        <v>662</v>
       </c>
       <c r="D839" s="10" t="s">
         <v>19</v>
@@ -40354,37 +40420,37 @@
       <c r="E839" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F839" s="10" t="s">
-        <v>38</v>
+      <c r="F839" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="G839" s="55">
-        <v>0</v>
+        <v>142799.35</v>
       </c>
       <c r="H839" s="55">
-        <v>0</v>
+        <v>200631.22</v>
       </c>
       <c r="I839" s="55">
-        <v>0</v>
+        <v>260124.32</v>
       </c>
       <c r="J839" s="55">
-        <v>0</v>
+        <v>313433.53000000003</v>
       </c>
       <c r="K839" s="55">
-        <v>0</v>
+        <v>315102</v>
       </c>
       <c r="L839" s="55">
-        <v>0</v>
+        <v>315102</v>
       </c>
     </row>
     <row r="840" spans="1:12">
-      <c r="A840" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="B840" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C840" s="20" t="s">
-        <v>686</v>
+      <c r="A840" s="41" t="s">
+        <v>655</v>
+      </c>
+      <c r="B840" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="C840" s="44" t="s">
+        <v>663</v>
       </c>
       <c r="D840" s="10" t="s">
         <v>19</v>
@@ -40402,74 +40468,66 @@
         <v>0</v>
       </c>
       <c r="I840" s="55">
-        <v>0</v>
+        <v>17721.21</v>
       </c>
       <c r="J840" s="55">
-        <v>0</v>
+        <v>17737.8</v>
       </c>
       <c r="K840" s="55">
-        <v>0</v>
+        <v>17924.73</v>
       </c>
       <c r="L840" s="55">
-        <v>0</v>
+        <v>17924.73</v>
       </c>
     </row>
     <row r="841" spans="1:12">
-      <c r="A841" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="B841" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="C841" s="5" t="s">
-        <v>687</v>
+      <c r="A841" s="41" t="s">
+        <v>655</v>
+      </c>
+      <c r="B841" s="43" t="s">
+        <v>664</v>
+      </c>
+      <c r="C841" s="44" t="s">
+        <v>665</v>
       </c>
       <c r="D841" s="10" t="s">
         <v>19</v>
       </c>
       <c r="E841" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F841" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G841" s="55">
-        <v>537221.23</v>
-      </c>
-      <c r="H841" s="55">
-        <v>534084.6</v>
-      </c>
-      <c r="I841" s="55">
-        <v>549859.68999999994</v>
-      </c>
-      <c r="J841" s="55">
-        <v>557240.99</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F841" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G841" s="55"/>
+      <c r="H841" s="55"/>
+      <c r="I841" s="55"/>
+      <c r="J841" s="55"/>
       <c r="K841" s="55">
-        <v>557240.99</v>
+        <v>0</v>
       </c>
       <c r="L841" s="55">
-        <v>557240.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="842" spans="1:12">
-      <c r="A842" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="B842" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="C842" s="46" t="s">
-        <v>689</v>
+      <c r="A842" s="41" t="s">
+        <v>655</v>
+      </c>
+      <c r="B842" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="C842" s="5" t="s">
+        <v>666</v>
       </c>
       <c r="D842" s="10" t="s">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="E842" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F842" s="10" t="s">
-        <v>690</v>
+        <v>38</v>
       </c>
       <c r="G842" s="55">
         <v>0</v>
@@ -40478,27 +40536,27 @@
         <v>0</v>
       </c>
       <c r="I842" s="55">
-        <v>30010.87</v>
+        <v>0</v>
       </c>
       <c r="J842" s="55">
-        <v>30531.01</v>
+        <v>0</v>
       </c>
       <c r="K842" s="55">
-        <v>30531.01</v>
+        <v>0</v>
       </c>
       <c r="L842" s="55">
-        <v>30531.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="843" spans="1:12">
-      <c r="A843" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="B843" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="C843" s="46" t="s">
-        <v>691</v>
+      <c r="A843" s="41" t="s">
+        <v>655</v>
+      </c>
+      <c r="B843" s="41" t="s">
+        <v>667</v>
+      </c>
+      <c r="C843" s="5" t="s">
+        <v>668</v>
       </c>
       <c r="D843" s="10" t="s">
         <v>19</v>
@@ -40516,21 +40574,570 @@
         <v>0</v>
       </c>
       <c r="I843" s="55">
+        <v>161361.94</v>
+      </c>
+      <c r="J843" s="55">
+        <v>163040.57999999999</v>
+      </c>
+      <c r="K843" s="55">
+        <v>162864.82999999999</v>
+      </c>
+      <c r="L843" s="55">
+        <v>162864.82999999999</v>
+      </c>
+    </row>
+    <row r="844" spans="1:12">
+      <c r="A844" s="41" t="s">
+        <v>655</v>
+      </c>
+      <c r="B844" s="41" t="s">
+        <v>718</v>
+      </c>
+      <c r="C844" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D844" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="E844" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F844" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="G844" s="55">
+        <v>0</v>
+      </c>
+      <c r="H844" s="55">
+        <v>0</v>
+      </c>
+      <c r="I844" s="55">
+        <v>0</v>
+      </c>
+      <c r="J844" s="55">
+        <v>0</v>
+      </c>
+      <c r="K844" s="55">
+        <v>0</v>
+      </c>
+      <c r="L844" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" spans="1:12">
+      <c r="A845" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B845" s="41" t="s">
+        <v>720</v>
+      </c>
+      <c r="C845" s="20" t="s">
+        <v>721</v>
+      </c>
+      <c r="D845" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="E845" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F845" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="G845" s="55">
+        <v>0</v>
+      </c>
+      <c r="H845" s="55">
+        <v>0</v>
+      </c>
+      <c r="I845" s="55">
+        <v>0</v>
+      </c>
+      <c r="J845" s="55">
+        <v>0</v>
+      </c>
+      <c r="K845" s="55">
+        <v>0</v>
+      </c>
+      <c r="L845" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846" spans="1:12">
+      <c r="A846" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B846" s="41" t="s">
+        <v>669</v>
+      </c>
+      <c r="C846" s="45" t="s">
+        <v>670</v>
+      </c>
+      <c r="D846" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="E846" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F846" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G846" s="55">
+        <v>116648.98</v>
+      </c>
+      <c r="H846" s="55">
+        <v>118474.12</v>
+      </c>
+      <c r="I846" s="55">
+        <v>118915.05</v>
+      </c>
+      <c r="J846" s="55">
+        <v>120933.46</v>
+      </c>
+      <c r="K846" s="55">
+        <v>121791.84</v>
+      </c>
+      <c r="L846" s="55">
+        <v>121791.84</v>
+      </c>
+    </row>
+    <row r="847" spans="1:12">
+      <c r="A847" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B847" s="41" t="s">
+        <v>671</v>
+      </c>
+      <c r="C847" s="45" t="s">
+        <v>672</v>
+      </c>
+      <c r="D847" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E847" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F847" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G847" s="55">
+        <v>0</v>
+      </c>
+      <c r="H847" s="55">
+        <v>0</v>
+      </c>
+      <c r="I847" s="55">
+        <v>0</v>
+      </c>
+      <c r="J847" s="55">
+        <v>0</v>
+      </c>
+      <c r="K847" s="55">
+        <v>0</v>
+      </c>
+      <c r="L847" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848" spans="1:12">
+      <c r="A848" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B848" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="C848" s="42" t="s">
+        <v>674</v>
+      </c>
+      <c r="D848" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E848" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F848" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G848" s="55">
+        <v>16134.05</v>
+      </c>
+      <c r="H848" s="55">
+        <v>16067.17</v>
+      </c>
+      <c r="I848" s="55">
+        <v>21047.88</v>
+      </c>
+      <c r="J848" s="55">
+        <v>0</v>
+      </c>
+      <c r="K848" s="55">
+        <v>0</v>
+      </c>
+      <c r="L848" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849" spans="1:12">
+      <c r="A849" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B849" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="C849" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="D849" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E849" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F849" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G849" s="55"/>
+      <c r="H849" s="55"/>
+      <c r="I849" s="55"/>
+      <c r="J849" s="55">
+        <v>9859.2000000000007</v>
+      </c>
+      <c r="K849" s="55">
+        <v>9864.1299999999992</v>
+      </c>
+      <c r="L849" s="55">
+        <v>9864.1299999999992</v>
+      </c>
+    </row>
+    <row r="850" spans="1:12">
+      <c r="A850" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B850" s="41" t="s">
+        <v>676</v>
+      </c>
+      <c r="C850" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="D850" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E850" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F850" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G850" s="55"/>
+      <c r="H850" s="55"/>
+      <c r="I850" s="55"/>
+      <c r="J850" s="55">
+        <v>9799.82</v>
+      </c>
+      <c r="K850" s="55">
+        <v>9804.7900000000009</v>
+      </c>
+      <c r="L850" s="55">
+        <v>9804.7900000000009</v>
+      </c>
+    </row>
+    <row r="851" spans="1:12">
+      <c r="A851" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B851" s="41" t="s">
+        <v>678</v>
+      </c>
+      <c r="C851" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="D851" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E851" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F851" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G851" s="55"/>
+      <c r="H851" s="55"/>
+      <c r="I851" s="55"/>
+      <c r="J851" s="55"/>
+      <c r="K851" s="55">
+        <v>0</v>
+      </c>
+      <c r="L851" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852" spans="1:12">
+      <c r="A852" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="B852" s="41" t="s">
+        <v>680</v>
+      </c>
+      <c r="C852" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="D852" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E852" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F852" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G852" s="55">
+        <v>439231.76</v>
+      </c>
+      <c r="H852" s="55">
+        <v>439525.45</v>
+      </c>
+      <c r="I852" s="55">
+        <v>549702.69999999995</v>
+      </c>
+      <c r="J852" s="55">
+        <v>551448.99</v>
+      </c>
+      <c r="K852" s="55">
+        <v>551673.94999999995</v>
+      </c>
+      <c r="L852" s="55">
+        <v>551673.94999999995</v>
+      </c>
+    </row>
+    <row r="853" spans="1:12">
+      <c r="A853" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B853" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="C853" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="D853" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E853" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F853" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G853" s="55">
+        <v>299289.07</v>
+      </c>
+      <c r="H853" s="55">
+        <v>301225.59000000003</v>
+      </c>
+      <c r="I853" s="55">
+        <v>303430.18</v>
+      </c>
+      <c r="J853" s="55">
+        <v>306139.03999999998</v>
+      </c>
+      <c r="K853" s="55">
+        <v>307847.58</v>
+      </c>
+      <c r="L853" s="55">
+        <v>307847.58</v>
+      </c>
+    </row>
+    <row r="854" spans="1:12">
+      <c r="A854" s="41" t="s">
+        <v>655</v>
+      </c>
+      <c r="B854" s="41" t="s">
+        <v>487</v>
+      </c>
+      <c r="C854" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="D854" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E854" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F854" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G854" s="55">
+        <v>0</v>
+      </c>
+      <c r="H854" s="55">
+        <v>0</v>
+      </c>
+      <c r="I854" s="55">
+        <v>0</v>
+      </c>
+      <c r="J854" s="55">
+        <v>0</v>
+      </c>
+      <c r="K854" s="55">
+        <v>0</v>
+      </c>
+      <c r="L854" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855" spans="1:12">
+      <c r="A855" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="B855" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C855" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="D855" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E855" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F855" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G855" s="55">
+        <v>0</v>
+      </c>
+      <c r="H855" s="55">
+        <v>0</v>
+      </c>
+      <c r="I855" s="55">
+        <v>0</v>
+      </c>
+      <c r="J855" s="55">
+        <v>0</v>
+      </c>
+      <c r="K855" s="55">
+        <v>0</v>
+      </c>
+      <c r="L855" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856" spans="1:12">
+      <c r="A856" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="B856" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="C856" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="D856" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E856" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F856" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G856" s="55">
+        <v>537221.23</v>
+      </c>
+      <c r="H856" s="55">
+        <v>534084.6</v>
+      </c>
+      <c r="I856" s="55">
+        <v>549859.68999999994</v>
+      </c>
+      <c r="J856" s="55">
+        <v>557240.99</v>
+      </c>
+      <c r="K856" s="55">
+        <v>557240.99</v>
+      </c>
+      <c r="L856" s="55">
+        <v>557240.99</v>
+      </c>
+    </row>
+    <row r="857" spans="1:12">
+      <c r="A857" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="B857" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C857" s="46" t="s">
+        <v>689</v>
+      </c>
+      <c r="D857" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E857" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F857" s="10" t="s">
+        <v>690</v>
+      </c>
+      <c r="G857" s="55">
+        <v>0</v>
+      </c>
+      <c r="H857" s="55">
+        <v>0</v>
+      </c>
+      <c r="I857" s="55">
+        <v>30010.87</v>
+      </c>
+      <c r="J857" s="55">
+        <v>30531.01</v>
+      </c>
+      <c r="K857" s="55">
+        <v>30531.01</v>
+      </c>
+      <c r="L857" s="55">
+        <v>30531.01</v>
+      </c>
+    </row>
+    <row r="858" spans="1:12">
+      <c r="A858" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="B858" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C858" s="46" t="s">
+        <v>691</v>
+      </c>
+      <c r="D858" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E858" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F858" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G858" s="55">
+        <v>0</v>
+      </c>
+      <c r="H858" s="55">
+        <v>0</v>
+      </c>
+      <c r="I858" s="55">
         <v>219000</v>
       </c>
-      <c r="J843" s="55">
+      <c r="J858" s="55">
         <v>219000</v>
       </c>
-      <c r="K843" s="55">
+      <c r="K858" s="55">
         <v>219000</v>
       </c>
-      <c r="L843" s="55">
+      <c r="L858" s="55">
         <v>219000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L843" xr:uid="{73121E59-3896-423B-A6D4-88AA04C4094C}"/>
-  <conditionalFormatting sqref="E2:E720 E792:E843">
+  <conditionalFormatting sqref="E2:E720 E792:E858">
     <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"Conquest"</formula>
     </cfRule>
@@ -40539,28 +41146,28 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E840:E843" xr:uid="{19E01F5B-073B-4F14-8CA3-ED94EC9E9723}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E855:E858" xr:uid="{19E01F5B-073B-4F14-8CA3-ED94EC9E9723}">
       <formula1>"DF,SP,GO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D840:D843" xr:uid="{6CF9EFBF-2F7B-4DC5-BB7E-E4FA9C3ECD4C}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D855:D858" xr:uid="{6CF9EFBF-2F7B-4DC5-BB7E-E4FA9C3ECD4C}">
       <formula1>"Bluemetrix,Vcinvest,Nexco"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D816" xr:uid="{E4EF4B2A-4DF5-4F3B-B254-92DB49DDB533}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D831" xr:uid="{E4EF4B2A-4DF5-4F3B-B254-92DB49DDB533}">
       <formula1>"Bluemetrix,Voga,Conquest,VcInvest,MI Smart,Altum,Poupinvista,Solution For Life,Miura,Expert"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E816 E2:E720" xr:uid="{9DD72545-26F8-4BBD-9958-B686C5A2E60C}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E831 E2:E720" xr:uid="{9DD72545-26F8-4BBD-9958-B686C5A2E60C}">
       <formula1>"DF,GO,SUL,SP,RJ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E817:E839" xr:uid="{6357B105-7D02-4F64-9527-44F2D0849E84}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E832:E854" xr:uid="{6357B105-7D02-4F64-9527-44F2D0849E84}">
       <formula1>"DF,SP,GO,SUL,RJ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D817:D839" xr:uid="{C3E3039A-3F42-44C5-B999-A66A6203E241}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D832:D854" xr:uid="{C3E3039A-3F42-44C5-B999-A66A6203E241}">
       <formula1>"Bluemetrix,Vcinvest,Voga,Bullside,Miura,Expert"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D792:D815" xr:uid="{85C74F63-B89F-4B56-96C4-E121BD3ED2D8}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D792:D830" xr:uid="{85C74F63-B89F-4B56-96C4-E121BD3ED2D8}">
       <formula1>"Bluemetrix,Voga,Conquest"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E792:E815" xr:uid="{AC4F4B29-1C8B-48C7-BAAD-471A0EFDF01F}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E792:E830" xr:uid="{AC4F4B29-1C8B-48C7-BAAD-471A0EFDF01F}">
       <formula1>"DF,GO,SUL,SP"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E721:E791" xr:uid="{1EE7B329-2F84-4B04-B2FF-0C258186E699}">
